--- a/research/traditional_assets/database/data/lithuania/lithuania_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_real_estate_operations_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nsel_inr1l" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.04379999999999999</v>
+        <v>-0.0393</v>
       </c>
       <c r="E2">
-        <v>0.0319</v>
+        <v>0.0199</v>
       </c>
       <c r="G2">
-        <v>0.2891278375149343</v>
+        <v>0.2569219256672488</v>
       </c>
       <c r="H2">
-        <v>0.2891278375149343</v>
+        <v>0.2569219256672488</v>
       </c>
       <c r="I2">
-        <v>0.09510155316606929</v>
+        <v>0.3983537041656274</v>
       </c>
       <c r="J2">
-        <v>0.08839075808378617</v>
+        <v>0.3685608641061813</v>
       </c>
       <c r="K2">
-        <v>7.26</v>
+        <v>6.41</v>
       </c>
       <c r="L2">
-        <v>1.734767025089605</v>
+        <v>1.598902469443752</v>
       </c>
       <c r="M2">
-        <v>14.46</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>0.2927125506072875</v>
+        <v>0.02186147186147186</v>
       </c>
       <c r="O2">
-        <v>1.991735537190083</v>
+        <v>0.1575663026521061</v>
       </c>
       <c r="P2">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="Q2">
-        <v>0.02348178137651821</v>
+        <v>0.02186147186147186</v>
       </c>
       <c r="R2">
-        <v>0.1597796143250689</v>
+        <v>0.1575663026521061</v>
       </c>
       <c r="S2">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.9197786998616874</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4.92</v>
+        <v>1.7</v>
       </c>
       <c r="V2">
-        <v>0.09959514170040484</v>
+        <v>0.03679653679653679</v>
       </c>
       <c r="W2">
-        <v>0.1462931995540691</v>
+        <v>0.1659128524570431</v>
       </c>
       <c r="X2">
-        <v>0.05273363473150196</v>
+        <v>0.09386779698902159</v>
       </c>
       <c r="Y2">
-        <v>0.09355956482256715</v>
+        <v>0.07204505546802153</v>
       </c>
       <c r="Z2">
-        <v>0.06987810986809151</v>
+        <v>0.0911550704865848</v>
       </c>
       <c r="AA2">
-        <v>0.01175180601419026</v>
+        <v>0.03492939888219439</v>
       </c>
       <c r="AB2">
-        <v>0.04656134097309977</v>
+        <v>0.08074153314491449</v>
       </c>
       <c r="AC2">
-        <v>-0.03480953495890951</v>
+        <v>-0.0458121342627201</v>
       </c>
       <c r="AD2">
-        <v>12.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12.1</v>
+        <v>14.8</v>
       </c>
       <c r="AG2">
-        <v>7.18</v>
+        <v>13.1</v>
       </c>
       <c r="AH2">
-        <v>0.1967479674796748</v>
+        <v>0.2426229508196721</v>
       </c>
       <c r="AI2">
-        <v>0.2474437627811861</v>
+        <v>0.2879377431906615</v>
       </c>
       <c r="AJ2">
-        <v>0.1268999646518204</v>
+        <v>0.2209106239460371</v>
       </c>
       <c r="AK2">
-        <v>0.163256025466121</v>
+        <v>0.2635814889336016</v>
       </c>
       <c r="AL2">
-        <v>0.413</v>
+        <v>0.307</v>
       </c>
       <c r="AM2">
-        <v>0.386</v>
+        <v>0.291</v>
       </c>
       <c r="AN2">
-        <v>161.3333333333333</v>
+        <v>15.0253807106599</v>
       </c>
       <c r="AO2">
-        <v>0.963680387409201</v>
+        <v>5.201954397394137</v>
       </c>
       <c r="AP2">
-        <v>95.73333333333333</v>
+        <v>13.2994923857868</v>
       </c>
       <c r="AQ2">
-        <v>1.031088082901555</v>
+        <v>5.487972508591065</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INVL Baltic Farmland, AB (NSEL:INL1L)</t>
+          <t>AB INVL Baltic Farmland (NSEL:INL1L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,10 +724,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0534</v>
+        <v>0.0574</v>
       </c>
       <c r="E3">
-        <v>0.0216</v>
+        <v>0.0757</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,16 +736,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5622641509433962</v>
+        <v>0.9931412894375857</v>
       </c>
       <c r="J3">
-        <v>0.4829123554473524</v>
+        <v>0.8477170291985108</v>
       </c>
       <c r="K3">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="L3">
-        <v>1.333333333333333</v>
+        <v>2.290809327846365</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -773,25 +775,25 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.06794871794871796</v>
+        <v>0.1050314465408805</v>
       </c>
       <c r="X3">
-        <v>0.0454146986775453</v>
+        <v>0.07983877944908858</v>
       </c>
       <c r="Y3">
-        <v>0.02253401927117266</v>
+        <v>0.02519266709179191</v>
       </c>
       <c r="Z3">
-        <v>0.05096153846153847</v>
+        <v>0.04584905660377359</v>
       </c>
       <c r="AA3">
-        <v>0.02460995657568239</v>
+        <v>0.03886702605570531</v>
       </c>
       <c r="AB3">
-        <v>0.0454146986775453</v>
+        <v>0.07983877944908858</v>
       </c>
       <c r="AC3">
-        <v>-0.02080474210186292</v>
+        <v>-0.04097175339338328</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -841,121 +843,8833 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.141</v>
+        <v>-0.136</v>
       </c>
       <c r="E4">
-        <v>0.04219999999999999</v>
+        <v>-0.0359</v>
       </c>
       <c r="G4">
-        <v>0.3569321533923304</v>
+        <v>0.3140243902439024</v>
       </c>
       <c r="H4">
-        <v>0.3569321533923304</v>
+        <v>0.3140243902439024</v>
       </c>
       <c r="I4">
-        <v>-0.01445427728613569</v>
+        <v>0.2661585365853659</v>
       </c>
       <c r="J4">
-        <v>-0.01445427728613569</v>
+        <v>0.2653198017011683</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>4.74</v>
       </c>
       <c r="L4">
-        <v>1.828908554572271</v>
+        <v>1.445121951219512</v>
       </c>
       <c r="M4">
-        <v>14.46</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0.6788732394366197</v>
+        <v>0.05489130434782609</v>
       </c>
       <c r="O4">
-        <v>2.332258064516129</v>
+        <v>0.2130801687763713</v>
       </c>
       <c r="P4">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="Q4">
-        <v>0.05446009389671361</v>
+        <v>0.05489130434782609</v>
       </c>
       <c r="R4">
-        <v>0.1870967741935484</v>
+        <v>0.2130801687763713</v>
       </c>
       <c r="S4">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.9197786998616874</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>4.92</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
-        <v>0.2309859154929577</v>
+        <v>0.09239130434782609</v>
       </c>
       <c r="W4">
-        <v>0.2246376811594203</v>
+        <v>0.2267942583732058</v>
       </c>
       <c r="X4">
-        <v>0.06005257078545861</v>
+        <v>0.1078968145289546</v>
       </c>
       <c r="Y4">
-        <v>0.1645851103739617</v>
+        <v>0.1188974438442512</v>
       </c>
       <c r="Z4">
-        <v>0.07654097990517048</v>
+        <v>0.1168091168091168</v>
       </c>
       <c r="AA4">
-        <v>-0.001106344547301874</v>
+        <v>0.03099177170868347</v>
       </c>
       <c r="AB4">
-        <v>0.04770798326865423</v>
+        <v>0.08164428684074039</v>
       </c>
       <c r="AC4">
-        <v>-0.04881432781595611</v>
+        <v>-0.05065251513205692</v>
       </c>
       <c r="AD4">
-        <v>12.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>12.1</v>
+        <v>14.8</v>
       </c>
       <c r="AG4">
-        <v>7.18</v>
+        <v>13.1</v>
       </c>
       <c r="AH4">
-        <v>0.3622754491017964</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="AI4">
-        <v>0.3666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="AJ4">
-        <v>0.2521067415730337</v>
+        <v>0.4158730158730159</v>
       </c>
       <c r="AK4">
-        <v>0.2556980056980057</v>
+        <v>0.3711048158640227</v>
       </c>
       <c r="AL4">
-        <v>0.413</v>
+        <v>0.307</v>
       </c>
       <c r="AM4">
-        <v>0.386</v>
+        <v>0.291</v>
       </c>
       <c r="AN4">
-        <v>161.3333333333333</v>
+        <v>15.0253807106599</v>
       </c>
       <c r="AO4">
-        <v>-0.1186440677966102</v>
+        <v>2.843648208469055</v>
       </c>
       <c r="AP4">
-        <v>95.73333333333333</v>
+        <v>13.2994923857868</v>
       </c>
       <c r="AQ4">
-        <v>-0.1269430051813472</v>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Special Closed-Ended Type Real Estate Investment Company INVL BALTIC REAL ESTATE (NSEL:INR1L)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NSEL:INR1L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.44578313253012</v>
+      </c>
+      <c r="F2">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>18.4</v>
+      </c>
+      <c r="H2">
+        <v>33.4548936424252</v>
+      </c>
+      <c r="I2">
+        <v>31.5</v>
+      </c>
+      <c r="J2">
+        <v>33.0828936424252</v>
+      </c>
+      <c r="K2">
+        <v>14.8</v>
+      </c>
+      <c r="L2">
+        <v>1.328</v>
+      </c>
+      <c r="M2">
+        <v>0.0816442868407404</v>
+      </c>
+      <c r="N2">
+        <v>0.07959434677239401</v>
+      </c>
+      <c r="O2">
+        <v>0.0490060091743119</v>
+      </c>
+      <c r="P2">
+        <v>0.038845</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.107896814528955</v>
+      </c>
+      <c r="T2">
+        <v>0.0812922362212438</v>
+      </c>
+      <c r="U2">
+        <v>0.936928936510054</v>
+      </c>
+      <c r="V2">
+        <v>0.576180044827115</v>
+      </c>
+      <c r="W2">
+        <v>14.38467216788379</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>18.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.05765412844036698</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.985</v>
+      </c>
+      <c r="AH2">
+        <v>0.112</v>
+      </c>
+      <c r="AI2">
+        <v>2.342</v>
+      </c>
+      <c r="AJ2">
+        <v>14.8</v>
+      </c>
+      <c r="AK2">
+        <v>14.8</v>
+      </c>
+      <c r="AL2">
+        <v>0.307</v>
+      </c>
+      <c r="AM2">
+        <v>14.8</v>
+      </c>
+      <c r="AN2">
+        <v>1.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07983877944908858</v>
+      </c>
+      <c r="C2">
+        <v>34.58584732783263</v>
+      </c>
+      <c r="D2">
+        <v>32.88584732783263</v>
+      </c>
+      <c r="E2">
+        <v>-14.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.7</v>
+      </c>
+      <c r="H2">
+        <v>18.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.985</v>
+      </c>
+      <c r="K2">
+        <v>0.112</v>
+      </c>
+      <c r="L2">
+        <v>0.873</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.873</v>
+      </c>
+      <c r="O2">
+        <v>0.13095</v>
+      </c>
+      <c r="P2">
+        <v>0.74205</v>
+      </c>
+      <c r="Q2">
+        <v>0.85405</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07983877944908858</v>
+      </c>
+      <c r="T2">
+        <v>0.5564716730724656</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07977767127991493</v>
+      </c>
+      <c r="C3">
+        <v>34.30288852171114</v>
+      </c>
+      <c r="D3">
+        <v>32.93488852171114</v>
+      </c>
+      <c r="E3">
+        <v>-14.468</v>
+      </c>
+      <c r="F3">
+        <v>0.332</v>
+      </c>
+      <c r="G3">
+        <v>1.7</v>
+      </c>
+      <c r="H3">
+        <v>18.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.985</v>
+      </c>
+      <c r="K3">
+        <v>0.112</v>
+      </c>
+      <c r="L3">
+        <v>0.873</v>
+      </c>
+      <c r="M3">
+        <v>0.0151724</v>
+      </c>
+      <c r="N3">
+        <v>0.8578276</v>
+      </c>
+      <c r="O3">
+        <v>0.12867414</v>
+      </c>
+      <c r="P3">
+        <v>0.72915346</v>
+      </c>
+      <c r="Q3">
+        <v>0.84115346</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08019113260597469</v>
+      </c>
+      <c r="T3">
+        <v>0.5612494601645018</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>57.53868867153515</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07971656311074132</v>
+      </c>
+      <c r="C4">
+        <v>34.02007619991499</v>
+      </c>
+      <c r="D4">
+        <v>32.98407619991499</v>
+      </c>
+      <c r="E4">
+        <v>-14.136</v>
+      </c>
+      <c r="F4">
+        <v>0.664</v>
+      </c>
+      <c r="G4">
+        <v>1.7</v>
+      </c>
+      <c r="H4">
+        <v>18.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.985</v>
+      </c>
+      <c r="K4">
+        <v>0.112</v>
+      </c>
+      <c r="L4">
+        <v>0.873</v>
+      </c>
+      <c r="M4">
+        <v>0.03034480000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.8426552</v>
+      </c>
+      <c r="O4">
+        <v>0.12639828</v>
+      </c>
+      <c r="P4">
+        <v>0.71625692</v>
+      </c>
+      <c r="Q4">
+        <v>0.82825692</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08055067664361359</v>
+      </c>
+      <c r="T4">
+        <v>0.5661247531155594</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>28.76934433576757</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07965545494156767</v>
+      </c>
+      <c r="C5">
+        <v>33.73741101974122</v>
+      </c>
+      <c r="D5">
+        <v>33.03341101974122</v>
+      </c>
+      <c r="E5">
+        <v>-13.804</v>
+      </c>
+      <c r="F5">
+        <v>0.996</v>
+      </c>
+      <c r="G5">
+        <v>1.7</v>
+      </c>
+      <c r="H5">
+        <v>18.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.985</v>
+      </c>
+      <c r="K5">
+        <v>0.112</v>
+      </c>
+      <c r="L5">
+        <v>0.873</v>
+      </c>
+      <c r="M5">
+        <v>0.04551720000000001</v>
+      </c>
+      <c r="N5">
+        <v>0.8274828</v>
+      </c>
+      <c r="O5">
+        <v>0.12412242</v>
+      </c>
+      <c r="P5">
+        <v>0.7033603799999999</v>
+      </c>
+      <c r="Q5">
+        <v>0.8153603799999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08091763396037904</v>
+      </c>
+      <c r="T5">
+        <v>0.5711005675707623</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>19.17956289051171</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07959434677239403</v>
+      </c>
+      <c r="C6">
+        <v>33.45489364242517</v>
+      </c>
+      <c r="D6">
+        <v>33.08289364242517</v>
+      </c>
+      <c r="E6">
+        <v>-13.472</v>
+      </c>
+      <c r="F6">
+        <v>1.328</v>
+      </c>
+      <c r="G6">
+        <v>1.7</v>
+      </c>
+      <c r="H6">
+        <v>18.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.985</v>
+      </c>
+      <c r="K6">
+        <v>0.112</v>
+      </c>
+      <c r="L6">
+        <v>0.873</v>
+      </c>
+      <c r="M6">
+        <v>0.06068960000000001</v>
+      </c>
+      <c r="N6">
+        <v>0.8123104</v>
+      </c>
+      <c r="O6">
+        <v>0.12184656</v>
+      </c>
+      <c r="P6">
+        <v>0.6904638399999999</v>
+      </c>
+      <c r="Q6">
+        <v>0.8024638399999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08129223622124379</v>
+      </c>
+      <c r="T6">
+        <v>0.5761800448271154</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>14.38467216788379</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07960123860322042</v>
+      </c>
+      <c r="C7">
+        <v>33.11730553495499</v>
+      </c>
+      <c r="D7">
+        <v>33.07730553495499</v>
+      </c>
+      <c r="E7">
+        <v>-13.14</v>
+      </c>
+      <c r="F7">
+        <v>1.66</v>
+      </c>
+      <c r="G7">
+        <v>1.7</v>
+      </c>
+      <c r="H7">
+        <v>18.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.985</v>
+      </c>
+      <c r="K7">
+        <v>0.112</v>
+      </c>
+      <c r="L7">
+        <v>0.873</v>
+      </c>
+      <c r="M7">
+        <v>0.078518</v>
+      </c>
+      <c r="N7">
+        <v>0.794482</v>
+      </c>
+      <c r="O7">
+        <v>0.1191723</v>
+      </c>
+      <c r="P7">
+        <v>0.6753097</v>
+      </c>
+      <c r="Q7">
+        <v>0.7873097</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08167472484549518</v>
+      </c>
+      <c r="T7">
+        <v>0.5813664584467602</v>
+      </c>
+      <c r="U7">
+        <v>0.0473</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.040205</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>11.11846965027127</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07974753043404677</v>
+      </c>
+      <c r="C8">
+        <v>32.6671313853978</v>
+      </c>
+      <c r="D8">
+        <v>32.9591313853978</v>
+      </c>
+      <c r="E8">
+        <v>-12.808</v>
+      </c>
+      <c r="F8">
+        <v>1.992</v>
+      </c>
+      <c r="G8">
+        <v>1.7</v>
+      </c>
+      <c r="H8">
+        <v>18.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.985</v>
+      </c>
+      <c r="K8">
+        <v>0.112</v>
+      </c>
+      <c r="L8">
+        <v>0.873</v>
+      </c>
+      <c r="M8">
+        <v>0.1017912</v>
+      </c>
+      <c r="N8">
+        <v>0.7712088</v>
+      </c>
+      <c r="O8">
+        <v>0.11568132</v>
+      </c>
+      <c r="P8">
+        <v>0.6555274800000001</v>
+      </c>
+      <c r="Q8">
+        <v>0.76752748</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08206535152558167</v>
+      </c>
+      <c r="T8">
+        <v>0.5866632212923546</v>
+      </c>
+      <c r="U8">
+        <v>0.0511</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.043435</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>8.576379883526279</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07984537226487315</v>
+      </c>
+      <c r="C9">
+        <v>32.25656511643125</v>
+      </c>
+      <c r="D9">
+        <v>32.88056511643124</v>
+      </c>
+      <c r="E9">
+        <v>-12.476</v>
+      </c>
+      <c r="F9">
+        <v>2.324</v>
+      </c>
+      <c r="G9">
+        <v>1.7</v>
+      </c>
+      <c r="H9">
+        <v>18.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.985</v>
+      </c>
+      <c r="K9">
+        <v>0.112</v>
+      </c>
+      <c r="L9">
+        <v>0.873</v>
+      </c>
+      <c r="M9">
+        <v>0.123172</v>
+      </c>
+      <c r="N9">
+        <v>0.7498279999999999</v>
+      </c>
+      <c r="O9">
+        <v>0.1124742</v>
+      </c>
+      <c r="P9">
+        <v>0.6373538</v>
+      </c>
+      <c r="Q9">
+        <v>0.7493538</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08246437877943349</v>
+      </c>
+      <c r="T9">
+        <v>0.5920738930163492</v>
+      </c>
+      <c r="U9">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>7.087649790536808</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07998231409569953</v>
+      </c>
+      <c r="C10">
+        <v>31.8152287451145</v>
+      </c>
+      <c r="D10">
+        <v>32.7712287451145</v>
+      </c>
+      <c r="E10">
+        <v>-12.144</v>
+      </c>
+      <c r="F10">
+        <v>2.656</v>
+      </c>
+      <c r="G10">
+        <v>1.7</v>
+      </c>
+      <c r="H10">
+        <v>18.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.985</v>
+      </c>
+      <c r="K10">
+        <v>0.112</v>
+      </c>
+      <c r="L10">
+        <v>0.873</v>
+      </c>
+      <c r="M10">
+        <v>0.14608</v>
+      </c>
+      <c r="N10">
+        <v>0.72692</v>
+      </c>
+      <c r="O10">
+        <v>0.109038</v>
+      </c>
+      <c r="P10">
+        <v>0.617882</v>
+      </c>
+      <c r="Q10">
+        <v>0.729882</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08287208053880382</v>
+      </c>
+      <c r="T10">
+        <v>0.5976021880386914</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.04675</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.976177437020811</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0800002559265259</v>
+      </c>
+      <c r="C11">
+        <v>31.46895757546046</v>
+      </c>
+      <c r="D11">
+        <v>32.75695757546046</v>
+      </c>
+      <c r="E11">
+        <v>-11.812</v>
+      </c>
+      <c r="F11">
+        <v>2.988</v>
+      </c>
+      <c r="G11">
+        <v>1.7</v>
+      </c>
+      <c r="H11">
+        <v>18.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.985</v>
+      </c>
+      <c r="K11">
+        <v>0.112</v>
+      </c>
+      <c r="L11">
+        <v>0.873</v>
+      </c>
+      <c r="M11">
+        <v>0.16434</v>
+      </c>
+      <c r="N11">
+        <v>0.70866</v>
+      </c>
+      <c r="O11">
+        <v>0.106299</v>
+      </c>
+      <c r="P11">
+        <v>0.6023609999999999</v>
+      </c>
+      <c r="Q11">
+        <v>0.7143609999999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08328874277640208</v>
+      </c>
+      <c r="T11">
+        <v>0.6032519840505355</v>
+      </c>
+      <c r="U11">
+        <v>0.055</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.04675</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>5.312157721796275</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08001819775735225</v>
+      </c>
+      <c r="C12">
+        <v>31.12269882997468</v>
+      </c>
+      <c r="D12">
+        <v>32.74269882997468</v>
+      </c>
+      <c r="E12">
+        <v>-11.48</v>
+      </c>
+      <c r="F12">
+        <v>3.32</v>
+      </c>
+      <c r="G12">
+        <v>1.7</v>
+      </c>
+      <c r="H12">
+        <v>18.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.985</v>
+      </c>
+      <c r="K12">
+        <v>0.112</v>
+      </c>
+      <c r="L12">
+        <v>0.873</v>
+      </c>
+      <c r="M12">
+        <v>0.1826</v>
+      </c>
+      <c r="N12">
+        <v>0.6904</v>
+      </c>
+      <c r="O12">
+        <v>0.10356</v>
+      </c>
+      <c r="P12">
+        <v>0.58684</v>
+      </c>
+      <c r="Q12">
+        <v>0.69884</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08371466417483583</v>
+      </c>
+      <c r="T12">
+        <v>0.6090273310848652</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.04675</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>4.780941949616649</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08039143958817863</v>
+      </c>
+      <c r="C13">
+        <v>30.49686565231833</v>
+      </c>
+      <c r="D13">
+        <v>32.44886565231833</v>
+      </c>
+      <c r="E13">
+        <v>-11.148</v>
+      </c>
+      <c r="F13">
+        <v>3.652</v>
+      </c>
+      <c r="G13">
+        <v>1.7</v>
+      </c>
+      <c r="H13">
+        <v>18.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.985</v>
+      </c>
+      <c r="K13">
+        <v>0.112</v>
+      </c>
+      <c r="L13">
+        <v>0.873</v>
+      </c>
+      <c r="M13">
+        <v>0.2147376</v>
+      </c>
+      <c r="N13">
+        <v>0.6582623999999999</v>
+      </c>
+      <c r="O13">
+        <v>0.09873936</v>
+      </c>
+      <c r="P13">
+        <v>0.55952304</v>
+      </c>
+      <c r="Q13">
+        <v>0.67152304</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08415015684065014</v>
+      </c>
+      <c r="T13">
+        <v>0.6149324611986179</v>
+      </c>
+      <c r="U13">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.04998</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>4.065426827905313</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08159428141900499</v>
+      </c>
+      <c r="C14">
+        <v>29.25280797369262</v>
+      </c>
+      <c r="D14">
+        <v>31.53680797369262</v>
+      </c>
+      <c r="E14">
+        <v>-10.816</v>
+      </c>
+      <c r="F14">
+        <v>3.984</v>
+      </c>
+      <c r="G14">
+        <v>1.7</v>
+      </c>
+      <c r="H14">
+        <v>18.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.985</v>
+      </c>
+      <c r="K14">
+        <v>0.112</v>
+      </c>
+      <c r="L14">
+        <v>0.873</v>
+      </c>
+      <c r="M14">
+        <v>0.2792784</v>
+      </c>
+      <c r="N14">
+        <v>0.5937216000000001</v>
+      </c>
+      <c r="O14">
+        <v>0.08905824000000002</v>
+      </c>
+      <c r="P14">
+        <v>0.50466336</v>
+      </c>
+      <c r="Q14">
+        <v>0.61666336</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08459554706705112</v>
+      </c>
+      <c r="T14">
+        <v>0.6209717988149559</v>
+      </c>
+      <c r="U14">
+        <v>0.0701</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>3.125913067390819</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08409422324983136</v>
+      </c>
+      <c r="C15">
+        <v>27.18018456065139</v>
+      </c>
+      <c r="D15">
+        <v>29.79618456065139</v>
+      </c>
+      <c r="E15">
+        <v>-10.484</v>
+      </c>
+      <c r="F15">
+        <v>4.316000000000001</v>
+      </c>
+      <c r="G15">
+        <v>1.7</v>
+      </c>
+      <c r="H15">
+        <v>18.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.985</v>
+      </c>
+      <c r="K15">
+        <v>0.112</v>
+      </c>
+      <c r="L15">
+        <v>0.873</v>
+      </c>
+      <c r="M15">
+        <v>0.3944824000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.4785175999999999</v>
+      </c>
+      <c r="O15">
+        <v>0.07177763999999999</v>
+      </c>
+      <c r="P15">
+        <v>0.4067399599999999</v>
+      </c>
+      <c r="Q15">
+        <v>0.5187399599999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08505117614923144</v>
+      </c>
+      <c r="T15">
+        <v>0.6271499717787959</v>
+      </c>
+      <c r="U15">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.213026487366736</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08442156508065772</v>
+      </c>
+      <c r="C16">
+        <v>26.63439229840699</v>
+      </c>
+      <c r="D16">
+        <v>29.58239229840699</v>
+      </c>
+      <c r="E16">
+        <v>-10.152</v>
+      </c>
+      <c r="F16">
+        <v>4.648000000000001</v>
+      </c>
+      <c r="G16">
+        <v>1.7</v>
+      </c>
+      <c r="H16">
+        <v>18.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.985</v>
+      </c>
+      <c r="K16">
+        <v>0.112</v>
+      </c>
+      <c r="L16">
+        <v>0.873</v>
+      </c>
+      <c r="M16">
+        <v>0.4248272000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.4481727999999999</v>
+      </c>
+      <c r="O16">
+        <v>0.06722591999999999</v>
+      </c>
+      <c r="P16">
+        <v>0.3809468799999999</v>
+      </c>
+      <c r="Q16">
+        <v>0.4929468799999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08551740125657875</v>
+      </c>
+      <c r="T16">
+        <v>0.6334718231836556</v>
+      </c>
+      <c r="U16">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>2.054953166840541</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08743915691148409</v>
+      </c>
+      <c r="C17">
+        <v>24.46708940657383</v>
+      </c>
+      <c r="D17">
+        <v>27.74708940657383</v>
+      </c>
+      <c r="E17">
+        <v>-9.82</v>
+      </c>
+      <c r="F17">
+        <v>4.98</v>
+      </c>
+      <c r="G17">
+        <v>1.7</v>
+      </c>
+      <c r="H17">
+        <v>18.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.985</v>
+      </c>
+      <c r="K17">
+        <v>0.112</v>
+      </c>
+      <c r="L17">
+        <v>0.873</v>
+      </c>
+      <c r="M17">
+        <v>0.56025</v>
+      </c>
+      <c r="N17">
+        <v>0.31275</v>
+      </c>
+      <c r="O17">
+        <v>0.0469125</v>
+      </c>
+      <c r="P17">
+        <v>0.2658374999999999</v>
+      </c>
+      <c r="Q17">
+        <v>0.3778374999999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08599459636645186</v>
+      </c>
+      <c r="T17">
+        <v>0.6399424240333353</v>
+      </c>
+      <c r="U17">
+        <v>0.1125</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.095625</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>1.558232931726907</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1003191639971192</v>
+      </c>
+      <c r="C18">
+        <v>18.32579869223385</v>
+      </c>
+      <c r="D18">
+        <v>21.93779869223386</v>
+      </c>
+      <c r="E18">
+        <v>-9.488</v>
+      </c>
+      <c r="F18">
+        <v>5.312</v>
+      </c>
+      <c r="G18">
+        <v>1.7</v>
+      </c>
+      <c r="H18">
+        <v>18.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.985</v>
+      </c>
+      <c r="K18">
+        <v>0.112</v>
+      </c>
+      <c r="L18">
+        <v>0.873</v>
+      </c>
+      <c r="M18">
+        <v>1.0443392</v>
+      </c>
+      <c r="N18">
+        <v>-0.1713392</v>
+      </c>
+      <c r="O18">
+        <v>-0.02570088000000001</v>
+      </c>
+      <c r="P18">
+        <v>-0.14563832</v>
+      </c>
+      <c r="Q18">
+        <v>-0.03363832000000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08667552512565831</v>
+      </c>
+      <c r="T18">
+        <v>0.6491755827911108</v>
+      </c>
+      <c r="U18">
+        <v>0.1966</v>
+      </c>
+      <c r="V18">
+        <v>0.1253902946475628</v>
+      </c>
+      <c r="W18">
+        <v>0.1719482680722892</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.8359352976504185</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.104887400758152</v>
+      </c>
+      <c r="C19">
+        <v>16.47736655400004</v>
+      </c>
+      <c r="D19">
+        <v>20.42136655400004</v>
+      </c>
+      <c r="E19">
+        <v>-9.155999999999999</v>
+      </c>
+      <c r="F19">
+        <v>5.644000000000001</v>
+      </c>
+      <c r="G19">
+        <v>1.7</v>
+      </c>
+      <c r="H19">
+        <v>18.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.985</v>
+      </c>
+      <c r="K19">
+        <v>0.112</v>
+      </c>
+      <c r="L19">
+        <v>0.873</v>
+      </c>
+      <c r="M19">
+        <v>1.2066872</v>
+      </c>
+      <c r="N19">
+        <v>-0.3336872000000002</v>
+      </c>
+      <c r="O19">
+        <v>-0.05005308000000003</v>
+      </c>
+      <c r="P19">
+        <v>-0.2836341200000002</v>
+      </c>
+      <c r="Q19">
+        <v>-0.1716341200000002</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08733214200793467</v>
+      </c>
+      <c r="T19">
+        <v>0.6580790808959032</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1085202528045379</v>
+      </c>
+      <c r="W19">
+        <v>0.1905983699503898</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.7234683520302526</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.106637400758152</v>
+      </c>
+      <c r="C20">
+        <v>15.61855699068985</v>
+      </c>
+      <c r="D20">
+        <v>19.89455699068985</v>
+      </c>
+      <c r="E20">
+        <v>-8.824000000000002</v>
+      </c>
+      <c r="F20">
+        <v>5.976</v>
+      </c>
+      <c r="G20">
+        <v>1.7</v>
+      </c>
+      <c r="H20">
+        <v>18.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.985</v>
+      </c>
+      <c r="K20">
+        <v>0.112</v>
+      </c>
+      <c r="L20">
+        <v>0.873</v>
+      </c>
+      <c r="M20">
+        <v>1.2776688</v>
+      </c>
+      <c r="N20">
+        <v>-0.4046687999999998</v>
+      </c>
+      <c r="O20">
+        <v>-0.06070031999999998</v>
+      </c>
+      <c r="P20">
+        <v>-0.3439684799999999</v>
+      </c>
+      <c r="Q20">
+        <v>-0.2319684799999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08792399739827533</v>
+      </c>
+      <c r="T20">
+        <v>0.6661044355409751</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1024913498709525</v>
+      </c>
+      <c r="W20">
+        <v>0.1918873493975903</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.6832756658063499</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1083874007581521</v>
+      </c>
+      <c r="C21">
+        <v>14.78624408412351</v>
+      </c>
+      <c r="D21">
+        <v>19.39424408412351</v>
+      </c>
+      <c r="E21">
+        <v>-8.492000000000001</v>
+      </c>
+      <c r="F21">
+        <v>6.308000000000001</v>
+      </c>
+      <c r="G21">
+        <v>1.7</v>
+      </c>
+      <c r="H21">
+        <v>18.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.985</v>
+      </c>
+      <c r="K21">
+        <v>0.112</v>
+      </c>
+      <c r="L21">
+        <v>0.873</v>
+      </c>
+      <c r="M21">
+        <v>1.3486504</v>
+      </c>
+      <c r="N21">
+        <v>-0.4756504000000001</v>
+      </c>
+      <c r="O21">
+        <v>-0.07134756000000003</v>
+      </c>
+      <c r="P21">
+        <v>-0.4043028400000001</v>
+      </c>
+      <c r="Q21">
+        <v>-0.2923028400000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08853046650195776</v>
+      </c>
+      <c r="T21">
+        <v>0.6743279470908637</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.09709706829879708</v>
+      </c>
+      <c r="W21">
+        <v>0.1930406467977172</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.6473137886586471</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.110137400758152</v>
+      </c>
+      <c r="C22">
+        <v>13.97847784107972</v>
+      </c>
+      <c r="D22">
+        <v>18.91847784107972</v>
+      </c>
+      <c r="E22">
+        <v>-8.16</v>
+      </c>
+      <c r="F22">
+        <v>6.640000000000001</v>
+      </c>
+      <c r="G22">
+        <v>1.7</v>
+      </c>
+      <c r="H22">
+        <v>18.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.985</v>
+      </c>
+      <c r="K22">
+        <v>0.112</v>
+      </c>
+      <c r="L22">
+        <v>0.873</v>
+      </c>
+      <c r="M22">
+        <v>1.419632</v>
+      </c>
+      <c r="N22">
+        <v>-0.546632</v>
+      </c>
+      <c r="O22">
+        <v>-0.08199480000000001</v>
+      </c>
+      <c r="P22">
+        <v>-0.4646372</v>
+      </c>
+      <c r="Q22">
+        <v>-0.3526372</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08915209733323221</v>
+      </c>
+      <c r="T22">
+        <v>0.6827570464294995</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.09224221488385724</v>
+      </c>
+      <c r="W22">
+        <v>0.1940786144578313</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.6149480992257148</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.111887400758152</v>
+      </c>
+      <c r="C23">
+        <v>13.19349503038375</v>
+      </c>
+      <c r="D23">
+        <v>18.46549503038376</v>
+      </c>
+      <c r="E23">
+        <v>-7.828</v>
+      </c>
+      <c r="F23">
+        <v>6.972</v>
+      </c>
+      <c r="G23">
+        <v>1.7</v>
+      </c>
+      <c r="H23">
+        <v>18.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.985</v>
+      </c>
+      <c r="K23">
+        <v>0.112</v>
+      </c>
+      <c r="L23">
+        <v>0.873</v>
+      </c>
+      <c r="M23">
+        <v>1.4906136</v>
+      </c>
+      <c r="N23">
+        <v>-0.6176136000000001</v>
+      </c>
+      <c r="O23">
+        <v>-0.09264204000000002</v>
+      </c>
+      <c r="P23">
+        <v>-0.5249715600000001</v>
+      </c>
+      <c r="Q23">
+        <v>-0.4129715600000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08978946565390604</v>
+      </c>
+      <c r="T23">
+        <v>0.6913995406881007</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.08784972846081641</v>
+      </c>
+      <c r="W23">
+        <v>0.1950177280550774</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5856648564054426</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.113637400758152</v>
+      </c>
+      <c r="C24">
+        <v>12.4296973466614</v>
+      </c>
+      <c r="D24">
+        <v>18.0336973466614</v>
+      </c>
+      <c r="E24">
+        <v>-7.496</v>
+      </c>
+      <c r="F24">
+        <v>7.304</v>
+      </c>
+      <c r="G24">
+        <v>1.7</v>
+      </c>
+      <c r="H24">
+        <v>18.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.985</v>
+      </c>
+      <c r="K24">
+        <v>0.112</v>
+      </c>
+      <c r="L24">
+        <v>0.873</v>
+      </c>
+      <c r="M24">
+        <v>1.5615952</v>
+      </c>
+      <c r="N24">
+        <v>-0.6885952</v>
+      </c>
+      <c r="O24">
+        <v>-0.10328928</v>
+      </c>
+      <c r="P24">
+        <v>-0.5853059199999999</v>
+      </c>
+      <c r="Q24">
+        <v>-0.4733059199999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09044317675203305</v>
+      </c>
+      <c r="T24">
+        <v>0.7002636373635893</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.08385655898532476</v>
+      </c>
+      <c r="W24">
+        <v>0.1958714676889376</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.5590437265688317</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.115387400758152</v>
+      </c>
+      <c r="C25">
+        <v>11.68563256780418</v>
+      </c>
+      <c r="D25">
+        <v>17.62163256780418</v>
+      </c>
+      <c r="E25">
+        <v>-7.164</v>
+      </c>
+      <c r="F25">
+        <v>7.636000000000001</v>
+      </c>
+      <c r="G25">
+        <v>1.7</v>
+      </c>
+      <c r="H25">
+        <v>18.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.985</v>
+      </c>
+      <c r="K25">
+        <v>0.112</v>
+      </c>
+      <c r="L25">
+        <v>0.873</v>
+      </c>
+      <c r="M25">
+        <v>1.6325768</v>
+      </c>
+      <c r="N25">
+        <v>-0.7595768000000001</v>
+      </c>
+      <c r="O25">
+        <v>-0.11393652</v>
+      </c>
+      <c r="P25">
+        <v>-0.6456402800000001</v>
+      </c>
+      <c r="Q25">
+        <v>-0.5336402800000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09111386735920229</v>
+      </c>
+      <c r="T25">
+        <v>0.7093579703163631</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.08021062163813672</v>
+      </c>
+      <c r="W25">
+        <v>0.1966509690937664</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.5347374775875782</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.117137400758152</v>
+      </c>
+      <c r="C26">
+        <v>10.95997823800504</v>
+      </c>
+      <c r="D26">
+        <v>17.22797823800504</v>
+      </c>
+      <c r="E26">
+        <v>-6.832000000000001</v>
+      </c>
+      <c r="F26">
+        <v>7.968</v>
+      </c>
+      <c r="G26">
+        <v>1.7</v>
+      </c>
+      <c r="H26">
+        <v>18.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.985</v>
+      </c>
+      <c r="K26">
+        <v>0.112</v>
+      </c>
+      <c r="L26">
+        <v>0.873</v>
+      </c>
+      <c r="M26">
+        <v>1.7035584</v>
+      </c>
+      <c r="N26">
+        <v>-0.8305583999999999</v>
+      </c>
+      <c r="O26">
+        <v>-0.12458376</v>
+      </c>
+      <c r="P26">
+        <v>-0.7059746399999999</v>
+      </c>
+      <c r="Q26">
+        <v>-0.5939746399999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.0918022077191918</v>
+      </c>
+      <c r="T26">
+        <v>0.7186916278205258</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.07686851240321436</v>
+      </c>
+      <c r="W26">
+        <v>0.1973655120481928</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.5124567493547624</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1252166618115966</v>
+      </c>
+      <c r="C27">
+        <v>9.017301191588199</v>
+      </c>
+      <c r="D27">
+        <v>15.6173011915882</v>
+      </c>
+      <c r="E27">
+        <v>-6.5</v>
+      </c>
+      <c r="F27">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G27">
+        <v>1.7</v>
+      </c>
+      <c r="H27">
+        <v>18.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.985</v>
+      </c>
+      <c r="K27">
+        <v>0.112</v>
+      </c>
+      <c r="L27">
+        <v>0.873</v>
+      </c>
+      <c r="M27">
+        <v>1.98204</v>
+      </c>
+      <c r="N27">
+        <v>-1.10904</v>
+      </c>
+      <c r="O27">
+        <v>-0.1663560000000001</v>
+      </c>
+      <c r="P27">
+        <v>-0.9426840000000002</v>
+      </c>
+      <c r="Q27">
+        <v>-0.8306840000000002</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09261458522670717</v>
+      </c>
+      <c r="T27">
+        <v>0.7297071861982872</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06606829327359691</v>
+      </c>
+      <c r="W27">
+        <v>0.2230228915662651</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.440455288490646</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1272166618115966</v>
+      </c>
+      <c r="C28">
+        <v>8.332035169741172</v>
+      </c>
+      <c r="D28">
+        <v>15.26403516974117</v>
+      </c>
+      <c r="E28">
+        <v>-6.167999999999999</v>
+      </c>
+      <c r="F28">
+        <v>8.632000000000001</v>
+      </c>
+      <c r="G28">
+        <v>1.7</v>
+      </c>
+      <c r="H28">
+        <v>18.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.985</v>
+      </c>
+      <c r="K28">
+        <v>0.112</v>
+      </c>
+      <c r="L28">
+        <v>0.873</v>
+      </c>
+      <c r="M28">
+        <v>2.0613216</v>
+      </c>
+      <c r="N28">
+        <v>-1.1883216</v>
+      </c>
+      <c r="O28">
+        <v>-0.1782482400000001</v>
+      </c>
+      <c r="P28">
+        <v>-1.01007336</v>
+      </c>
+      <c r="Q28">
+        <v>-0.8980733600000003</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09334180935139239</v>
+      </c>
+      <c r="T28">
+        <v>0.7395680941198857</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06352720507076624</v>
+      </c>
+      <c r="W28">
+        <v>0.223629703429101</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.423514700471775</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1292166618115966</v>
+      </c>
+      <c r="C29">
+        <v>7.662397507303531</v>
+      </c>
+      <c r="D29">
+        <v>14.92639750730353</v>
+      </c>
+      <c r="E29">
+        <v>-5.835999999999999</v>
+      </c>
+      <c r="F29">
+        <v>8.964000000000002</v>
+      </c>
+      <c r="G29">
+        <v>1.7</v>
+      </c>
+      <c r="H29">
+        <v>18.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.985</v>
+      </c>
+      <c r="K29">
+        <v>0.112</v>
+      </c>
+      <c r="L29">
+        <v>0.873</v>
+      </c>
+      <c r="M29">
+        <v>2.140603200000001</v>
+      </c>
+      <c r="N29">
+        <v>-1.267603200000001</v>
+      </c>
+      <c r="O29">
+        <v>-0.1901404800000001</v>
+      </c>
+      <c r="P29">
+        <v>-1.07746272</v>
+      </c>
+      <c r="Q29">
+        <v>-0.9654627200000004</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09408895742469914</v>
+      </c>
+      <c r="T29">
+        <v>0.7496991639023499</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.06117434562370083</v>
+      </c>
+      <c r="W29">
+        <v>0.2241915662650603</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.4078289708246721</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1312166618115966</v>
+      </c>
+      <c r="C30">
+        <v>7.007373558705757</v>
+      </c>
+      <c r="D30">
+        <v>14.60337355870576</v>
+      </c>
+      <c r="E30">
+        <v>-5.504</v>
+      </c>
+      <c r="F30">
+        <v>9.296000000000001</v>
+      </c>
+      <c r="G30">
+        <v>1.7</v>
+      </c>
+      <c r="H30">
+        <v>18.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.985</v>
+      </c>
+      <c r="K30">
+        <v>0.112</v>
+      </c>
+      <c r="L30">
+        <v>0.873</v>
+      </c>
+      <c r="M30">
+        <v>2.2198848</v>
+      </c>
+      <c r="N30">
+        <v>-1.3468848</v>
+      </c>
+      <c r="O30">
+        <v>-0.2020327200000001</v>
+      </c>
+      <c r="P30">
+        <v>-1.14485208</v>
+      </c>
+      <c r="Q30">
+        <v>-1.03285208</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.0948568596111533</v>
+      </c>
+      <c r="T30">
+        <v>0.7601116522898825</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05898954756571152</v>
+      </c>
+      <c r="W30">
+        <v>0.2247132960413081</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3932636504380768</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1332166618115966</v>
+      </c>
+      <c r="C31">
+        <v>6.366034650116806</v>
+      </c>
+      <c r="D31">
+        <v>14.29403465011681</v>
+      </c>
+      <c r="E31">
+        <v>-5.172000000000001</v>
+      </c>
+      <c r="F31">
+        <v>9.628</v>
+      </c>
+      <c r="G31">
+        <v>1.7</v>
+      </c>
+      <c r="H31">
+        <v>18.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.985</v>
+      </c>
+      <c r="K31">
+        <v>0.112</v>
+      </c>
+      <c r="L31">
+        <v>0.873</v>
+      </c>
+      <c r="M31">
+        <v>2.2991664</v>
+      </c>
+      <c r="N31">
+        <v>-1.4261664</v>
+      </c>
+      <c r="O31">
+        <v>-0.2139249600000001</v>
+      </c>
+      <c r="P31">
+        <v>-1.21224144</v>
+      </c>
+      <c r="Q31">
+        <v>-1.10024144</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.0956463928451132</v>
+      </c>
+      <c r="T31">
+        <v>0.7708174502094582</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.0569554252358594</v>
+      </c>
+      <c r="W31">
+        <v>0.2251990444536768</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3797028349057293</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1352166618115966</v>
+      </c>
+      <c r="C32">
+        <v>5.737529162755123</v>
+      </c>
+      <c r="D32">
+        <v>13.99752916275513</v>
+      </c>
+      <c r="E32">
+        <v>-4.84</v>
+      </c>
+      <c r="F32">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="G32">
+        <v>1.7</v>
+      </c>
+      <c r="H32">
+        <v>18.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.985</v>
+      </c>
+      <c r="K32">
+        <v>0.112</v>
+      </c>
+      <c r="L32">
+        <v>0.873</v>
+      </c>
+      <c r="M32">
+        <v>2.378448</v>
+      </c>
+      <c r="N32">
+        <v>-1.505448</v>
+      </c>
+      <c r="O32">
+        <v>-0.2258172000000001</v>
+      </c>
+      <c r="P32">
+        <v>-1.2796308</v>
+      </c>
+      <c r="Q32">
+        <v>-1.1676308</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09645848417147196</v>
+      </c>
+      <c r="T32">
+        <v>0.7818291280695935</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05505691106133076</v>
+      </c>
+      <c r="W32">
+        <v>0.2256524096385542</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.367046073742205</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1372166618115966</v>
+      </c>
+      <c r="C33">
+        <v>5.121074703416699</v>
+      </c>
+      <c r="D33">
+        <v>13.7130747034167</v>
+      </c>
+      <c r="E33">
+        <v>-4.507999999999999</v>
+      </c>
+      <c r="F33">
+        <v>10.292</v>
+      </c>
+      <c r="G33">
+        <v>1.7</v>
+      </c>
+      <c r="H33">
+        <v>18.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.985</v>
+      </c>
+      <c r="K33">
+        <v>0.112</v>
+      </c>
+      <c r="L33">
+        <v>0.873</v>
+      </c>
+      <c r="M33">
+        <v>2.4577296</v>
+      </c>
+      <c r="N33">
+        <v>-1.5847296</v>
+      </c>
+      <c r="O33">
+        <v>-0.2377094400000001</v>
+      </c>
+      <c r="P33">
+        <v>-1.34702016</v>
+      </c>
+      <c r="Q33">
+        <v>-1.23502016</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09729411437685562</v>
+      </c>
+      <c r="T33">
+        <v>0.7931599849981383</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.05328088167225557</v>
+      </c>
+      <c r="W33">
+        <v>0.2260765254566654</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.355205877815037</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1392166618115966</v>
+      </c>
+      <c r="C34">
+        <v>4.515951210641258</v>
+      </c>
+      <c r="D34">
+        <v>13.43995121064126</v>
+      </c>
+      <c r="E34">
+        <v>-4.176</v>
+      </c>
+      <c r="F34">
+        <v>10.624</v>
+      </c>
+      <c r="G34">
+        <v>1.7</v>
+      </c>
+      <c r="H34">
+        <v>18.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.985</v>
+      </c>
+      <c r="K34">
+        <v>0.112</v>
+      </c>
+      <c r="L34">
+        <v>0.873</v>
+      </c>
+      <c r="M34">
+        <v>2.5370112</v>
+      </c>
+      <c r="N34">
+        <v>-1.6640112</v>
+      </c>
+      <c r="O34">
+        <v>-0.2496016800000001</v>
+      </c>
+      <c r="P34">
+        <v>-1.41440952</v>
+      </c>
+      <c r="Q34">
+        <v>-1.30240952</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09815432194122113</v>
+      </c>
+      <c r="T34">
+        <v>0.8048241024245815</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05161585411999758</v>
+      </c>
+      <c r="W34">
+        <v>0.2264741340361446</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3441056941333172</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1412166618115966</v>
+      </c>
+      <c r="C35">
+        <v>3.921494868618218</v>
+      </c>
+      <c r="D35">
+        <v>13.17749486861822</v>
+      </c>
+      <c r="E35">
+        <v>-3.843999999999999</v>
+      </c>
+      <c r="F35">
+        <v>10.956</v>
+      </c>
+      <c r="G35">
+        <v>1.7</v>
+      </c>
+      <c r="H35">
+        <v>18.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.985</v>
+      </c>
+      <c r="K35">
+        <v>0.112</v>
+      </c>
+      <c r="L35">
+        <v>0.873</v>
+      </c>
+      <c r="M35">
+        <v>2.616292800000001</v>
+      </c>
+      <c r="N35">
+        <v>-1.743292800000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.2614939200000001</v>
+      </c>
+      <c r="P35">
+        <v>-1.48179888</v>
+      </c>
+      <c r="Q35">
+        <v>-1.36979888</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09904020734332891</v>
+      </c>
+      <c r="T35">
+        <v>0.8168364024607693</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.0500517373284825</v>
+      </c>
+      <c r="W35">
+        <v>0.2268476451259584</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.33367824885655</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1432166618115966</v>
+      </c>
+      <c r="C36">
+        <v>3.337092720532025</v>
+      </c>
+      <c r="D36">
+        <v>12.92509272053203</v>
+      </c>
+      <c r="E36">
+        <v>-3.511999999999999</v>
+      </c>
+      <c r="F36">
+        <v>11.288</v>
+      </c>
+      <c r="G36">
+        <v>1.7</v>
+      </c>
+      <c r="H36">
+        <v>18.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.985</v>
+      </c>
+      <c r="K36">
+        <v>0.112</v>
+      </c>
+      <c r="L36">
+        <v>0.873</v>
+      </c>
+      <c r="M36">
+        <v>2.695574400000001</v>
+      </c>
+      <c r="N36">
+        <v>-1.822574400000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.2733861600000002</v>
+      </c>
+      <c r="P36">
+        <v>-1.549188240000001</v>
+      </c>
+      <c r="Q36">
+        <v>-1.437188240000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09995293775762176</v>
+      </c>
+      <c r="T36">
+        <v>0.8292127115889627</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04857962740705653</v>
+      </c>
+      <c r="W36">
+        <v>0.2271991849751949</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3238641827137102</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1452166618115966</v>
+      </c>
+      <c r="C37">
+        <v>2.762177889329839</v>
+      </c>
+      <c r="D37">
+        <v>12.68217788932984</v>
+      </c>
+      <c r="E37">
+        <v>-3.179999999999998</v>
+      </c>
+      <c r="F37">
+        <v>11.62</v>
+      </c>
+      <c r="G37">
+        <v>1.7</v>
+      </c>
+      <c r="H37">
+        <v>18.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.985</v>
+      </c>
+      <c r="K37">
+        <v>0.112</v>
+      </c>
+      <c r="L37">
+        <v>0.873</v>
+      </c>
+      <c r="M37">
+        <v>2.774856000000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.901856000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.2852784000000002</v>
+      </c>
+      <c r="P37">
+        <v>-1.616577600000001</v>
+      </c>
+      <c r="Q37">
+        <v>-1.5045776</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1008937521846621</v>
+      </c>
+      <c r="T37">
+        <v>0.8419698302287929</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.04719163805256921</v>
+      </c>
+      <c r="W37">
+        <v>0.2275306368330465</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3146109203504613</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1472166618115966</v>
+      </c>
+      <c r="C38">
+        <v>2.196225327474199</v>
+      </c>
+      <c r="D38">
+        <v>12.4482253274742</v>
+      </c>
+      <c r="E38">
+        <v>-2.848000000000001</v>
+      </c>
+      <c r="F38">
+        <v>11.952</v>
+      </c>
+      <c r="G38">
+        <v>1.7</v>
+      </c>
+      <c r="H38">
+        <v>18.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.985</v>
+      </c>
+      <c r="K38">
+        <v>0.112</v>
+      </c>
+      <c r="L38">
+        <v>0.873</v>
+      </c>
+      <c r="M38">
+        <v>2.8541376</v>
+      </c>
+      <c r="N38">
+        <v>-1.9811376</v>
+      </c>
+      <c r="O38">
+        <v>-0.29717064</v>
+      </c>
+      <c r="P38">
+        <v>-1.68396696</v>
+      </c>
+      <c r="Q38">
+        <v>-1.57196696</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1018639670625475</v>
+      </c>
+      <c r="T38">
+        <v>0.8551256088261178</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04588075921777563</v>
+      </c>
+      <c r="W38">
+        <v>0.2278436746987952</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3058717281185042</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1492166618115967</v>
+      </c>
+      <c r="C39">
+        <v>1.638748028609387</v>
+      </c>
+      <c r="D39">
+        <v>12.22274802860939</v>
+      </c>
+      <c r="E39">
+        <v>-2.516</v>
+      </c>
+      <c r="F39">
+        <v>12.284</v>
+      </c>
+      <c r="G39">
+        <v>1.7</v>
+      </c>
+      <c r="H39">
+        <v>18.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.985</v>
+      </c>
+      <c r="K39">
+        <v>0.112</v>
+      </c>
+      <c r="L39">
+        <v>0.873</v>
+      </c>
+      <c r="M39">
+        <v>2.9334192</v>
+      </c>
+      <c r="N39">
+        <v>-2.0604192</v>
+      </c>
+      <c r="O39">
+        <v>-0.30906288</v>
+      </c>
+      <c r="P39">
+        <v>-1.75135632</v>
+      </c>
+      <c r="Q39">
+        <v>-1.63935632</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1028649824127466</v>
+      </c>
+      <c r="T39">
+        <v>0.8686990311884372</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04464073869837629</v>
+      </c>
+      <c r="W39">
+        <v>0.2281397915988278</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.297604924655842</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1512166618115967</v>
+      </c>
+      <c r="C40">
+        <v>1.08929364361628</v>
+      </c>
+      <c r="D40">
+        <v>12.00529364361628</v>
+      </c>
+      <c r="E40">
+        <v>-2.183999999999999</v>
+      </c>
+      <c r="F40">
+        <v>12.616</v>
+      </c>
+      <c r="G40">
+        <v>1.7</v>
+      </c>
+      <c r="H40">
+        <v>18.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.985</v>
+      </c>
+      <c r="K40">
+        <v>0.112</v>
+      </c>
+      <c r="L40">
+        <v>0.873</v>
+      </c>
+      <c r="M40">
+        <v>3.012700800000001</v>
+      </c>
+      <c r="N40">
+        <v>-2.139700800000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.3209551200000001</v>
+      </c>
+      <c r="P40">
+        <v>-1.818745680000001</v>
+      </c>
+      <c r="Q40">
+        <v>-1.70674568</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1038982885806942</v>
+      </c>
+      <c r="T40">
+        <v>0.8827103058850249</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04346598241684006</v>
+      </c>
+      <c r="W40">
+        <v>0.2284203233988586</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2897732161122669</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1532166618115967</v>
+      </c>
+      <c r="C41">
+        <v>0.5474414515747945</v>
+      </c>
+      <c r="D41">
+        <v>11.7954414515748</v>
+      </c>
+      <c r="E41">
+        <v>-1.851999999999999</v>
+      </c>
+      <c r="F41">
+        <v>12.948</v>
+      </c>
+      <c r="G41">
+        <v>1.7</v>
+      </c>
+      <c r="H41">
+        <v>18.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.985</v>
+      </c>
+      <c r="K41">
+        <v>0.112</v>
+      </c>
+      <c r="L41">
+        <v>0.873</v>
+      </c>
+      <c r="M41">
+        <v>3.0919824</v>
+      </c>
+      <c r="N41">
+        <v>-2.218982400000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.3328473600000001</v>
+      </c>
+      <c r="P41">
+        <v>-1.886135040000001</v>
+      </c>
+      <c r="Q41">
+        <v>-1.77413504</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1049654736393941</v>
+      </c>
+      <c r="T41">
+        <v>0.8971809666372383</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.0423514700471775</v>
+      </c>
+      <c r="W41">
+        <v>0.228686468952734</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2823431336478499</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1552166618115967</v>
+      </c>
+      <c r="C42">
+        <v>0.01279964295355107</v>
+      </c>
+      <c r="D42">
+        <v>11.59279964295355</v>
+      </c>
+      <c r="E42">
+        <v>-1.52</v>
+      </c>
+      <c r="F42">
+        <v>13.28</v>
+      </c>
+      <c r="G42">
+        <v>1.7</v>
+      </c>
+      <c r="H42">
+        <v>18.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.985</v>
+      </c>
+      <c r="K42">
+        <v>0.112</v>
+      </c>
+      <c r="L42">
+        <v>0.873</v>
+      </c>
+      <c r="M42">
+        <v>3.171264</v>
+      </c>
+      <c r="N42">
+        <v>-2.298264000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.3447396000000001</v>
+      </c>
+      <c r="P42">
+        <v>-1.9535244</v>
+      </c>
+      <c r="Q42">
+        <v>-1.8415244</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.106068231533384</v>
+      </c>
+      <c r="T42">
+        <v>0.9121339827478591</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04129268329599807</v>
+      </c>
+      <c r="W42">
+        <v>0.2289393072289157</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2752845553066536</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1572166618115967</v>
+      </c>
+      <c r="C43">
+        <v>-0.5149971218868199</v>
+      </c>
+      <c r="D43">
+        <v>11.39700287811318</v>
+      </c>
+      <c r="E43">
+        <v>-1.187999999999999</v>
+      </c>
+      <c r="F43">
+        <v>13.612</v>
+      </c>
+      <c r="G43">
+        <v>1.7</v>
+      </c>
+      <c r="H43">
+        <v>18.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.985</v>
+      </c>
+      <c r="K43">
+        <v>0.112</v>
+      </c>
+      <c r="L43">
+        <v>0.873</v>
+      </c>
+      <c r="M43">
+        <v>3.250545600000001</v>
+      </c>
+      <c r="N43">
+        <v>-2.3775456</v>
+      </c>
+      <c r="O43">
+        <v>-0.3566318400000001</v>
+      </c>
+      <c r="P43">
+        <v>-2.02091376</v>
+      </c>
+      <c r="Q43">
+        <v>-1.90891376</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1072083710508989</v>
+      </c>
+      <c r="T43">
+        <v>0.9275938807605346</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.0402855446790225</v>
+      </c>
+      <c r="W43">
+        <v>0.2291798119306495</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.26857029786015</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1592166618115967</v>
+      </c>
+      <c r="C44">
+        <v>-1.036289910885488</v>
+      </c>
+      <c r="D44">
+        <v>11.20771008911451</v>
+      </c>
+      <c r="E44">
+        <v>-0.8559999999999999</v>
+      </c>
+      <c r="F44">
+        <v>13.944</v>
+      </c>
+      <c r="G44">
+        <v>1.7</v>
+      </c>
+      <c r="H44">
+        <v>18.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.985</v>
+      </c>
+      <c r="K44">
+        <v>0.112</v>
+      </c>
+      <c r="L44">
+        <v>0.873</v>
+      </c>
+      <c r="M44">
+        <v>3.3298272</v>
+      </c>
+      <c r="N44">
+        <v>-2.4568272</v>
+      </c>
+      <c r="O44">
+        <v>-0.3685240800000001</v>
+      </c>
+      <c r="P44">
+        <v>-2.08830312</v>
+      </c>
+      <c r="Q44">
+        <v>-1.97630312</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1083878257241903</v>
+      </c>
+      <c r="T44">
+        <v>0.9435868787046817</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03932636504380767</v>
+      </c>
+      <c r="W44">
+        <v>0.2294088640275387</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2621757669587179</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1612166618115966</v>
+      </c>
+      <c r="C45">
+        <v>-1.551397502993552</v>
+      </c>
+      <c r="D45">
+        <v>11.02460249700645</v>
+      </c>
+      <c r="E45">
+        <v>-0.5239999999999991</v>
+      </c>
+      <c r="F45">
+        <v>14.276</v>
+      </c>
+      <c r="G45">
+        <v>1.7</v>
+      </c>
+      <c r="H45">
+        <v>18.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.985</v>
+      </c>
+      <c r="K45">
+        <v>0.112</v>
+      </c>
+      <c r="L45">
+        <v>0.873</v>
+      </c>
+      <c r="M45">
+        <v>3.409108800000001</v>
+      </c>
+      <c r="N45">
+        <v>-2.536108800000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.3804163200000002</v>
+      </c>
+      <c r="P45">
+        <v>-2.155692480000001</v>
+      </c>
+      <c r="Q45">
+        <v>-2.043692480000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1096086647719831</v>
+      </c>
+      <c r="T45">
+        <v>0.9601410344714304</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03841179841488192</v>
+      </c>
+      <c r="W45">
+        <v>0.2296272625385262</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2560786560992127</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1632166618115966</v>
+      </c>
+      <c r="C46">
+        <v>-2.060618179653417</v>
+      </c>
+      <c r="D46">
+        <v>10.84738182034658</v>
+      </c>
+      <c r="E46">
+        <v>-0.1920000000000002</v>
+      </c>
+      <c r="F46">
+        <v>14.608</v>
+      </c>
+      <c r="G46">
+        <v>1.7</v>
+      </c>
+      <c r="H46">
+        <v>18.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.985</v>
+      </c>
+      <c r="K46">
+        <v>0.112</v>
+      </c>
+      <c r="L46">
+        <v>0.873</v>
+      </c>
+      <c r="M46">
+        <v>3.4883904</v>
+      </c>
+      <c r="N46">
+        <v>-2.6153904</v>
+      </c>
+      <c r="O46">
+        <v>-0.39230856</v>
+      </c>
+      <c r="P46">
+        <v>-2.22308184</v>
+      </c>
+      <c r="Q46">
+        <v>-2.11108184</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1108731052143399</v>
+      </c>
+      <c r="T46">
+        <v>0.9772864100869917</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03753880299636188</v>
+      </c>
+      <c r="W46">
+        <v>0.2298357338444688</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2502586866424126</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1652166618115966</v>
+      </c>
+      <c r="C47">
+        <v>-2.564231346223387</v>
+      </c>
+      <c r="D47">
+        <v>10.67576865377661</v>
+      </c>
+      <c r="E47">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="F47">
+        <v>14.94</v>
+      </c>
+      <c r="G47">
+        <v>1.7</v>
+      </c>
+      <c r="H47">
+        <v>18.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.985</v>
+      </c>
+      <c r="K47">
+        <v>0.112</v>
+      </c>
+      <c r="L47">
+        <v>0.873</v>
+      </c>
+      <c r="M47">
+        <v>3.567672</v>
+      </c>
+      <c r="N47">
+        <v>-2.694672000000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.4042008000000001</v>
+      </c>
+      <c r="P47">
+        <v>-2.290471200000001</v>
+      </c>
+      <c r="Q47">
+        <v>-2.178471200000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1121835253091461</v>
+      </c>
+      <c r="T47">
+        <v>0.9950552539067552</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.0367046073742205</v>
+      </c>
+      <c r="W47">
+        <v>0.2300349397590361</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2446973824948032</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1672166618115966</v>
+      </c>
+      <c r="C48">
+        <v>-3.062499001886941</v>
+      </c>
+      <c r="D48">
+        <v>10.50950099811306</v>
+      </c>
+      <c r="E48">
+        <v>0.4720000000000013</v>
+      </c>
+      <c r="F48">
+        <v>15.272</v>
+      </c>
+      <c r="G48">
+        <v>1.7</v>
+      </c>
+      <c r="H48">
+        <v>18.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.985</v>
+      </c>
+      <c r="K48">
+        <v>0.112</v>
+      </c>
+      <c r="L48">
+        <v>0.873</v>
+      </c>
+      <c r="M48">
+        <v>3.646953600000001</v>
+      </c>
+      <c r="N48">
+        <v>-2.7739536</v>
+      </c>
+      <c r="O48">
+        <v>-0.4160930400000001</v>
+      </c>
+      <c r="P48">
+        <v>-2.35786056</v>
+      </c>
+      <c r="Q48">
+        <v>-2.24586056</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1135424794815377</v>
+      </c>
+      <c r="T48">
+        <v>1.013482203053176</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03590668112695483</v>
+      </c>
+      <c r="W48">
+        <v>0.2302254845468832</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2393778741796989</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1692166618115966</v>
+      </c>
+      <c r="C49">
+        <v>-3.555667074311541</v>
+      </c>
+      <c r="D49">
+        <v>10.34833292568846</v>
+      </c>
+      <c r="E49">
+        <v>0.804000000000002</v>
+      </c>
+      <c r="F49">
+        <v>15.604</v>
+      </c>
+      <c r="G49">
+        <v>1.7</v>
+      </c>
+      <c r="H49">
+        <v>18.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.985</v>
+      </c>
+      <c r="K49">
+        <v>0.112</v>
+      </c>
+      <c r="L49">
+        <v>0.873</v>
+      </c>
+      <c r="M49">
+        <v>3.726235200000001</v>
+      </c>
+      <c r="N49">
+        <v>-2.853235200000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.4279852800000002</v>
+      </c>
+      <c r="P49">
+        <v>-2.425249920000001</v>
+      </c>
+      <c r="Q49">
+        <v>-2.313249920000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1149527149434535</v>
+      </c>
+      <c r="T49">
+        <v>1.032604508771161</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03514270918808345</v>
+      </c>
+      <c r="W49">
+        <v>0.2304079210458857</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2342847279205562</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1712166618115966</v>
+      </c>
+      <c r="C50">
+        <v>-4.043966633356639</v>
+      </c>
+      <c r="D50">
+        <v>10.19203336664336</v>
+      </c>
+      <c r="E50">
+        <v>1.135999999999999</v>
+      </c>
+      <c r="F50">
+        <v>15.936</v>
+      </c>
+      <c r="G50">
+        <v>1.7</v>
+      </c>
+      <c r="H50">
+        <v>18.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.985</v>
+      </c>
+      <c r="K50">
+        <v>0.112</v>
+      </c>
+      <c r="L50">
+        <v>0.873</v>
+      </c>
+      <c r="M50">
+        <v>3.8055168</v>
+      </c>
+      <c r="N50">
+        <v>-2.9325168</v>
+      </c>
+      <c r="O50">
+        <v>-0.4398775200000001</v>
+      </c>
+      <c r="P50">
+        <v>-2.49263928</v>
+      </c>
+      <c r="Q50">
+        <v>-2.38063928</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1164171902308276</v>
+      </c>
+      <c r="T50">
+        <v>1.052462287785991</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03441056941333172</v>
+      </c>
+      <c r="W50">
+        <v>0.2305827560240964</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2294037960888782</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1732166618115966</v>
+      </c>
+      <c r="C51">
+        <v>-4.52761499642831</v>
+      </c>
+      <c r="D51">
+        <v>10.04038500357169</v>
+      </c>
+      <c r="E51">
+        <v>1.468</v>
+      </c>
+      <c r="F51">
+        <v>16.268</v>
+      </c>
+      <c r="G51">
+        <v>1.7</v>
+      </c>
+      <c r="H51">
+        <v>18.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.985</v>
+      </c>
+      <c r="K51">
+        <v>0.112</v>
+      </c>
+      <c r="L51">
+        <v>0.873</v>
+      </c>
+      <c r="M51">
+        <v>3.8847984</v>
+      </c>
+      <c r="N51">
+        <v>-3.0117984</v>
+      </c>
+      <c r="O51">
+        <v>-0.4517697600000001</v>
+      </c>
+      <c r="P51">
+        <v>-2.56002864</v>
+      </c>
+      <c r="Q51">
+        <v>-2.44802864</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1179390959216282</v>
+      </c>
+      <c r="T51">
+        <v>1.073098803232775</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.0337083128946923</v>
+      </c>
+      <c r="W51">
+        <v>0.2307504548807475</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2247220859646154</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1752166618115966</v>
+      </c>
+      <c r="C52">
+        <v>-5.006816736600467</v>
+      </c>
+      <c r="D52">
+        <v>9.893183263399536</v>
+      </c>
+      <c r="E52">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="F52">
+        <v>16.6</v>
+      </c>
+      <c r="G52">
+        <v>1.7</v>
+      </c>
+      <c r="H52">
+        <v>18.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.985</v>
+      </c>
+      <c r="K52">
+        <v>0.112</v>
+      </c>
+      <c r="L52">
+        <v>0.873</v>
+      </c>
+      <c r="M52">
+        <v>3.96408</v>
+      </c>
+      <c r="N52">
+        <v>-3.091080000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.4636620000000002</v>
+      </c>
+      <c r="P52">
+        <v>-2.627418</v>
+      </c>
+      <c r="Q52">
+        <v>-2.515418</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1195218778400607</v>
+      </c>
+      <c r="T52">
+        <v>1.094560779297431</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03303414663679845</v>
+      </c>
+      <c r="W52">
+        <v>0.2309114457831325</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2202276442453229</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1772166618115966</v>
+      </c>
+      <c r="C53">
+        <v>-5.481764603337281</v>
+      </c>
+      <c r="D53">
+        <v>9.750235396662722</v>
+      </c>
+      <c r="E53">
+        <v>2.132000000000001</v>
+      </c>
+      <c r="F53">
+        <v>16.932</v>
+      </c>
+      <c r="G53">
+        <v>1.7</v>
+      </c>
+      <c r="H53">
+        <v>18.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.985</v>
+      </c>
+      <c r="K53">
+        <v>0.112</v>
+      </c>
+      <c r="L53">
+        <v>0.873</v>
+      </c>
+      <c r="M53">
+        <v>4.043361600000001</v>
+      </c>
+      <c r="N53">
+        <v>-3.170361600000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.4755542400000001</v>
+      </c>
+      <c r="P53">
+        <v>-2.69480736</v>
+      </c>
+      <c r="Q53">
+        <v>-2.58280736</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1211692631021028</v>
+      </c>
+      <c r="T53">
+        <v>1.116898754385133</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03238641827137102</v>
+      </c>
+      <c r="W53">
+        <v>0.2310661233167966</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2159094551424735</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1792166618115967</v>
+      </c>
+      <c r="C54">
+        <v>-5.952640364530712</v>
+      </c>
+      <c r="D54">
+        <v>9.611359635469292</v>
+      </c>
+      <c r="E54">
+        <v>2.464000000000002</v>
+      </c>
+      <c r="F54">
+        <v>17.264</v>
+      </c>
+      <c r="G54">
+        <v>1.7</v>
+      </c>
+      <c r="H54">
+        <v>18.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.985</v>
+      </c>
+      <c r="K54">
+        <v>0.112</v>
+      </c>
+      <c r="L54">
+        <v>0.873</v>
+      </c>
+      <c r="M54">
+        <v>4.122643200000001</v>
+      </c>
+      <c r="N54">
+        <v>-3.2496432</v>
+      </c>
+      <c r="O54">
+        <v>-0.4874464800000001</v>
+      </c>
+      <c r="P54">
+        <v>-2.76219672</v>
+      </c>
+      <c r="Q54">
+        <v>-2.65019672</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.12288528941673</v>
+      </c>
+      <c r="T54">
+        <v>1.140167478434824</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03176360253538312</v>
+      </c>
+      <c r="W54">
+        <v>0.2312148517145505</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2117573502358875</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1812166618115967</v>
+      </c>
+      <c r="C55">
+        <v>-6.419615577588079</v>
+      </c>
+      <c r="D55">
+        <v>9.476384422411925</v>
+      </c>
+      <c r="E55">
+        <v>2.796000000000003</v>
+      </c>
+      <c r="F55">
+        <v>17.596</v>
+      </c>
+      <c r="G55">
+        <v>1.7</v>
+      </c>
+      <c r="H55">
+        <v>18.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.985</v>
+      </c>
+      <c r="K55">
+        <v>0.112</v>
+      </c>
+      <c r="L55">
+        <v>0.873</v>
+      </c>
+      <c r="M55">
+        <v>4.201924800000001</v>
+      </c>
+      <c r="N55">
+        <v>-3.328924800000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.4993387200000002</v>
+      </c>
+      <c r="P55">
+        <v>-2.829586080000001</v>
+      </c>
+      <c r="Q55">
+        <v>-2.717586080000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1246743381277242</v>
+      </c>
+      <c r="T55">
+        <v>1.164426360954714</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03116428927999853</v>
+      </c>
+      <c r="W55">
+        <v>0.2313579677199364</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2077619285333235</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1832166618115967</v>
+      </c>
+      <c r="C56">
+        <v>-6.882852296447769</v>
+      </c>
+      <c r="D56">
+        <v>9.345147703552236</v>
+      </c>
+      <c r="E56">
+        <v>3.128000000000004</v>
+      </c>
+      <c r="F56">
+        <v>17.928</v>
+      </c>
+      <c r="G56">
+        <v>1.7</v>
+      </c>
+      <c r="H56">
+        <v>18.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.985</v>
+      </c>
+      <c r="K56">
+        <v>0.112</v>
+      </c>
+      <c r="L56">
+        <v>0.873</v>
+      </c>
+      <c r="M56">
+        <v>4.281206400000001</v>
+      </c>
+      <c r="N56">
+        <v>-3.408206400000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.5112309600000002</v>
+      </c>
+      <c r="P56">
+        <v>-2.896975440000001</v>
+      </c>
+      <c r="Q56">
+        <v>-2.784975440000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1265411715652834</v>
+      </c>
+      <c r="T56">
+        <v>1.189739977497208</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03058717281185041</v>
+      </c>
+      <c r="W56">
+        <v>0.2314957831325301</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2039144854123361</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1852166618115966</v>
+      </c>
+      <c r="C57">
+        <v>-7.342503720649432</v>
+      </c>
+      <c r="D57">
+        <v>9.21749627935057</v>
+      </c>
+      <c r="E57">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="F57">
+        <v>18.26</v>
+      </c>
+      <c r="G57">
+        <v>1.7</v>
+      </c>
+      <c r="H57">
+        <v>18.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.985</v>
+      </c>
+      <c r="K57">
+        <v>0.112</v>
+      </c>
+      <c r="L57">
+        <v>0.873</v>
+      </c>
+      <c r="M57">
+        <v>4.360488000000001</v>
+      </c>
+      <c r="N57">
+        <v>-3.487488000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.5231232000000002</v>
+      </c>
+      <c r="P57">
+        <v>-2.964364800000001</v>
+      </c>
+      <c r="Q57">
+        <v>-2.852364800000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1284909753778453</v>
+      </c>
+      <c r="T57">
+        <v>1.216178643663812</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.0300310423970895</v>
+      </c>
+      <c r="W57">
+        <v>0.231628587075575</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.20020694931393</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1872166618115967</v>
+      </c>
+      <c r="C58">
+        <v>-7.798714791924594</v>
+      </c>
+      <c r="D58">
+        <v>9.093285208075409</v>
+      </c>
+      <c r="E58">
+        <v>3.792000000000002</v>
+      </c>
+      <c r="F58">
+        <v>18.592</v>
+      </c>
+      <c r="G58">
+        <v>1.7</v>
+      </c>
+      <c r="H58">
+        <v>18.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.985</v>
+      </c>
+      <c r="K58">
+        <v>0.112</v>
+      </c>
+      <c r="L58">
+        <v>0.873</v>
+      </c>
+      <c r="M58">
+        <v>4.439769600000001</v>
+      </c>
+      <c r="N58">
+        <v>-3.566769600000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.5350154400000002</v>
+      </c>
+      <c r="P58">
+        <v>-3.03175416</v>
+      </c>
+      <c r="Q58">
+        <v>-2.91975416</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1305294066364327</v>
+      </c>
+      <c r="T58">
+        <v>1.243819067383444</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02949477378285576</v>
+      </c>
+      <c r="W58">
+        <v>0.231756648020654</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1966318252190384</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1892166618115967</v>
+      </c>
+      <c r="C59">
+        <v>-8.251622743192188</v>
+      </c>
+      <c r="D59">
+        <v>8.972377256807816</v>
+      </c>
+      <c r="E59">
+        <v>4.124000000000002</v>
+      </c>
+      <c r="F59">
+        <v>18.924</v>
+      </c>
+      <c r="G59">
+        <v>1.7</v>
+      </c>
+      <c r="H59">
+        <v>18.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.985</v>
+      </c>
+      <c r="K59">
+        <v>0.112</v>
+      </c>
+      <c r="L59">
+        <v>0.873</v>
+      </c>
+      <c r="M59">
+        <v>4.519051200000001</v>
+      </c>
+      <c r="N59">
+        <v>-3.6460512</v>
+      </c>
+      <c r="O59">
+        <v>-0.5469076800000001</v>
+      </c>
+      <c r="P59">
+        <v>-3.09914352</v>
+      </c>
+      <c r="Q59">
+        <v>-2.98714352</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1326626486512335</v>
+      </c>
+      <c r="T59">
+        <v>1.272745092206315</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02897732161122671</v>
+      </c>
+      <c r="W59">
+        <v>0.2318802155992391</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1931821440748448</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1912166618115966</v>
+      </c>
+      <c r="C60">
+        <v>-8.701357604330905</v>
+      </c>
+      <c r="D60">
+        <v>8.854642395669096</v>
+      </c>
+      <c r="E60">
+        <v>4.456</v>
+      </c>
+      <c r="F60">
+        <v>19.256</v>
+      </c>
+      <c r="G60">
+        <v>1.7</v>
+      </c>
+      <c r="H60">
+        <v>18.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.985</v>
+      </c>
+      <c r="K60">
+        <v>0.112</v>
+      </c>
+      <c r="L60">
+        <v>0.873</v>
+      </c>
+      <c r="M60">
+        <v>4.598332800000001</v>
+      </c>
+      <c r="N60">
+        <v>-3.7253328</v>
+      </c>
+      <c r="O60">
+        <v>-0.5587999200000001</v>
+      </c>
+      <c r="P60">
+        <v>-3.16653288</v>
+      </c>
+      <c r="Q60">
+        <v>-3.05453288</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1348974736191199</v>
+      </c>
+      <c r="T60">
+        <v>1.303048546782656</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.0284777126179297</v>
+      </c>
+      <c r="W60">
+        <v>0.2319995222268384</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1898514174528647</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1932166618115966</v>
+      </c>
+      <c r="C61">
+        <v>-9.148042668646992</v>
+      </c>
+      <c r="D61">
+        <v>8.739957331353009</v>
+      </c>
+      <c r="E61">
+        <v>4.788</v>
+      </c>
+      <c r="F61">
+        <v>19.588</v>
+      </c>
+      <c r="G61">
+        <v>1.7</v>
+      </c>
+      <c r="H61">
+        <v>18.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.985</v>
+      </c>
+      <c r="K61">
+        <v>0.112</v>
+      </c>
+      <c r="L61">
+        <v>0.873</v>
+      </c>
+      <c r="M61">
+        <v>4.6776144</v>
+      </c>
+      <c r="N61">
+        <v>-3.8046144</v>
+      </c>
+      <c r="O61">
+        <v>-0.5706921600000001</v>
+      </c>
+      <c r="P61">
+        <v>-3.23392224</v>
+      </c>
+      <c r="Q61">
+        <v>-3.12192224</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1372413144390985</v>
+      </c>
+      <c r="T61">
+        <v>1.334830218655403</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02799503952271055</v>
+      </c>
+      <c r="W61">
+        <v>0.2321147845619767</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1866335968180703</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1952166618115966</v>
+      </c>
+      <c r="C62">
+        <v>-9.591794923555492</v>
+      </c>
+      <c r="D62">
+        <v>8.628205076444511</v>
+      </c>
+      <c r="E62">
+        <v>5.120000000000001</v>
+      </c>
+      <c r="F62">
+        <v>19.92</v>
+      </c>
+      <c r="G62">
+        <v>1.7</v>
+      </c>
+      <c r="H62">
+        <v>18.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.985</v>
+      </c>
+      <c r="K62">
+        <v>0.112</v>
+      </c>
+      <c r="L62">
+        <v>0.873</v>
+      </c>
+      <c r="M62">
+        <v>4.756896</v>
+      </c>
+      <c r="N62">
+        <v>-3.883896</v>
+      </c>
+      <c r="O62">
+        <v>-0.5825844000000001</v>
+      </c>
+      <c r="P62">
+        <v>-3.3013116</v>
+      </c>
+      <c r="Q62">
+        <v>-3.1893116</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1397023473000759</v>
+      </c>
+      <c r="T62">
+        <v>1.368200974121788</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02752845553066538</v>
+      </c>
+      <c r="W62">
+        <v>0.2322262048192771</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1835230368711025</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1972166618115966</v>
+      </c>
+      <c r="C63">
+        <v>-10.03272544863758</v>
+      </c>
+      <c r="D63">
+        <v>8.519274551362422</v>
+      </c>
+      <c r="E63">
+        <v>5.452000000000002</v>
+      </c>
+      <c r="F63">
+        <v>20.252</v>
+      </c>
+      <c r="G63">
+        <v>1.7</v>
+      </c>
+      <c r="H63">
+        <v>18.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.985</v>
+      </c>
+      <c r="K63">
+        <v>0.112</v>
+      </c>
+      <c r="L63">
+        <v>0.873</v>
+      </c>
+      <c r="M63">
+        <v>4.836177600000001</v>
+      </c>
+      <c r="N63">
+        <v>-3.963177600000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.5944766400000002</v>
+      </c>
+      <c r="P63">
+        <v>-3.36870096</v>
+      </c>
+      <c r="Q63">
+        <v>-3.25670096</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1422895869744369</v>
+      </c>
+      <c r="T63">
+        <v>1.403283050381322</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02707716937442495</v>
+      </c>
+      <c r="W63">
+        <v>0.2323339719533873</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1805144624961664</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1992166618115966</v>
+      </c>
+      <c r="C64">
+        <v>-10.47093978392113</v>
+      </c>
+      <c r="D64">
+        <v>8.413060216078872</v>
+      </c>
+      <c r="E64">
+        <v>5.784000000000002</v>
+      </c>
+      <c r="F64">
+        <v>20.584</v>
+      </c>
+      <c r="G64">
+        <v>1.7</v>
+      </c>
+      <c r="H64">
+        <v>18.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.985</v>
+      </c>
+      <c r="K64">
+        <v>0.112</v>
+      </c>
+      <c r="L64">
+        <v>0.873</v>
+      </c>
+      <c r="M64">
+        <v>4.915459200000001</v>
+      </c>
+      <c r="N64">
+        <v>-4.042459200000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.6063688800000002</v>
+      </c>
+      <c r="P64">
+        <v>-3.43609032</v>
+      </c>
+      <c r="Q64">
+        <v>-3.32409032</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1450129971579747</v>
+      </c>
+      <c r="T64">
+        <v>1.440211551707146</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02664044083612778</v>
+      </c>
+      <c r="W64">
+        <v>0.2324382627283327</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1776029389075185</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2012166618115966</v>
+      </c>
+      <c r="C65">
+        <v>-10.90653827095121</v>
+      </c>
+      <c r="D65">
+        <v>8.309461729048792</v>
+      </c>
+      <c r="E65">
+        <v>6.116</v>
+      </c>
+      <c r="F65">
+        <v>20.916</v>
+      </c>
+      <c r="G65">
+        <v>1.7</v>
+      </c>
+      <c r="H65">
+        <v>18.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.985</v>
+      </c>
+      <c r="K65">
+        <v>0.112</v>
+      </c>
+      <c r="L65">
+        <v>0.873</v>
+      </c>
+      <c r="M65">
+        <v>4.994740800000001</v>
+      </c>
+      <c r="N65">
+        <v>-4.1217408</v>
+      </c>
+      <c r="O65">
+        <v>-0.6182611200000001</v>
+      </c>
+      <c r="P65">
+        <v>-3.50347968</v>
+      </c>
+      <c r="Q65">
+        <v>-3.39147968</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1478836187027848</v>
+      </c>
+      <c r="T65">
+        <v>1.479136188239771</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02621757669587178</v>
+      </c>
+      <c r="W65">
+        <v>0.2325392426850258</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1747838446391453</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2032166618115966</v>
+      </c>
+      <c r="C66">
+        <v>-11.33961636896746</v>
+      </c>
+      <c r="D66">
+        <v>8.208383631032538</v>
+      </c>
+      <c r="E66">
+        <v>6.448</v>
+      </c>
+      <c r="F66">
+        <v>21.248</v>
+      </c>
+      <c r="G66">
+        <v>1.7</v>
+      </c>
+      <c r="H66">
+        <v>18.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.985</v>
+      </c>
+      <c r="K66">
+        <v>0.112</v>
+      </c>
+      <c r="L66">
+        <v>0.873</v>
+      </c>
+      <c r="M66">
+        <v>5.0740224</v>
+      </c>
+      <c r="N66">
+        <v>-4.2010224</v>
+      </c>
+      <c r="O66">
+        <v>-0.6301533600000001</v>
+      </c>
+      <c r="P66">
+        <v>-3.57086904</v>
+      </c>
+      <c r="Q66">
+        <v>-3.45886904</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1509137192223066</v>
+      </c>
+      <c r="T66">
+        <v>1.520223304579765</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02580792705999879</v>
+      </c>
+      <c r="W66">
+        <v>0.2326370670180723</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1720528470666586</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2052166618115966</v>
+      </c>
+      <c r="C67">
+        <v>-11.7702649482825</v>
+      </c>
+      <c r="D67">
+        <v>8.109735051717502</v>
+      </c>
+      <c r="E67">
+        <v>6.780000000000001</v>
+      </c>
+      <c r="F67">
+        <v>21.58</v>
+      </c>
+      <c r="G67">
+        <v>1.7</v>
+      </c>
+      <c r="H67">
+        <v>18.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.985</v>
+      </c>
+      <c r="K67">
+        <v>0.112</v>
+      </c>
+      <c r="L67">
+        <v>0.873</v>
+      </c>
+      <c r="M67">
+        <v>5.153304</v>
+      </c>
+      <c r="N67">
+        <v>-4.280304</v>
+      </c>
+      <c r="O67">
+        <v>-0.6420456000000001</v>
+      </c>
+      <c r="P67">
+        <v>-3.6382584</v>
+      </c>
+      <c r="Q67">
+        <v>-3.5262584</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1541169683429439</v>
+      </c>
+      <c r="T67">
+        <v>1.563658256139187</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0254108820283065</v>
+      </c>
+      <c r="W67">
+        <v>0.2327318813716404</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1694058801887101</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2072166618115966</v>
+      </c>
+      <c r="C68">
+        <v>-12.19857056275656</v>
+      </c>
+      <c r="D68">
+        <v>8.013429437243442</v>
+      </c>
+      <c r="E68">
+        <v>7.112000000000002</v>
+      </c>
+      <c r="F68">
+        <v>21.912</v>
+      </c>
+      <c r="G68">
+        <v>1.7</v>
+      </c>
+      <c r="H68">
+        <v>18.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.985</v>
+      </c>
+      <c r="K68">
+        <v>0.112</v>
+      </c>
+      <c r="L68">
+        <v>0.873</v>
+      </c>
+      <c r="M68">
+        <v>5.232585600000001</v>
+      </c>
+      <c r="N68">
+        <v>-4.359585600000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.6539378400000002</v>
+      </c>
+      <c r="P68">
+        <v>-3.705647760000001</v>
+      </c>
+      <c r="Q68">
+        <v>-3.593647760000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1575086438824423</v>
+      </c>
+      <c r="T68">
+        <v>1.609648204849163</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02502586866424125</v>
+      </c>
+      <c r="W68">
+        <v>0.2328238225629792</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.166839124428275</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2092166618115967</v>
+      </c>
+      <c r="C69">
+        <v>-12.62461570308565</v>
+      </c>
+      <c r="D69">
+        <v>7.919384296914354</v>
+      </c>
+      <c r="E69">
+        <v>7.444000000000003</v>
+      </c>
+      <c r="F69">
+        <v>22.244</v>
+      </c>
+      <c r="G69">
+        <v>1.7</v>
+      </c>
+      <c r="H69">
+        <v>18.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.985</v>
+      </c>
+      <c r="K69">
+        <v>0.112</v>
+      </c>
+      <c r="L69">
+        <v>0.873</v>
+      </c>
+      <c r="M69">
+        <v>5.311867200000001</v>
+      </c>
+      <c r="N69">
+        <v>-4.438867200000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.6658300800000002</v>
+      </c>
+      <c r="P69">
+        <v>-3.773037120000001</v>
+      </c>
+      <c r="Q69">
+        <v>-3.66103712</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1611058755152436</v>
+      </c>
+      <c r="T69">
+        <v>1.658425423177926</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02465234823641675</v>
+      </c>
+      <c r="W69">
+        <v>0.2329130192411437</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1643489882427783</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2112166618115967</v>
+      </c>
+      <c r="C70">
+        <v>-13.04847903246118</v>
+      </c>
+      <c r="D70">
+        <v>7.827520967538821</v>
+      </c>
+      <c r="E70">
+        <v>7.776000000000003</v>
+      </c>
+      <c r="F70">
+        <v>22.576</v>
+      </c>
+      <c r="G70">
+        <v>1.7</v>
+      </c>
+      <c r="H70">
+        <v>18.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.985</v>
+      </c>
+      <c r="K70">
+        <v>0.112</v>
+      </c>
+      <c r="L70">
+        <v>0.873</v>
+      </c>
+      <c r="M70">
+        <v>5.391148800000002</v>
+      </c>
+      <c r="N70">
+        <v>-4.518148800000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.6777223200000003</v>
+      </c>
+      <c r="P70">
+        <v>-3.840426480000001</v>
+      </c>
+      <c r="Q70">
+        <v>-3.728426480000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1649279341250949</v>
+      </c>
+      <c r="T70">
+        <v>1.710251217652236</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02428981370352827</v>
+      </c>
+      <c r="W70">
+        <v>0.2329995924875975</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1619320913568552</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2132166618115967</v>
+      </c>
+      <c r="C71">
+        <v>-13.470235606016</v>
+      </c>
+      <c r="D71">
+        <v>7.737764393984005</v>
+      </c>
+      <c r="E71">
+        <v>8.108000000000004</v>
+      </c>
+      <c r="F71">
+        <v>22.908</v>
+      </c>
+      <c r="G71">
+        <v>1.7</v>
+      </c>
+      <c r="H71">
+        <v>18.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.985</v>
+      </c>
+      <c r="K71">
+        <v>0.112</v>
+      </c>
+      <c r="L71">
+        <v>0.873</v>
+      </c>
+      <c r="M71">
+        <v>5.470430400000001</v>
+      </c>
+      <c r="N71">
+        <v>-4.597430400000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.6896145600000003</v>
+      </c>
+      <c r="P71">
+        <v>-3.907815840000001</v>
+      </c>
+      <c r="Q71">
+        <v>-3.795815840000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1689965771613883</v>
+      </c>
+      <c r="T71">
+        <v>1.76542061177005</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02393778741796989</v>
+      </c>
+      <c r="W71">
+        <v>0.2330836563645888</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1595852494531326</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2152166618115967</v>
+      </c>
+      <c r="C72">
+        <v>-13.88995707534351</v>
+      </c>
+      <c r="D72">
+        <v>7.650042924656492</v>
+      </c>
+      <c r="E72">
+        <v>8.440000000000005</v>
+      </c>
+      <c r="F72">
+        <v>23.24000000000001</v>
+      </c>
+      <c r="G72">
+        <v>1.7</v>
+      </c>
+      <c r="H72">
+        <v>18.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.985</v>
+      </c>
+      <c r="K72">
+        <v>0.112</v>
+      </c>
+      <c r="L72">
+        <v>0.873</v>
+      </c>
+      <c r="M72">
+        <v>5.549712000000001</v>
+      </c>
+      <c r="N72">
+        <v>-4.676712000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.7015068000000003</v>
+      </c>
+      <c r="P72">
+        <v>-3.975205200000001</v>
+      </c>
+      <c r="Q72">
+        <v>-3.863205200000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1733364630667679</v>
+      </c>
+      <c r="T72">
+        <v>1.824267965495718</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0235958190262846</v>
+      </c>
+      <c r="W72">
+        <v>0.2331653184165232</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1573054601752307</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2172166618115967</v>
+      </c>
+      <c r="C73">
+        <v>-14.30771187926126</v>
+      </c>
+      <c r="D73">
+        <v>7.56428812073874</v>
+      </c>
+      <c r="E73">
+        <v>8.771999999999998</v>
+      </c>
+      <c r="F73">
+        <v>23.572</v>
+      </c>
+      <c r="G73">
+        <v>1.7</v>
+      </c>
+      <c r="H73">
+        <v>18.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.985</v>
+      </c>
+      <c r="K73">
+        <v>0.112</v>
+      </c>
+      <c r="L73">
+        <v>0.873</v>
+      </c>
+      <c r="M73">
+        <v>5.6289936</v>
+      </c>
+      <c r="N73">
+        <v>-4.7559936</v>
+      </c>
+      <c r="O73">
+        <v>-0.7133990400000001</v>
+      </c>
+      <c r="P73">
+        <v>-4.04259456</v>
+      </c>
+      <c r="Q73">
+        <v>-3.930594559999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1779756514483806</v>
+      </c>
+      <c r="T73">
+        <v>1.887173757409363</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02326348354704116</v>
+      </c>
+      <c r="W73">
+        <v>0.2332446801289666</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1550898903136078</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2192166618115967</v>
+      </c>
+      <c r="C74">
+        <v>-14.72356542188625</v>
+      </c>
+      <c r="D74">
+        <v>7.480434578113749</v>
+      </c>
+      <c r="E74">
+        <v>9.103999999999999</v>
+      </c>
+      <c r="F74">
+        <v>23.904</v>
+      </c>
+      <c r="G74">
+        <v>1.7</v>
+      </c>
+      <c r="H74">
+        <v>18.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.985</v>
+      </c>
+      <c r="K74">
+        <v>0.112</v>
+      </c>
+      <c r="L74">
+        <v>0.873</v>
+      </c>
+      <c r="M74">
+        <v>5.7082752</v>
+      </c>
+      <c r="N74">
+        <v>-4.8352752</v>
+      </c>
+      <c r="O74">
+        <v>-0.7252912800000001</v>
+      </c>
+      <c r="P74">
+        <v>-4.109983919999999</v>
+      </c>
+      <c r="Q74">
+        <v>-3.997983919999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1829462104286799</v>
+      </c>
+      <c r="T74">
+        <v>1.954572820173983</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02294037960888782</v>
+      </c>
+      <c r="W74">
+        <v>0.2333218373493976</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1529358640592521</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2212166618115967</v>
+      </c>
+      <c r="C75">
+        <v>-15.13758023899588</v>
+      </c>
+      <c r="D75">
+        <v>7.398419761004118</v>
+      </c>
+      <c r="E75">
+        <v>9.436</v>
+      </c>
+      <c r="F75">
+        <v>24.236</v>
+      </c>
+      <c r="G75">
+        <v>1.7</v>
+      </c>
+      <c r="H75">
+        <v>18.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.985</v>
+      </c>
+      <c r="K75">
+        <v>0.112</v>
+      </c>
+      <c r="L75">
+        <v>0.873</v>
+      </c>
+      <c r="M75">
+        <v>5.787556800000001</v>
+      </c>
+      <c r="N75">
+        <v>-4.914556800000001</v>
+      </c>
+      <c r="O75">
+        <v>-0.7371835200000002</v>
+      </c>
+      <c r="P75">
+        <v>-4.17737328</v>
+      </c>
+      <c r="Q75">
+        <v>-4.06537328</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1882849589630754</v>
+      </c>
+      <c r="T75">
+        <v>2.026964406106353</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0226261278334236</v>
+      </c>
+      <c r="W75">
+        <v>0.2333968806733785</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.150840852222824</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2232166618115966</v>
+      </c>
+      <c r="C76">
+        <v>-15.54981615356375</v>
+      </c>
+      <c r="D76">
+        <v>7.318183846436248</v>
+      </c>
+      <c r="E76">
+        <v>9.768000000000001</v>
+      </c>
+      <c r="F76">
+        <v>24.568</v>
+      </c>
+      <c r="G76">
+        <v>1.7</v>
+      </c>
+      <c r="H76">
+        <v>18.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.985</v>
+      </c>
+      <c r="K76">
+        <v>0.112</v>
+      </c>
+      <c r="L76">
+        <v>0.873</v>
+      </c>
+      <c r="M76">
+        <v>5.866838400000001</v>
+      </c>
+      <c r="N76">
+        <v>-4.9938384</v>
+      </c>
+      <c r="O76">
+        <v>-0.7490757600000002</v>
+      </c>
+      <c r="P76">
+        <v>-4.24476264</v>
+      </c>
+      <c r="Q76">
+        <v>-4.13276264</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1940343804616552</v>
+      </c>
+      <c r="T76">
+        <v>2.104924575571982</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02232036934918814</v>
+      </c>
+      <c r="W76">
+        <v>0.2334698957994139</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1488024623279209</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2252166618115967</v>
+      </c>
+      <c r="C77">
+        <v>-15.96033042128337</v>
+      </c>
+      <c r="D77">
+        <v>7.239669578716629</v>
+      </c>
+      <c r="E77">
+        <v>10.1</v>
+      </c>
+      <c r="F77">
+        <v>24.9</v>
+      </c>
+      <c r="G77">
+        <v>1.7</v>
+      </c>
+      <c r="H77">
+        <v>18.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.985</v>
+      </c>
+      <c r="K77">
+        <v>0.112</v>
+      </c>
+      <c r="L77">
+        <v>0.873</v>
+      </c>
+      <c r="M77">
+        <v>5.946120000000001</v>
+      </c>
+      <c r="N77">
+        <v>-5.07312</v>
+      </c>
+      <c r="O77">
+        <v>-0.7609680000000002</v>
+      </c>
+      <c r="P77">
+        <v>-4.312152</v>
+      </c>
+      <c r="Q77">
+        <v>-4.200152</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2002437556801215</v>
+      </c>
+      <c r="T77">
+        <v>2.189121558594862</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0220227644245323</v>
+      </c>
+      <c r="W77">
+        <v>0.2335409638554217</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1468184294968821</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2272166618115967</v>
+      </c>
+      <c r="C78">
+        <v>-16.36917786682358</v>
+      </c>
+      <c r="D78">
+        <v>7.162822133176425</v>
+      </c>
+      <c r="E78">
+        <v>10.432</v>
+      </c>
+      <c r="F78">
+        <v>25.232</v>
+      </c>
+      <c r="G78">
+        <v>1.7</v>
+      </c>
+      <c r="H78">
+        <v>18.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.985</v>
+      </c>
+      <c r="K78">
+        <v>0.112</v>
+      </c>
+      <c r="L78">
+        <v>0.873</v>
+      </c>
+      <c r="M78">
+        <v>6.025401600000001</v>
+      </c>
+      <c r="N78">
+        <v>-5.152401600000001</v>
+      </c>
+      <c r="O78">
+        <v>-0.7728602400000003</v>
+      </c>
+      <c r="P78">
+        <v>-4.379541360000001</v>
+      </c>
+      <c r="Q78">
+        <v>-4.267541360000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2069705788334599</v>
+      </c>
+      <c r="T78">
+        <v>2.280334956869648</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02173299120842003</v>
+      </c>
+      <c r="W78">
+        <v>0.2336101616994293</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1448866080561335</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2292166618115966</v>
+      </c>
+      <c r="C79">
+        <v>-16.77641101149727</v>
+      </c>
+      <c r="D79">
+        <v>7.087588988502737</v>
+      </c>
+      <c r="E79">
+        <v>10.764</v>
+      </c>
+      <c r="F79">
+        <v>25.564</v>
+      </c>
+      <c r="G79">
+        <v>1.7</v>
+      </c>
+      <c r="H79">
+        <v>18.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.985</v>
+      </c>
+      <c r="K79">
+        <v>0.112</v>
+      </c>
+      <c r="L79">
+        <v>0.873</v>
+      </c>
+      <c r="M79">
+        <v>6.104683200000001</v>
+      </c>
+      <c r="N79">
+        <v>-5.231683200000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.7847524800000002</v>
+      </c>
+      <c r="P79">
+        <v>-4.446930720000001</v>
+      </c>
+      <c r="Q79">
+        <v>-4.334930720000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2142823431305668</v>
+      </c>
+      <c r="T79">
+        <v>2.379479954994415</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02145074456934964</v>
+      </c>
+      <c r="W79">
+        <v>0.2336775621968393</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1430049637956643</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2312166618115967</v>
+      </c>
+      <c r="C80">
+        <v>-17.18208019296808</v>
+      </c>
+      <c r="D80">
+        <v>7.013919807031929</v>
+      </c>
+      <c r="E80">
+        <v>11.096</v>
+      </c>
+      <c r="F80">
+        <v>25.896</v>
+      </c>
+      <c r="G80">
+        <v>1.7</v>
+      </c>
+      <c r="H80">
+        <v>18.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.985</v>
+      </c>
+      <c r="K80">
+        <v>0.112</v>
+      </c>
+      <c r="L80">
+        <v>0.873</v>
+      </c>
+      <c r="M80">
+        <v>6.183964800000001</v>
+      </c>
+      <c r="N80">
+        <v>-5.310964800000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.7966447200000002</v>
+      </c>
+      <c r="P80">
+        <v>-4.514320080000001</v>
+      </c>
+      <c r="Q80">
+        <v>-4.402320080000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2222588132728653</v>
+      </c>
+      <c r="T80">
+        <v>2.487638134766888</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02117573502358875</v>
+      </c>
+      <c r="W80">
+        <v>0.233743234476367</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1411715668239251</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2332166618115967</v>
+      </c>
+      <c r="C81">
+        <v>-17.58623367756837</v>
+      </c>
+      <c r="D81">
+        <v>6.941766322431635</v>
+      </c>
+      <c r="E81">
+        <v>11.428</v>
+      </c>
+      <c r="F81">
+        <v>26.22800000000001</v>
+      </c>
+      <c r="G81">
+        <v>1.7</v>
+      </c>
+      <c r="H81">
+        <v>18.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.985</v>
+      </c>
+      <c r="K81">
+        <v>0.112</v>
+      </c>
+      <c r="L81">
+        <v>0.873</v>
+      </c>
+      <c r="M81">
+        <v>6.263246400000002</v>
+      </c>
+      <c r="N81">
+        <v>-5.390246400000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.8085369600000003</v>
+      </c>
+      <c r="P81">
+        <v>-4.581709440000001</v>
+      </c>
+      <c r="Q81">
+        <v>-4.469709440000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2309949472382399</v>
+      </c>
+      <c r="T81">
+        <v>2.606097093565312</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02090768774480914</v>
+      </c>
+      <c r="W81">
+        <v>0.2338072441665396</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1393845849653943</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2352166618115966</v>
+      </c>
+      <c r="C82">
+        <v>-17.98891776575525</v>
+      </c>
+      <c r="D82">
+        <v>6.871082234244758</v>
+      </c>
+      <c r="E82">
+        <v>11.76</v>
+      </c>
+      <c r="F82">
+        <v>26.56</v>
+      </c>
+      <c r="G82">
+        <v>1.7</v>
+      </c>
+      <c r="H82">
+        <v>18.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.985</v>
+      </c>
+      <c r="K82">
+        <v>0.112</v>
+      </c>
+      <c r="L82">
+        <v>0.873</v>
+      </c>
+      <c r="M82">
+        <v>6.342528000000001</v>
+      </c>
+      <c r="N82">
+        <v>-5.469528</v>
+      </c>
+      <c r="O82">
+        <v>-0.8204292000000002</v>
+      </c>
+      <c r="P82">
+        <v>-4.6490988</v>
+      </c>
+      <c r="Q82">
+        <v>-4.5370988</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2406046946001519</v>
+      </c>
+      <c r="T82">
+        <v>2.736401948243577</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02064634164799903</v>
+      </c>
+      <c r="W82">
+        <v>0.2338696536144578</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1376422776533269</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2372166618115966</v>
+      </c>
+      <c r="C83">
+        <v>-18.39017689118866</v>
+      </c>
+      <c r="D83">
+        <v>6.801823108811341</v>
+      </c>
+      <c r="E83">
+        <v>12.092</v>
+      </c>
+      <c r="F83">
+        <v>26.892</v>
+      </c>
+      <c r="G83">
+        <v>1.7</v>
+      </c>
+      <c r="H83">
+        <v>18.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.985</v>
+      </c>
+      <c r="K83">
+        <v>0.112</v>
+      </c>
+      <c r="L83">
+        <v>0.873</v>
+      </c>
+      <c r="M83">
+        <v>6.421809600000001</v>
+      </c>
+      <c r="N83">
+        <v>-5.548809600000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.8323214400000003</v>
+      </c>
+      <c r="P83">
+        <v>-4.716488160000001</v>
+      </c>
+      <c r="Q83">
+        <v>-4.604488160000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2512259943159494</v>
+      </c>
+      <c r="T83">
+        <v>2.880423103414292</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02039144854123361</v>
+      </c>
+      <c r="W83">
+        <v>0.2339305220883534</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1359429902748908</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2392166618115966</v>
+      </c>
+      <c r="C84">
+        <v>-18.79005371387724</v>
+      </c>
+      <c r="D84">
+        <v>6.733946286122761</v>
+      </c>
+      <c r="E84">
+        <v>12.424</v>
+      </c>
+      <c r="F84">
+        <v>27.224</v>
+      </c>
+      <c r="G84">
+        <v>1.7</v>
+      </c>
+      <c r="H84">
+        <v>18.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.985</v>
+      </c>
+      <c r="K84">
+        <v>0.112</v>
+      </c>
+      <c r="L84">
+        <v>0.873</v>
+      </c>
+      <c r="M84">
+        <v>6.501091200000001</v>
+      </c>
+      <c r="N84">
+        <v>-5.628091200000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.8442136800000003</v>
+      </c>
+      <c r="P84">
+        <v>-4.783877520000001</v>
+      </c>
+      <c r="Q84">
+        <v>-4.671877520000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2630274384446132</v>
+      </c>
+      <c r="T84">
+        <v>3.040446609159531</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02014277233951125</v>
+      </c>
+      <c r="W84">
+        <v>0.2339899059653247</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.134285148930075</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2412166618115966</v>
+      </c>
+      <c r="C85">
+        <v>-19.18858920780205</v>
+      </c>
+      <c r="D85">
+        <v>6.667410792197955</v>
+      </c>
+      <c r="E85">
+        <v>12.756</v>
+      </c>
+      <c r="F85">
+        <v>27.556</v>
+      </c>
+      <c r="G85">
+        <v>1.7</v>
+      </c>
+      <c r="H85">
+        <v>18.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.985</v>
+      </c>
+      <c r="K85">
+        <v>0.112</v>
+      </c>
+      <c r="L85">
+        <v>0.873</v>
+      </c>
+      <c r="M85">
+        <v>6.580372800000001</v>
+      </c>
+      <c r="N85">
+        <v>-5.707372800000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.8561059200000003</v>
+      </c>
+      <c r="P85">
+        <v>-4.851266880000001</v>
+      </c>
+      <c r="Q85">
+        <v>-4.739266880000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2762172877648846</v>
+      </c>
+      <c r="T85">
+        <v>3.219296409698327</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01990008833542075</v>
+      </c>
+      <c r="W85">
+        <v>0.2340478589055015</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1326672555694717</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2432166618115966</v>
+      </c>
+      <c r="C86">
+        <v>-19.58582274339656</v>
+      </c>
+      <c r="D86">
+        <v>6.602177256603449</v>
+      </c>
+      <c r="E86">
+        <v>13.088</v>
+      </c>
+      <c r="F86">
+        <v>27.888</v>
+      </c>
+      <c r="G86">
+        <v>1.7</v>
+      </c>
+      <c r="H86">
+        <v>18.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.985</v>
+      </c>
+      <c r="K86">
+        <v>0.112</v>
+      </c>
+      <c r="L86">
+        <v>0.873</v>
+      </c>
+      <c r="M86">
+        <v>6.659654400000001</v>
+      </c>
+      <c r="N86">
+        <v>-5.786654400000001</v>
+      </c>
+      <c r="O86">
+        <v>-0.8679981600000002</v>
+      </c>
+      <c r="P86">
+        <v>-4.918656240000001</v>
+      </c>
+      <c r="Q86">
+        <v>-4.806656240000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2910558682501898</v>
+      </c>
+      <c r="T86">
+        <v>3.420502435304471</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01966318252190384</v>
+      </c>
+      <c r="W86">
+        <v>0.2341044320137694</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.131087883479359</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2452166618115966</v>
+      </c>
+      <c r="C87">
+        <v>-19.98179216523159</v>
+      </c>
+      <c r="D87">
+        <v>6.53820783476841</v>
+      </c>
+      <c r="E87">
+        <v>13.42</v>
+      </c>
+      <c r="F87">
+        <v>28.22</v>
+      </c>
+      <c r="G87">
+        <v>1.7</v>
+      </c>
+      <c r="H87">
+        <v>18.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.985</v>
+      </c>
+      <c r="K87">
+        <v>0.112</v>
+      </c>
+      <c r="L87">
+        <v>0.873</v>
+      </c>
+      <c r="M87">
+        <v>6.738936000000001</v>
+      </c>
+      <c r="N87">
+        <v>-5.865936</v>
+      </c>
+      <c r="O87">
+        <v>-0.8798904000000002</v>
+      </c>
+      <c r="P87">
+        <v>-4.986045600000001</v>
+      </c>
+      <c r="Q87">
+        <v>-4.874045600000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3078729261335357</v>
+      </c>
+      <c r="T87">
+        <v>3.648535930991435</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01943185096282262</v>
+      </c>
+      <c r="W87">
+        <v>0.234159673990078</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1295456730854841</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2472166618115966</v>
+      </c>
+      <c r="C88">
+        <v>-20.37653386522753</v>
+      </c>
+      <c r="D88">
+        <v>6.475466134772478</v>
+      </c>
+      <c r="E88">
+        <v>13.752</v>
+      </c>
+      <c r="F88">
+        <v>28.552</v>
+      </c>
+      <c r="G88">
+        <v>1.7</v>
+      </c>
+      <c r="H88">
+        <v>18.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.985</v>
+      </c>
+      <c r="K88">
+        <v>0.112</v>
+      </c>
+      <c r="L88">
+        <v>0.873</v>
+      </c>
+      <c r="M88">
+        <v>6.818217600000001</v>
+      </c>
+      <c r="N88">
+        <v>-5.945217600000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.8917826400000003</v>
+      </c>
+      <c r="P88">
+        <v>-5.053434960000001</v>
+      </c>
+      <c r="Q88">
+        <v>-4.94143496</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3270924208573597</v>
+      </c>
+      <c r="T88">
+        <v>3.909145640347967</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01920589920744096</v>
+      </c>
+      <c r="W88">
+        <v>0.2342136312692631</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1280393280496064</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2492166618115966</v>
+      </c>
+      <c r="C89">
+        <v>-20.77008285169106</v>
+      </c>
+      <c r="D89">
+        <v>6.413917148308938</v>
+      </c>
+      <c r="E89">
+        <v>14.084</v>
+      </c>
+      <c r="F89">
+        <v>28.884</v>
+      </c>
+      <c r="G89">
+        <v>1.7</v>
+      </c>
+      <c r="H89">
+        <v>18.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.985</v>
+      </c>
+      <c r="K89">
+        <v>0.112</v>
+      </c>
+      <c r="L89">
+        <v>0.873</v>
+      </c>
+      <c r="M89">
+        <v>6.897499200000001</v>
+      </c>
+      <c r="N89">
+        <v>-6.024499200000001</v>
+      </c>
+      <c r="O89">
+        <v>-0.9036748800000003</v>
+      </c>
+      <c r="P89">
+        <v>-5.120824320000001</v>
+      </c>
+      <c r="Q89">
+        <v>-5.00882432</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3492687609233105</v>
+      </c>
+      <c r="T89">
+        <v>4.209849151143964</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01898514174528647</v>
+      </c>
+      <c r="W89">
+        <v>0.2342663481512256</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1265676116352431</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2512166618115966</v>
+      </c>
+      <c r="C90">
+        <v>-21.16247281445206</v>
+      </c>
+      <c r="D90">
+        <v>6.353527185547938</v>
+      </c>
+      <c r="E90">
+        <v>14.416</v>
+      </c>
+      <c r="F90">
+        <v>29.216</v>
+      </c>
+      <c r="G90">
+        <v>1.7</v>
+      </c>
+      <c r="H90">
+        <v>18.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.985</v>
+      </c>
+      <c r="K90">
+        <v>0.112</v>
+      </c>
+      <c r="L90">
+        <v>0.873</v>
+      </c>
+      <c r="M90">
+        <v>6.9767808</v>
+      </c>
+      <c r="N90">
+        <v>-6.1037808</v>
+      </c>
+      <c r="O90">
+        <v>-0.9155671200000002</v>
+      </c>
+      <c r="P90">
+        <v>-5.18821368</v>
+      </c>
+      <c r="Q90">
+        <v>-5.07621368</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3751411576669197</v>
+      </c>
+      <c r="T90">
+        <v>4.560669913739295</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01876940149818094</v>
+      </c>
+      <c r="W90">
+        <v>0.2343178669222344</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1251293433212063</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2532166618115967</v>
+      </c>
+      <c r="C91">
+        <v>-21.55373618635485</v>
+      </c>
+      <c r="D91">
+        <v>6.294263813645147</v>
+      </c>
+      <c r="E91">
+        <v>14.748</v>
+      </c>
+      <c r="F91">
+        <v>29.548</v>
+      </c>
+      <c r="G91">
+        <v>1.7</v>
+      </c>
+      <c r="H91">
+        <v>18.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.985</v>
+      </c>
+      <c r="K91">
+        <v>0.112</v>
+      </c>
+      <c r="L91">
+        <v>0.873</v>
+      </c>
+      <c r="M91">
+        <v>7.056062400000001</v>
+      </c>
+      <c r="N91">
+        <v>-6.183062400000001</v>
+      </c>
+      <c r="O91">
+        <v>-0.9274593600000003</v>
+      </c>
+      <c r="P91">
+        <v>-5.25560304</v>
+      </c>
+      <c r="Q91">
+        <v>-5.14360304</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4057176265457307</v>
+      </c>
+      <c r="T91">
+        <v>4.975276269533777</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01855850934651598</v>
+      </c>
+      <c r="W91">
+        <v>0.234368227968052</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1237233956434399</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2552166618115966</v>
+      </c>
+      <c r="C92">
+        <v>-21.94390420133999</v>
+      </c>
+      <c r="D92">
+        <v>6.236095798660012</v>
+      </c>
+      <c r="E92">
+        <v>15.08</v>
+      </c>
+      <c r="F92">
+        <v>29.88</v>
+      </c>
+      <c r="G92">
+        <v>1.7</v>
+      </c>
+      <c r="H92">
+        <v>18.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.985</v>
+      </c>
+      <c r="K92">
+        <v>0.112</v>
+      </c>
+      <c r="L92">
+        <v>0.873</v>
+      </c>
+      <c r="M92">
+        <v>7.135344000000001</v>
+      </c>
+      <c r="N92">
+        <v>-6.262344000000001</v>
+      </c>
+      <c r="O92">
+        <v>-0.9393516000000002</v>
+      </c>
+      <c r="P92">
+        <v>-5.3229924</v>
+      </c>
+      <c r="Q92">
+        <v>-5.2109924</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4424093892003038</v>
+      </c>
+      <c r="T92">
+        <v>5.472803896487155</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01835230368711025</v>
+      </c>
+      <c r="W92">
+        <v>0.2344174698795181</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1223486912474017</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2572166618115966</v>
+      </c>
+      <c r="C93">
+        <v>-22.33300694933492</v>
+      </c>
+      <c r="D93">
+        <v>6.178993050665085</v>
+      </c>
+      <c r="E93">
+        <v>15.412</v>
+      </c>
+      <c r="F93">
+        <v>30.212</v>
+      </c>
+      <c r="G93">
+        <v>1.7</v>
+      </c>
+      <c r="H93">
+        <v>18.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.985</v>
+      </c>
+      <c r="K93">
+        <v>0.112</v>
+      </c>
+      <c r="L93">
+        <v>0.873</v>
+      </c>
+      <c r="M93">
+        <v>7.214625600000002</v>
+      </c>
+      <c r="N93">
+        <v>-6.341625600000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.9512438400000003</v>
+      </c>
+      <c r="P93">
+        <v>-5.390381760000001</v>
+      </c>
+      <c r="Q93">
+        <v>-5.278381760000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4872548768892264</v>
+      </c>
+      <c r="T93">
+        <v>6.080893218319061</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01815063002021893</v>
+      </c>
+      <c r="W93">
+        <v>0.2344656295511718</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1210042001347928</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2592166618115966</v>
+      </c>
+      <c r="C94">
+        <v>-22.72107342815626</v>
+      </c>
+      <c r="D94">
+        <v>6.122926571843747</v>
+      </c>
+      <c r="E94">
+        <v>15.744</v>
+      </c>
+      <c r="F94">
+        <v>30.544</v>
+      </c>
+      <c r="G94">
+        <v>1.7</v>
+      </c>
+      <c r="H94">
+        <v>18.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.985</v>
+      </c>
+      <c r="K94">
+        <v>0.112</v>
+      </c>
+      <c r="L94">
+        <v>0.873</v>
+      </c>
+      <c r="M94">
+        <v>7.293907200000001</v>
+      </c>
+      <c r="N94">
+        <v>-6.420907200000001</v>
+      </c>
+      <c r="O94">
+        <v>-0.9631360800000003</v>
+      </c>
+      <c r="P94">
+        <v>-5.457771120000001</v>
+      </c>
+      <c r="Q94">
+        <v>-5.345771120000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5433117365003799</v>
+      </c>
+      <c r="T94">
+        <v>6.841004870608946</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01795334056347742</v>
+      </c>
+      <c r="W94">
+        <v>0.2345127422734416</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1196889370898495</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2612166618115967</v>
+      </c>
+      <c r="C95">
+        <v>-23.10813159261185</v>
+      </c>
+      <c r="D95">
+        <v>6.06786840738815</v>
+      </c>
+      <c r="E95">
+        <v>16.076</v>
+      </c>
+      <c r="F95">
+        <v>30.876</v>
+      </c>
+      <c r="G95">
+        <v>1.7</v>
+      </c>
+      <c r="H95">
+        <v>18.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.985</v>
+      </c>
+      <c r="K95">
+        <v>0.112</v>
+      </c>
+      <c r="L95">
+        <v>0.873</v>
+      </c>
+      <c r="M95">
+        <v>7.373188800000001</v>
+      </c>
+      <c r="N95">
+        <v>-6.500188800000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.9750283200000003</v>
+      </c>
+      <c r="P95">
+        <v>-5.52516048</v>
+      </c>
+      <c r="Q95">
+        <v>-5.41316048</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6153848417147201</v>
+      </c>
+      <c r="T95">
+        <v>7.81829128069594</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01776029389075185</v>
+      </c>
+      <c r="W95">
+        <v>0.2345588418188885</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1184019592716791</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2632166618115967</v>
+      </c>
+      <c r="C96">
+        <v>-23.4942084009772</v>
+      </c>
+      <c r="D96">
+        <v>6.013791599022806</v>
+      </c>
+      <c r="E96">
+        <v>16.408</v>
+      </c>
+      <c r="F96">
+        <v>31.20800000000001</v>
+      </c>
+      <c r="G96">
+        <v>1.7</v>
+      </c>
+      <c r="H96">
+        <v>18.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.985</v>
+      </c>
+      <c r="K96">
+        <v>0.112</v>
+      </c>
+      <c r="L96">
+        <v>0.873</v>
+      </c>
+      <c r="M96">
+        <v>7.452470400000002</v>
+      </c>
+      <c r="N96">
+        <v>-6.579470400000002</v>
+      </c>
+      <c r="O96">
+        <v>-0.9869205600000004</v>
+      </c>
+      <c r="P96">
+        <v>-5.592549840000001</v>
+      </c>
+      <c r="Q96">
+        <v>-5.480549840000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7114823153338403</v>
+      </c>
+      <c r="T96">
+        <v>9.1213398274786</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01757135459404173</v>
+      </c>
+      <c r="W96">
+        <v>0.2346039605229429</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1171423639602782</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2652166618115966</v>
+      </c>
+      <c r="C97">
+        <v>-23.87932985900865</v>
+      </c>
+      <c r="D97">
+        <v>5.960670140991355</v>
+      </c>
+      <c r="E97">
+        <v>16.74000000000001</v>
+      </c>
+      <c r="F97">
+        <v>31.54000000000001</v>
+      </c>
+      <c r="G97">
+        <v>1.7</v>
+      </c>
+      <c r="H97">
+        <v>18.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.985</v>
+      </c>
+      <c r="K97">
+        <v>0.112</v>
+      </c>
+      <c r="L97">
+        <v>0.873</v>
+      </c>
+      <c r="M97">
+        <v>7.531752000000002</v>
+      </c>
+      <c r="N97">
+        <v>-6.658752000000002</v>
+      </c>
+      <c r="O97">
+        <v>-0.9988128000000004</v>
+      </c>
+      <c r="P97">
+        <v>-5.659939200000001</v>
+      </c>
+      <c r="Q97">
+        <v>-5.547939200000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8460187784006084</v>
+      </c>
+      <c r="T97">
+        <v>10.94560779297432</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01738639296673603</v>
+      </c>
+      <c r="W97">
+        <v>0.2346481293595434</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1159092864449068</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2672166618115966</v>
+      </c>
+      <c r="C98">
+        <v>-24.26352106164436</v>
+      </c>
+      <c r="D98">
+        <v>5.908478938355643</v>
+      </c>
+      <c r="E98">
+        <v>17.072</v>
+      </c>
+      <c r="F98">
+        <v>31.872</v>
+      </c>
+      <c r="G98">
+        <v>1.7</v>
+      </c>
+      <c r="H98">
+        <v>18.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.985</v>
+      </c>
+      <c r="K98">
+        <v>0.112</v>
+      </c>
+      <c r="L98">
+        <v>0.873</v>
+      </c>
+      <c r="M98">
+        <v>7.611033600000001</v>
+      </c>
+      <c r="N98">
+        <v>-6.738033600000001</v>
+      </c>
+      <c r="O98">
+        <v>-1.01070504</v>
+      </c>
+      <c r="P98">
+        <v>-5.72732856</v>
+      </c>
+      <c r="Q98">
+        <v>-5.61532856</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.047823473000758</v>
+      </c>
+      <c r="T98">
+        <v>13.68200974121787</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01720528470666586</v>
+      </c>
+      <c r="W98">
+        <v>0.2346913780120482</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1147018980444391</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2692166618115966</v>
+      </c>
+      <c r="C99">
+        <v>-24.64680623253349</v>
+      </c>
+      <c r="D99">
+        <v>5.857193767466509</v>
+      </c>
+      <c r="E99">
+        <v>17.404</v>
+      </c>
+      <c r="F99">
+        <v>32.204</v>
+      </c>
+      <c r="G99">
+        <v>1.7</v>
+      </c>
+      <c r="H99">
+        <v>18.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.985</v>
+      </c>
+      <c r="K99">
+        <v>0.112</v>
+      </c>
+      <c r="L99">
+        <v>0.873</v>
+      </c>
+      <c r="M99">
+        <v>7.690315200000001</v>
+      </c>
+      <c r="N99">
+        <v>-6.8173152</v>
+      </c>
+      <c r="O99">
+        <v>-1.02259728</v>
+      </c>
+      <c r="P99">
+        <v>-5.79471792</v>
+      </c>
+      <c r="Q99">
+        <v>-5.68271792</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.384164630667678</v>
+      </c>
+      <c r="T99">
+        <v>18.24267965495717</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01702791063752498</v>
+      </c>
+      <c r="W99">
+        <v>0.234733734939759</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1135194042501665</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2712166618115966</v>
+      </c>
+      <c r="C100">
+        <v>-25.02920876152442</v>
+      </c>
+      <c r="D100">
+        <v>5.806791238475582</v>
+      </c>
+      <c r="E100">
+        <v>17.736</v>
+      </c>
+      <c r="F100">
+        <v>32.536</v>
+      </c>
+      <c r="G100">
+        <v>1.7</v>
+      </c>
+      <c r="H100">
+        <v>18.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.985</v>
+      </c>
+      <c r="K100">
+        <v>0.112</v>
+      </c>
+      <c r="L100">
+        <v>0.873</v>
+      </c>
+      <c r="M100">
+        <v>7.7695968</v>
+      </c>
+      <c r="N100">
+        <v>-6.8965968</v>
+      </c>
+      <c r="O100">
+        <v>-1.03448952</v>
+      </c>
+      <c r="P100">
+        <v>-5.86210728</v>
+      </c>
+      <c r="Q100">
+        <v>-5.75010728</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.056846946001517</v>
+      </c>
+      <c r="T100">
+        <v>27.36401948243575</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01685415644734615</v>
+      </c>
+      <c r="W100">
+        <v>0.2347752274403738</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1123610429823076</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2732166618115967</v>
+      </c>
+      <c r="C101">
+        <v>-25.41075124023391</v>
+      </c>
+      <c r="D101">
+        <v>5.75724875976609</v>
+      </c>
+      <c r="E101">
+        <v>18.068</v>
+      </c>
+      <c r="F101">
+        <v>32.868</v>
+      </c>
+      <c r="G101">
+        <v>1.7</v>
+      </c>
+      <c r="H101">
+        <v>18.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.985</v>
+      </c>
+      <c r="K101">
+        <v>0.112</v>
+      </c>
+      <c r="L101">
+        <v>0.873</v>
+      </c>
+      <c r="M101">
+        <v>7.848878400000001</v>
+      </c>
+      <c r="N101">
+        <v>-6.975878400000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.04638176</v>
+      </c>
+      <c r="P101">
+        <v>-5.929496640000001</v>
+      </c>
+      <c r="Q101">
+        <v>-5.817496640000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.074893892003034</v>
+      </c>
+      <c r="T101">
+        <v>54.72803896487149</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.0166839124428275</v>
+      </c>
+      <c r="W101">
+        <v>0.2348158817086528</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1112260829521834</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/lithuania/lithuania_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_real_estate_operations_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07597042942827432</v>
+        <v>0.07589472378413191</v>
       </c>
       <c r="C2">
-        <v>43.36014111452741</v>
+        <v>43.03915166901665</v>
       </c>
       <c r="D2">
-        <v>42.53914111452741</v>
+        <v>42.64615166901665</v>
       </c>
       <c r="E2">
-        <v>-20.8</v>
+        <v>-20.372</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="G2">
         <v>0.821</v>
@@ -1451,28 +1451,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0215284</v>
       </c>
       <c r="N2">
-        <v>3.142666666666667</v>
+        <v>3.121138266666667</v>
       </c>
       <c r="O2">
-        <v>0.4714</v>
+        <v>0.46817074</v>
       </c>
       <c r="P2">
-        <v>2.671266666666667</v>
+        <v>2.652967526666667</v>
       </c>
       <c r="Q2">
-        <v>2.795266666666667</v>
+        <v>2.776967526666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07597042942827432</v>
+        <v>0.07622946846882012</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5573264013943646</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>145.9777162569753</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07589472378413191</v>
+        <v>0.07581901813998949</v>
       </c>
       <c r="C3">
-        <v>43.03915166901665</v>
+        <v>42.71870196820505</v>
       </c>
       <c r="D3">
-        <v>42.64615166901665</v>
+        <v>42.75370196820506</v>
       </c>
       <c r="E3">
-        <v>-20.372</v>
+        <v>-19.944</v>
       </c>
       <c r="F3">
-        <v>0.428</v>
+        <v>0.856</v>
       </c>
       <c r="G3">
         <v>0.821</v>
@@ -1533,28 +1533,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0215284</v>
+        <v>0.0430568</v>
       </c>
       <c r="N3">
-        <v>3.121138266666667</v>
+        <v>3.099609866666667</v>
       </c>
       <c r="O3">
-        <v>0.46817074</v>
+        <v>0.46494148</v>
       </c>
       <c r="P3">
-        <v>2.652967526666667</v>
+        <v>2.634668386666667</v>
       </c>
       <c r="Q3">
-        <v>2.776967526666667</v>
+        <v>2.758668386666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07622946846882012</v>
+        <v>0.07649379402039745</v>
       </c>
       <c r="T3">
-        <v>0.5573264013943646</v>
+        <v>0.5621676166988031</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>145.9777162569753</v>
+        <v>72.98885812848765</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07581901813998949</v>
+        <v>0.07574331249584708</v>
       </c>
       <c r="C4">
-        <v>42.71870196820505</v>
+        <v>42.39879610600042</v>
       </c>
       <c r="D4">
-        <v>42.75370196820506</v>
+        <v>42.86179610600042</v>
       </c>
       <c r="E4">
-        <v>-19.944</v>
+        <v>-19.516</v>
       </c>
       <c r="F4">
-        <v>0.856</v>
+        <v>1.284</v>
       </c>
       <c r="G4">
         <v>0.821</v>
@@ -1615,28 +1615,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0430568</v>
+        <v>0.06458519999999998</v>
       </c>
       <c r="N4">
-        <v>3.099609866666667</v>
+        <v>3.078081466666667</v>
       </c>
       <c r="O4">
-        <v>0.46494148</v>
+        <v>0.4617122200000001</v>
       </c>
       <c r="P4">
-        <v>2.634668386666667</v>
+        <v>2.616369246666667</v>
       </c>
       <c r="Q4">
-        <v>2.758668386666667</v>
+        <v>2.740369246666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07649379402039745</v>
+        <v>0.07676356958334751</v>
       </c>
       <c r="T4">
-        <v>0.5621676166988031</v>
+        <v>0.5671086508754979</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.98885812848765</v>
+        <v>48.65923875232512</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07574331249584708</v>
+        <v>0.07566760685170468</v>
       </c>
       <c r="C5">
-        <v>42.39879610600042</v>
+        <v>42.07943821781794</v>
       </c>
       <c r="D5">
-        <v>42.86179610600042</v>
+        <v>42.97043821781795</v>
       </c>
       <c r="E5">
-        <v>-19.516</v>
+        <v>-19.088</v>
       </c>
       <c r="F5">
-        <v>1.284</v>
+        <v>1.712</v>
       </c>
       <c r="G5">
         <v>0.821</v>
@@ -1697,28 +1697,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M5">
-        <v>0.06458519999999998</v>
+        <v>0.0861136</v>
       </c>
       <c r="N5">
-        <v>3.078081466666667</v>
+        <v>3.056553066666667</v>
       </c>
       <c r="O5">
-        <v>0.4617122200000001</v>
+        <v>0.45848296</v>
       </c>
       <c r="P5">
-        <v>2.616369246666667</v>
+        <v>2.598070106666667</v>
       </c>
       <c r="Q5">
-        <v>2.740369246666667</v>
+        <v>2.722070106666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07676356958334751</v>
+        <v>0.07703896547052572</v>
       </c>
       <c r="T5">
-        <v>0.5671086508754979</v>
+        <v>0.5721526232642072</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.65923875232512</v>
+        <v>36.49442906424382</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07566760685170468</v>
+        <v>0.07559190120756226</v>
       </c>
       <c r="C6">
-        <v>42.07943821781794</v>
+        <v>41.76063248110773</v>
       </c>
       <c r="D6">
-        <v>42.97043821781795</v>
+        <v>43.07963248110774</v>
       </c>
       <c r="E6">
-        <v>-19.088</v>
+        <v>-18.66</v>
       </c>
       <c r="F6">
-        <v>1.712</v>
+        <v>2.14</v>
       </c>
       <c r="G6">
         <v>0.821</v>
@@ -1779,28 +1779,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M6">
-        <v>0.0861136</v>
+        <v>0.107642</v>
       </c>
       <c r="N6">
-        <v>3.056553066666667</v>
+        <v>3.035024666666667</v>
       </c>
       <c r="O6">
-        <v>0.45848296</v>
+        <v>0.4552537</v>
       </c>
       <c r="P6">
-        <v>2.598070106666667</v>
+        <v>2.579770966666667</v>
       </c>
       <c r="Q6">
-        <v>2.722070106666667</v>
+        <v>2.703770966666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07703896547052572</v>
+        <v>0.07732015916585502</v>
       </c>
       <c r="T6">
-        <v>0.5721526232642072</v>
+        <v>0.5773027845453105</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.49442906424382</v>
+        <v>29.19554325139506</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07559190120756226</v>
+        <v>0.07551619556341986</v>
       </c>
       <c r="C7">
-        <v>41.76063248110773</v>
+        <v>41.44238311589003</v>
       </c>
       <c r="D7">
-        <v>43.07963248110774</v>
+        <v>43.18938311589003</v>
       </c>
       <c r="E7">
-        <v>-18.66</v>
+        <v>-18.232</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.568</v>
       </c>
       <c r="G7">
         <v>0.821</v>
@@ -1861,28 +1861,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M7">
-        <v>0.107642</v>
+        <v>0.1291704</v>
       </c>
       <c r="N7">
-        <v>3.035024666666667</v>
+        <v>3.013496266666667</v>
       </c>
       <c r="O7">
-        <v>0.4552537</v>
+        <v>0.45202444</v>
       </c>
       <c r="P7">
-        <v>2.579770966666667</v>
+        <v>2.561471826666667</v>
       </c>
       <c r="Q7">
-        <v>2.703770966666667</v>
+        <v>2.685471826666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07732015916585502</v>
+        <v>0.07760733570576581</v>
       </c>
       <c r="T7">
-        <v>0.5773027845453105</v>
+        <v>0.5825625237260116</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.19554325139506</v>
+        <v>24.32961937616255</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07551619556341985</v>
+        <v>0.07544048991927745</v>
       </c>
       <c r="C8">
-        <v>41.44238311589006</v>
+        <v>41.12469438529909</v>
       </c>
       <c r="D8">
-        <v>43.18938311589006</v>
+        <v>43.2996943852991</v>
       </c>
       <c r="E8">
-        <v>-18.232</v>
+        <v>-17.804</v>
       </c>
       <c r="F8">
-        <v>2.568</v>
+        <v>2.996</v>
       </c>
       <c r="G8">
         <v>0.821</v>
@@ -1943,28 +1943,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M8">
-        <v>0.1291704</v>
+        <v>0.1506988</v>
       </c>
       <c r="N8">
-        <v>3.013496266666667</v>
+        <v>2.991967866666667</v>
       </c>
       <c r="O8">
-        <v>0.45202444</v>
+        <v>0.4487951800000001</v>
       </c>
       <c r="P8">
-        <v>2.561471826666667</v>
+        <v>2.543172686666667</v>
       </c>
       <c r="Q8">
-        <v>2.685471826666667</v>
+        <v>2.667172686666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07760733570576581</v>
+        <v>0.07790068808524456</v>
       </c>
       <c r="T8">
-        <v>0.5825625237260116</v>
+        <v>0.5879353755772655</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.32961937616255</v>
+        <v>20.85395946528219</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07544048991927745</v>
+        <v>0.07536478427513504</v>
       </c>
       <c r="C9">
-        <v>41.12469438529909</v>
+        <v>40.807570596135</v>
       </c>
       <c r="D9">
-        <v>43.2996943852991</v>
+        <v>43.410570596135</v>
       </c>
       <c r="E9">
-        <v>-17.804</v>
+        <v>-17.376</v>
       </c>
       <c r="F9">
-        <v>2.996</v>
+        <v>3.424</v>
       </c>
       <c r="G9">
         <v>0.821</v>
@@ -2025,28 +2025,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M9">
-        <v>0.1506988</v>
+        <v>0.1722272</v>
       </c>
       <c r="N9">
-        <v>2.991967866666667</v>
+        <v>2.970439466666667</v>
       </c>
       <c r="O9">
-        <v>0.4487951800000001</v>
+        <v>0.44556592</v>
       </c>
       <c r="P9">
-        <v>2.543172686666667</v>
+        <v>2.524873546666667</v>
       </c>
       <c r="Q9">
-        <v>2.667172686666667</v>
+        <v>2.648873546666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07790068808524456</v>
+        <v>0.07820041769036418</v>
       </c>
       <c r="T9">
-        <v>0.5879353755772655</v>
+        <v>0.5934250285557205</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.85395946528219</v>
+        <v>18.24721453212191</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07536478427513504</v>
+        <v>0.07528907863099263</v>
       </c>
       <c r="C10">
-        <v>40.807570596135</v>
+        <v>40.49101609942436</v>
       </c>
       <c r="D10">
-        <v>43.410570596135</v>
+        <v>43.52201609942436</v>
       </c>
       <c r="E10">
-        <v>-17.376</v>
+        <v>-16.948</v>
       </c>
       <c r="F10">
-        <v>3.424</v>
+        <v>3.851999999999999</v>
       </c>
       <c r="G10">
         <v>0.821</v>
@@ -2107,28 +2107,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M10">
-        <v>0.1722272</v>
+        <v>0.1937556</v>
       </c>
       <c r="N10">
-        <v>2.970439466666667</v>
+        <v>2.948911066666667</v>
       </c>
       <c r="O10">
-        <v>0.44556592</v>
+        <v>0.44233666</v>
       </c>
       <c r="P10">
-        <v>2.524873546666667</v>
+        <v>2.506574406666667</v>
       </c>
       <c r="Q10">
-        <v>2.648873546666667</v>
+        <v>2.630574406666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07820041769036418</v>
+        <v>0.07850673475933255</v>
       </c>
       <c r="T10">
-        <v>0.5934250285557205</v>
+        <v>0.5990353332479877</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.24721453212191</v>
+        <v>16.21974625077504</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07528907863099263</v>
+        <v>0.07521337298685021</v>
       </c>
       <c r="C11">
-        <v>40.49101609942436</v>
+        <v>40.17503529098924</v>
       </c>
       <c r="D11">
-        <v>43.52201609942436</v>
+        <v>43.63403529098925</v>
       </c>
       <c r="E11">
-        <v>-16.948</v>
+        <v>-16.52</v>
       </c>
       <c r="F11">
-        <v>3.851999999999999</v>
+        <v>4.279999999999999</v>
       </c>
       <c r="G11">
         <v>0.821</v>
@@ -2189,28 +2189,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M11">
-        <v>0.1937556</v>
+        <v>0.2152839999999999</v>
       </c>
       <c r="N11">
-        <v>2.948911066666667</v>
+        <v>2.927382666666667</v>
       </c>
       <c r="O11">
-        <v>0.44233666</v>
+        <v>0.4391074</v>
       </c>
       <c r="P11">
-        <v>2.506574406666667</v>
+        <v>2.488275266666667</v>
       </c>
       <c r="Q11">
-        <v>2.630574406666667</v>
+        <v>2.612275266666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07850673475933255</v>
+        <v>0.07881985887427802</v>
       </c>
       <c r="T11">
-        <v>0.5990353332479877</v>
+        <v>0.604770311377861</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.21974625077504</v>
+        <v>14.59777162569753</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07521337298685021</v>
+        <v>0.0751376673427078</v>
       </c>
       <c r="C12">
-        <v>40.17503529098924</v>
+        <v>39.85963261202534</v>
       </c>
       <c r="D12">
-        <v>43.63403529098925</v>
+        <v>43.74663261202534</v>
       </c>
       <c r="E12">
-        <v>-16.52</v>
+        <v>-16.092</v>
       </c>
       <c r="F12">
-        <v>4.28</v>
+        <v>4.707999999999999</v>
       </c>
       <c r="G12">
         <v>0.821</v>
@@ -2271,28 +2271,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M12">
-        <v>0.215284</v>
+        <v>0.2368124</v>
       </c>
       <c r="N12">
-        <v>2.927382666666667</v>
+        <v>2.905854266666667</v>
       </c>
       <c r="O12">
-        <v>0.4391074</v>
+        <v>0.4358781400000001</v>
       </c>
       <c r="P12">
-        <v>2.488275266666667</v>
+        <v>2.469976126666667</v>
       </c>
       <c r="Q12">
-        <v>2.612275266666667</v>
+        <v>2.593976126666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07881985887427802</v>
+        <v>0.07914001948618854</v>
       </c>
       <c r="T12">
-        <v>0.604770311377861</v>
+        <v>0.610634165420765</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.59777162569753</v>
+        <v>13.27070147790685</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0751376673427078</v>
+        <v>0.0752149616985654</v>
       </c>
       <c r="C13">
-        <v>39.85963261202534</v>
+        <v>39.31667860245237</v>
       </c>
       <c r="D13">
-        <v>43.74663261202534</v>
+        <v>43.63167860245238</v>
       </c>
       <c r="E13">
-        <v>-16.092</v>
+        <v>-15.664</v>
       </c>
       <c r="F13">
-        <v>4.707999999999999</v>
+        <v>5.135999999999999</v>
       </c>
       <c r="G13">
         <v>0.821</v>
@@ -2353,45 +2353,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M13">
-        <v>0.2368124</v>
+        <v>0.2660448</v>
       </c>
       <c r="N13">
-        <v>2.905854266666667</v>
+        <v>2.876621866666667</v>
       </c>
       <c r="O13">
-        <v>0.4358781400000001</v>
+        <v>0.43149328</v>
       </c>
       <c r="P13">
-        <v>2.469976126666667</v>
+        <v>2.445128586666667</v>
       </c>
       <c r="Q13">
-        <v>2.593976126666667</v>
+        <v>2.569128586666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07914001948618854</v>
+        <v>0.07946745647564249</v>
       </c>
       <c r="T13">
-        <v>0.610634165420765</v>
+        <v>0.616631288873735</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.27070147790685</v>
+        <v>11.81254685927583</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0752149616985654</v>
+        <v>0.07515200605442299</v>
       </c>
       <c r="C14">
-        <v>39.31667860245237</v>
+        <v>38.98226199931931</v>
       </c>
       <c r="D14">
-        <v>43.63167860245238</v>
+        <v>43.72526199931932</v>
       </c>
       <c r="E14">
-        <v>-15.664</v>
+        <v>-15.236</v>
       </c>
       <c r="F14">
-        <v>5.135999999999999</v>
+        <v>5.564</v>
       </c>
       <c r="G14">
         <v>0.821</v>
@@ -2435,28 +2435,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M14">
-        <v>0.2660448</v>
+        <v>0.2882152</v>
       </c>
       <c r="N14">
-        <v>2.876621866666667</v>
+        <v>2.854451466666667</v>
       </c>
       <c r="O14">
-        <v>0.43149328</v>
+        <v>0.4281677200000001</v>
       </c>
       <c r="P14">
-        <v>2.445128586666667</v>
+        <v>2.426283746666667</v>
       </c>
       <c r="Q14">
-        <v>2.569128586666667</v>
+        <v>2.550283746666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07946745647564249</v>
+        <v>0.07980242075221032</v>
       </c>
       <c r="T14">
-        <v>0.616631288873735</v>
+        <v>0.6227662772336698</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.81254685927583</v>
+        <v>10.90388940856231</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07515200605442299</v>
+        <v>0.07508905041028056</v>
       </c>
       <c r="C15">
-        <v>38.98226199931931</v>
+        <v>38.64824770373455</v>
       </c>
       <c r="D15">
-        <v>43.72526199931932</v>
+        <v>43.81924770373455</v>
       </c>
       <c r="E15">
-        <v>-15.236</v>
+        <v>-14.808</v>
       </c>
       <c r="F15">
-        <v>5.564</v>
+        <v>5.992</v>
       </c>
       <c r="G15">
         <v>0.821</v>
@@ -2517,28 +2517,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M15">
-        <v>0.2882152</v>
+        <v>0.3103856</v>
       </c>
       <c r="N15">
-        <v>2.854451466666667</v>
+        <v>2.832281066666667</v>
       </c>
       <c r="O15">
-        <v>0.4281677200000001</v>
+        <v>0.42484216</v>
       </c>
       <c r="P15">
-        <v>2.426283746666667</v>
+        <v>2.407438906666667</v>
       </c>
       <c r="Q15">
-        <v>2.550283746666667</v>
+        <v>2.531438906666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07980242075221032</v>
+        <v>0.08014517489567508</v>
       </c>
       <c r="T15">
-        <v>0.6227662772336698</v>
+        <v>0.6290439397415101</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.90388940856231</v>
+        <v>10.12504016509357</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07508905041028056</v>
+        <v>0.07524284476613814</v>
       </c>
       <c r="C16">
-        <v>38.64824770373455</v>
+        <v>37.99135837499311</v>
       </c>
       <c r="D16">
-        <v>43.81924770373455</v>
+        <v>43.59035837499312</v>
       </c>
       <c r="E16">
-        <v>-14.808</v>
+        <v>-14.38</v>
       </c>
       <c r="F16">
-        <v>5.992</v>
+        <v>6.420000000000001</v>
       </c>
       <c r="G16">
         <v>0.821</v>
@@ -2599,45 +2599,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M16">
-        <v>0.3103856</v>
+        <v>0.3434700000000001</v>
       </c>
       <c r="N16">
-        <v>2.832281066666667</v>
+        <v>2.799196666666667</v>
       </c>
       <c r="O16">
-        <v>0.42484216</v>
+        <v>0.4198795</v>
       </c>
       <c r="P16">
-        <v>2.407438906666667</v>
+        <v>2.379317166666667</v>
       </c>
       <c r="Q16">
-        <v>2.531438906666667</v>
+        <v>2.503317166666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08014517489567508</v>
+        <v>0.08049599384251546</v>
       </c>
       <c r="T16">
-        <v>0.6290439397415101</v>
+        <v>0.6354693119554172</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.12504016509357</v>
+        <v>9.149755922399821</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07524284476613814</v>
+        <v>0.07519433912199575</v>
       </c>
       <c r="C17">
-        <v>37.99135837499311</v>
+        <v>37.63528985821517</v>
       </c>
       <c r="D17">
-        <v>43.59035837499312</v>
+        <v>43.66228985821517</v>
       </c>
       <c r="E17">
-        <v>-14.38</v>
+        <v>-13.952</v>
       </c>
       <c r="F17">
-        <v>6.419999999999999</v>
+        <v>6.848</v>
       </c>
       <c r="G17">
         <v>0.821</v>
@@ -2681,28 +2681,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M17">
-        <v>0.3434699999999999</v>
+        <v>0.366368</v>
       </c>
       <c r="N17">
-        <v>2.799196666666667</v>
+        <v>2.776298666666667</v>
       </c>
       <c r="O17">
-        <v>0.4198795</v>
+        <v>0.4164448</v>
       </c>
       <c r="P17">
-        <v>2.379317166666667</v>
+        <v>2.359853866666667</v>
       </c>
       <c r="Q17">
-        <v>2.503317166666667</v>
+        <v>2.483853866666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08049599384251546</v>
+        <v>0.0808551656214235</v>
       </c>
       <c r="T17">
-        <v>0.6354693119554172</v>
+        <v>0.6420476692220366</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.149755922399823</v>
+        <v>8.577896177249833</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07519433912199575</v>
+        <v>0.07514583347785332</v>
       </c>
       <c r="C18">
-        <v>37.63528985821517</v>
+        <v>37.27945913212261</v>
       </c>
       <c r="D18">
-        <v>43.66228985821517</v>
+        <v>43.73445913212262</v>
       </c>
       <c r="E18">
-        <v>-13.952</v>
+        <v>-13.524</v>
       </c>
       <c r="F18">
-        <v>6.848</v>
+        <v>7.276</v>
       </c>
       <c r="G18">
         <v>0.821</v>
@@ -2763,28 +2763,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M18">
-        <v>0.366368</v>
+        <v>0.389266</v>
       </c>
       <c r="N18">
-        <v>2.776298666666667</v>
+        <v>2.753400666666667</v>
       </c>
       <c r="O18">
-        <v>0.4164448</v>
+        <v>0.4130101</v>
       </c>
       <c r="P18">
-        <v>2.359853866666667</v>
+        <v>2.340390566666667</v>
       </c>
       <c r="Q18">
-        <v>2.483853866666667</v>
+        <v>2.464390566666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0808551656214235</v>
+        <v>0.08122299214199197</v>
       </c>
       <c r="T18">
-        <v>0.6420476692220366</v>
+        <v>0.6487845411215863</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.577896177249833</v>
+        <v>8.073314049176314</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07514583347785332</v>
+        <v>0.07509732783371091</v>
       </c>
       <c r="C19">
-        <v>37.27945913212261</v>
+        <v>36.92386737779827</v>
       </c>
       <c r="D19">
-        <v>43.73445913212262</v>
+        <v>43.80686737779828</v>
       </c>
       <c r="E19">
-        <v>-13.524</v>
+        <v>-13.096</v>
       </c>
       <c r="F19">
-        <v>7.276</v>
+        <v>7.704000000000001</v>
       </c>
       <c r="G19">
         <v>0.821</v>
@@ -2845,28 +2845,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M19">
-        <v>0.389266</v>
+        <v>0.412164</v>
       </c>
       <c r="N19">
-        <v>2.753400666666667</v>
+        <v>2.730502666666667</v>
       </c>
       <c r="O19">
-        <v>0.4130101</v>
+        <v>0.4095754</v>
       </c>
       <c r="P19">
-        <v>2.340390566666667</v>
+        <v>2.320927266666667</v>
       </c>
       <c r="Q19">
-        <v>2.464390566666667</v>
+        <v>2.444927266666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08122299214199197</v>
+        <v>0.08159979004111087</v>
       </c>
       <c r="T19">
-        <v>0.6487845411215863</v>
+        <v>0.6556857269699057</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.073314049176314</v>
+        <v>7.624796601999851</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07509732783371091</v>
+        <v>0.07517802218956851</v>
       </c>
       <c r="C20">
-        <v>36.92386737779827</v>
+        <v>36.37554045713696</v>
       </c>
       <c r="D20">
-        <v>43.80686737779828</v>
+        <v>43.68654045713696</v>
       </c>
       <c r="E20">
-        <v>-13.096</v>
+        <v>-12.668</v>
       </c>
       <c r="F20">
-        <v>7.703999999999999</v>
+        <v>8.132</v>
       </c>
       <c r="G20">
         <v>0.821</v>
@@ -2927,45 +2927,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M20">
-        <v>0.4121639999999999</v>
+        <v>0.4415676</v>
       </c>
       <c r="N20">
-        <v>2.730502666666667</v>
+        <v>2.701099066666667</v>
       </c>
       <c r="O20">
-        <v>0.4095754000000001</v>
+        <v>0.40516486</v>
       </c>
       <c r="P20">
-        <v>2.320927266666667</v>
+        <v>2.295934206666667</v>
       </c>
       <c r="Q20">
-        <v>2.444927266666667</v>
+        <v>2.419934206666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08159979004111087</v>
+        <v>0.08198589159205988</v>
       </c>
       <c r="T20">
-        <v>0.6556857269699057</v>
+        <v>0.6627573124688008</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.624796601999853</v>
+        <v>7.11706806990972</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07517802218956851</v>
+        <v>0.0751363165454261</v>
       </c>
       <c r="C21">
-        <v>36.37554045713696</v>
+        <v>36.00964693554562</v>
       </c>
       <c r="D21">
-        <v>43.68654045713696</v>
+        <v>43.74864693554562</v>
       </c>
       <c r="E21">
-        <v>-12.668</v>
+        <v>-12.24</v>
       </c>
       <c r="F21">
-        <v>8.132</v>
+        <v>8.56</v>
       </c>
       <c r="G21">
         <v>0.821</v>
@@ -3009,28 +3009,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M21">
-        <v>0.4415676</v>
+        <v>0.4648080000000001</v>
       </c>
       <c r="N21">
-        <v>2.701099066666667</v>
+        <v>2.677858666666667</v>
       </c>
       <c r="O21">
-        <v>0.40516486</v>
+        <v>0.4016788</v>
       </c>
       <c r="P21">
-        <v>2.295934206666667</v>
+        <v>2.276179866666667</v>
       </c>
       <c r="Q21">
-        <v>2.419934206666667</v>
+        <v>2.400179866666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08198589159205988</v>
+        <v>0.08238164568178262</v>
       </c>
       <c r="T21">
-        <v>0.6627573124688008</v>
+        <v>0.6700056876051682</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.11706806990972</v>
+        <v>6.761214666414232</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0751363165454261</v>
+        <v>0.07509461090128369</v>
       </c>
       <c r="C22">
-        <v>36.00964693554562</v>
+        <v>35.64393025130477</v>
       </c>
       <c r="D22">
-        <v>43.74864693554562</v>
+        <v>43.81093025130477</v>
       </c>
       <c r="E22">
-        <v>-12.24</v>
+        <v>-11.812</v>
       </c>
       <c r="F22">
-        <v>8.56</v>
+        <v>8.988</v>
       </c>
       <c r="G22">
         <v>0.821</v>
@@ -3091,28 +3091,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M22">
-        <v>0.4648080000000001</v>
+        <v>0.4880484</v>
       </c>
       <c r="N22">
-        <v>2.677858666666667</v>
+        <v>2.654618266666667</v>
       </c>
       <c r="O22">
-        <v>0.4016788</v>
+        <v>0.39819274</v>
       </c>
       <c r="P22">
-        <v>2.276179866666667</v>
+        <v>2.256425526666667</v>
       </c>
       <c r="Q22">
-        <v>2.400179866666667</v>
+        <v>2.380425526666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08238164568178262</v>
+        <v>0.08278741886238442</v>
       </c>
       <c r="T22">
-        <v>0.6700056876051682</v>
+        <v>0.6774375659095451</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.761214666414232</v>
+        <v>6.439252063251651</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07509461090128368</v>
+        <v>0.07505290525714127</v>
       </c>
       <c r="C23">
-        <v>35.64393025130479</v>
+        <v>35.27839116076139</v>
       </c>
       <c r="D23">
-        <v>43.81093025130479</v>
+        <v>43.87339116076139</v>
       </c>
       <c r="E23">
-        <v>-11.812</v>
+        <v>-11.384</v>
       </c>
       <c r="F23">
-        <v>8.988</v>
+        <v>9.415999999999999</v>
       </c>
       <c r="G23">
         <v>0.821</v>
@@ -3173,28 +3173,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M23">
-        <v>0.4880484</v>
+        <v>0.5112888</v>
       </c>
       <c r="N23">
-        <v>2.654618266666667</v>
+        <v>2.631377866666667</v>
       </c>
       <c r="O23">
-        <v>0.39819274</v>
+        <v>0.39470668</v>
       </c>
       <c r="P23">
-        <v>2.256425526666667</v>
+        <v>2.236671186666667</v>
       </c>
       <c r="Q23">
-        <v>2.380425526666667</v>
+        <v>2.360671186666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08278741886238442</v>
+        <v>0.08320359648351446</v>
       </c>
       <c r="T23">
-        <v>0.677437565909545</v>
+        <v>0.6850600051960853</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.439252063251651</v>
+        <v>6.146558787649303</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07505290525714127</v>
+        <v>0.07520669961299886</v>
       </c>
       <c r="C24">
-        <v>35.27839116076139</v>
+        <v>34.62093732807508</v>
       </c>
       <c r="D24">
-        <v>43.87339116076139</v>
+        <v>43.64393732807508</v>
       </c>
       <c r="E24">
-        <v>-11.384</v>
+        <v>-10.956</v>
       </c>
       <c r="F24">
-        <v>9.415999999999999</v>
+        <v>9.843999999999999</v>
       </c>
       <c r="G24">
         <v>0.821</v>
@@ -3255,45 +3255,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M24">
-        <v>0.5112888</v>
+        <v>0.5443732</v>
       </c>
       <c r="N24">
-        <v>2.631377866666667</v>
+        <v>2.598293466666667</v>
       </c>
       <c r="O24">
-        <v>0.39470668</v>
+        <v>0.38974402</v>
       </c>
       <c r="P24">
-        <v>2.236671186666667</v>
+        <v>2.208549446666667</v>
       </c>
       <c r="Q24">
-        <v>2.360671186666667</v>
+        <v>2.332549446666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08320359648351446</v>
+        <v>0.08363058391298553</v>
       </c>
       <c r="T24">
-        <v>0.6850600051960853</v>
+        <v>0.6928804299186396</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.146558787649303</v>
+        <v>5.773000336288905</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07520669961299886</v>
+        <v>0.07517349396885646</v>
       </c>
       <c r="C25">
-        <v>34.62093732807508</v>
+        <v>34.24227517849988</v>
       </c>
       <c r="D25">
-        <v>43.64393732807508</v>
+        <v>43.69327517849988</v>
       </c>
       <c r="E25">
-        <v>-10.956</v>
+        <v>-10.528</v>
       </c>
       <c r="F25">
-        <v>9.843999999999999</v>
+        <v>10.272</v>
       </c>
       <c r="G25">
         <v>0.821</v>
@@ -3337,28 +3337,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M25">
-        <v>0.5443732</v>
+        <v>0.5680416</v>
       </c>
       <c r="N25">
-        <v>2.598293466666667</v>
+        <v>2.574625066666667</v>
       </c>
       <c r="O25">
-        <v>0.38974402</v>
+        <v>0.3861937600000001</v>
       </c>
       <c r="P25">
-        <v>2.208549446666667</v>
+        <v>2.188431306666667</v>
       </c>
       <c r="Q25">
-        <v>2.332549446666667</v>
+        <v>2.312431306666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08363058391298553</v>
+        <v>0.08406880785375849</v>
       </c>
       <c r="T25">
-        <v>0.6928804299186396</v>
+        <v>0.7009066552917875</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.773000336288905</v>
+        <v>5.5324586556102</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07517349396885646</v>
+        <v>0.07514028832471405</v>
       </c>
       <c r="C26">
-        <v>34.24227517849988</v>
+        <v>33.86372470438513</v>
       </c>
       <c r="D26">
-        <v>43.69327517849988</v>
+        <v>43.74272470438514</v>
       </c>
       <c r="E26">
-        <v>-10.528</v>
+        <v>-10.1</v>
       </c>
       <c r="F26">
-        <v>10.272</v>
+        <v>10.7</v>
       </c>
       <c r="G26">
         <v>0.821</v>
@@ -3419,28 +3419,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M26">
-        <v>0.5680415999999999</v>
+        <v>0.59171</v>
       </c>
       <c r="N26">
-        <v>2.574625066666667</v>
+        <v>2.550956666666667</v>
       </c>
       <c r="O26">
-        <v>0.3861937600000001</v>
+        <v>0.3826435</v>
       </c>
       <c r="P26">
-        <v>2.188431306666667</v>
+        <v>2.168313166666667</v>
       </c>
       <c r="Q26">
-        <v>2.312431306666667</v>
+        <v>2.292313166666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08406880785375849</v>
+        <v>0.08451871776628539</v>
       </c>
       <c r="T26">
-        <v>0.7009066552917875</v>
+        <v>0.7091469133415526</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.532458655610201</v>
+        <v>5.311160309385793</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07514028832471405</v>
+        <v>0.07510708268057163</v>
       </c>
       <c r="C27">
-        <v>33.86372470438513</v>
+        <v>33.48528628532394</v>
       </c>
       <c r="D27">
-        <v>43.74272470438514</v>
+        <v>43.79228628532395</v>
       </c>
       <c r="E27">
-        <v>-10.1</v>
+        <v>-9.672000000000001</v>
       </c>
       <c r="F27">
-        <v>10.7</v>
+        <v>11.128</v>
       </c>
       <c r="G27">
         <v>0.821</v>
@@ -3501,28 +3501,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M27">
-        <v>0.59171</v>
+        <v>0.6153784</v>
       </c>
       <c r="N27">
-        <v>2.550956666666667</v>
+        <v>2.527288266666667</v>
       </c>
       <c r="O27">
-        <v>0.3826435</v>
+        <v>0.3790932400000001</v>
       </c>
       <c r="P27">
-        <v>2.168313166666667</v>
+        <v>2.148195026666667</v>
       </c>
       <c r="Q27">
-        <v>2.292313166666667</v>
+        <v>2.272195026666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08451871776628539</v>
+        <v>0.08498078740617787</v>
       </c>
       <c r="T27">
-        <v>0.7091469133415526</v>
+        <v>0.7176098810683385</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.311160309385793</v>
+        <v>5.106884912870954</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07510708268057163</v>
+        <v>0.07507387703642922</v>
       </c>
       <c r="C28">
-        <v>33.48528628532394</v>
+        <v>33.10696030263171</v>
       </c>
       <c r="D28">
-        <v>43.79228628532395</v>
+        <v>43.84196030263171</v>
       </c>
       <c r="E28">
-        <v>-9.672000000000001</v>
+        <v>-9.244000000000002</v>
       </c>
       <c r="F28">
-        <v>11.128</v>
+        <v>11.556</v>
       </c>
       <c r="G28">
         <v>0.821</v>
@@ -3583,28 +3583,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M28">
-        <v>0.6153784</v>
+        <v>0.6390468</v>
       </c>
       <c r="N28">
-        <v>2.527288266666667</v>
+        <v>2.503619866666667</v>
       </c>
       <c r="O28">
-        <v>0.3790932400000001</v>
+        <v>0.37554298</v>
       </c>
       <c r="P28">
-        <v>2.148195026666667</v>
+        <v>2.128076886666667</v>
       </c>
       <c r="Q28">
-        <v>2.272195026666667</v>
+        <v>2.252076886666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08498078740617787</v>
+        <v>0.08545551648825921</v>
       </c>
       <c r="T28">
-        <v>0.7176098810683385</v>
+        <v>0.7263047109246253</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.106884912870954</v>
+        <v>4.917741027209066</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07507387703642922</v>
+        <v>0.0750406713922868</v>
       </c>
       <c r="C29">
-        <v>33.10696030263171</v>
+        <v>32.72874713935596</v>
       </c>
       <c r="D29">
-        <v>43.84196030263171</v>
+        <v>43.89174713935596</v>
       </c>
       <c r="E29">
-        <v>-9.244000000000002</v>
+        <v>-8.816000000000001</v>
       </c>
       <c r="F29">
-        <v>11.556</v>
+        <v>11.984</v>
       </c>
       <c r="G29">
         <v>0.821</v>
@@ -3665,28 +3665,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M29">
-        <v>0.6390468</v>
+        <v>0.6627152000000001</v>
       </c>
       <c r="N29">
-        <v>2.503619866666667</v>
+        <v>2.479951466666667</v>
       </c>
       <c r="O29">
-        <v>0.37554298</v>
+        <v>0.37199272</v>
       </c>
       <c r="P29">
-        <v>2.128076886666667</v>
+        <v>2.107958746666667</v>
       </c>
       <c r="Q29">
-        <v>2.252076886666667</v>
+        <v>2.231958746666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08545551648825921</v>
+        <v>0.08594343248928724</v>
       </c>
       <c r="T29">
-        <v>0.7263047109246253</v>
+        <v>0.7352410638324757</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.917741027209066</v>
+        <v>4.742107419094457</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0750406713922868</v>
+        <v>0.07500746574814439</v>
       </c>
       <c r="C30">
-        <v>32.72874713935596</v>
+        <v>32.35064718028611</v>
       </c>
       <c r="D30">
-        <v>43.89174713935596</v>
+        <v>43.94164718028611</v>
       </c>
       <c r="E30">
-        <v>-8.816000000000001</v>
+        <v>-8.388</v>
       </c>
       <c r="F30">
-        <v>11.984</v>
+        <v>12.412</v>
       </c>
       <c r="G30">
         <v>0.821</v>
@@ -3747,28 +3747,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M30">
-        <v>0.6627152000000001</v>
+        <v>0.6863836000000001</v>
       </c>
       <c r="N30">
-        <v>2.479951466666667</v>
+        <v>2.456283066666667</v>
       </c>
       <c r="O30">
-        <v>0.37199272</v>
+        <v>0.36844246</v>
       </c>
       <c r="P30">
-        <v>2.107958746666667</v>
+        <v>2.087840606666667</v>
       </c>
       <c r="Q30">
-        <v>2.231958746666667</v>
+        <v>2.211840606666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08594343248928724</v>
+        <v>0.08644509260302027</v>
       </c>
       <c r="T30">
-        <v>0.7352410638324757</v>
+        <v>0.7444291449912513</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.742107419094457</v>
+        <v>4.578586473608441</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07500746574814439</v>
+        <v>0.07561176010400197</v>
       </c>
       <c r="C31">
-        <v>32.35064718028611</v>
+        <v>31.03193528385677</v>
       </c>
       <c r="D31">
-        <v>43.94164718028611</v>
+        <v>43.05093528385677</v>
       </c>
       <c r="E31">
-        <v>-8.388000000000002</v>
+        <v>-7.960000000000003</v>
       </c>
       <c r="F31">
-        <v>12.412</v>
+        <v>12.84</v>
       </c>
       <c r="G31">
         <v>0.821</v>
@@ -3829,45 +3829,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M31">
-        <v>0.6863836</v>
+        <v>0.7421519999999999</v>
       </c>
       <c r="N31">
-        <v>2.456283066666667</v>
+        <v>2.400514666666667</v>
       </c>
       <c r="O31">
-        <v>0.36844246</v>
+        <v>0.3600772</v>
       </c>
       <c r="P31">
-        <v>2.087840606666667</v>
+        <v>2.040437466666667</v>
       </c>
       <c r="Q31">
-        <v>2.211840606666667</v>
+        <v>2.164437466666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08644509260302027</v>
+        <v>0.08696108586285997</v>
       </c>
       <c r="T31">
-        <v>0.7444291449912513</v>
+        <v>0.7538797427545635</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.578586473608441</v>
+        <v>4.234532368930714</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07561176010400197</v>
+        <v>0.07559980445985957</v>
       </c>
       <c r="C32">
-        <v>31.03193528385677</v>
+        <v>30.62120726505196</v>
       </c>
       <c r="D32">
-        <v>43.05093528385677</v>
+        <v>43.06820726505197</v>
       </c>
       <c r="E32">
-        <v>-7.960000000000003</v>
+        <v>-7.532000000000002</v>
       </c>
       <c r="F32">
-        <v>12.84</v>
+        <v>13.268</v>
       </c>
       <c r="G32">
         <v>0.821</v>
@@ -3911,28 +3911,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M32">
-        <v>0.7421519999999999</v>
+        <v>0.7668904</v>
       </c>
       <c r="N32">
-        <v>2.400514666666667</v>
+        <v>2.375776266666667</v>
       </c>
       <c r="O32">
-        <v>0.3600772</v>
+        <v>0.3563664400000001</v>
       </c>
       <c r="P32">
-        <v>2.040437466666667</v>
+        <v>2.019409826666667</v>
       </c>
       <c r="Q32">
-        <v>2.164437466666667</v>
+        <v>2.143409826666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08696108586285997</v>
+        <v>0.08749203544907184</v>
       </c>
       <c r="T32">
-        <v>0.7538797427545635</v>
+        <v>0.7636042708878267</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.234532368930714</v>
+        <v>4.09793455057811</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07559980445985957</v>
+        <v>0.07653984881571715</v>
       </c>
       <c r="C33">
-        <v>30.62120726505196</v>
+        <v>28.8761537753251</v>
       </c>
       <c r="D33">
-        <v>43.06820726505197</v>
+        <v>41.7511537753251</v>
       </c>
       <c r="E33">
-        <v>-7.532000000000002</v>
+        <v>-7.104000000000001</v>
       </c>
       <c r="F33">
-        <v>13.268</v>
+        <v>13.696</v>
       </c>
       <c r="G33">
         <v>0.821</v>
@@ -3993,45 +3993,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M33">
-        <v>0.7668904</v>
+        <v>0.8395648</v>
       </c>
       <c r="N33">
-        <v>2.375776266666667</v>
+        <v>2.303101866666667</v>
       </c>
       <c r="O33">
-        <v>0.3563664400000001</v>
+        <v>0.34546528</v>
       </c>
       <c r="P33">
-        <v>2.019409826666667</v>
+        <v>1.957636586666667</v>
       </c>
       <c r="Q33">
-        <v>2.143409826666667</v>
+        <v>2.081636586666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08749203544907184</v>
+        <v>0.08803860119958407</v>
       </c>
       <c r="T33">
-        <v>0.7636042708878267</v>
+        <v>0.773614814554421</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.09793455057811</v>
+        <v>3.743209180121257</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07653984881571715</v>
+        <v>0.07655764317157474</v>
       </c>
       <c r="C34">
-        <v>28.8761537753251</v>
+        <v>28.42399929497046</v>
       </c>
       <c r="D34">
-        <v>41.7511537753251</v>
+        <v>41.72699929497046</v>
       </c>
       <c r="E34">
-        <v>-7.104000000000001</v>
+        <v>-6.676</v>
       </c>
       <c r="F34">
-        <v>13.696</v>
+        <v>14.124</v>
       </c>
       <c r="G34">
         <v>0.821</v>
@@ -4075,28 +4075,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M34">
-        <v>0.8395648</v>
+        <v>0.8658012</v>
       </c>
       <c r="N34">
-        <v>2.303101866666667</v>
+        <v>2.276865466666667</v>
       </c>
       <c r="O34">
-        <v>0.34546528</v>
+        <v>0.34152982</v>
       </c>
       <c r="P34">
-        <v>1.957636586666667</v>
+        <v>1.935335646666667</v>
       </c>
       <c r="Q34">
-        <v>2.081636586666667</v>
+        <v>2.059335646666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08803860119958407</v>
+        <v>0.08860148234563395</v>
       </c>
       <c r="T34">
-        <v>0.773614814554421</v>
+        <v>0.7839241804200184</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.743209180121257</v>
+        <v>3.629778598905461</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07655764317157474</v>
+        <v>0.07657543752743234</v>
       </c>
       <c r="C35">
-        <v>28.42399929497046</v>
+        <v>27.97187274685353</v>
       </c>
       <c r="D35">
-        <v>41.72699929497046</v>
+        <v>41.70287274685354</v>
       </c>
       <c r="E35">
-        <v>-6.676</v>
+        <v>-6.248000000000001</v>
       </c>
       <c r="F35">
-        <v>14.124</v>
+        <v>14.552</v>
       </c>
       <c r="G35">
         <v>0.821</v>
@@ -4157,28 +4157,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M35">
-        <v>0.8658012</v>
+        <v>0.8920376</v>
       </c>
       <c r="N35">
-        <v>2.276865466666667</v>
+        <v>2.250629066666667</v>
       </c>
       <c r="O35">
-        <v>0.34152982</v>
+        <v>0.33759436</v>
       </c>
       <c r="P35">
-        <v>1.935335646666667</v>
+        <v>1.913034706666667</v>
       </c>
       <c r="Q35">
-        <v>2.059335646666667</v>
+        <v>2.037034706666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08860148234563395</v>
+        <v>0.08918142049610961</v>
       </c>
       <c r="T35">
-        <v>0.7839241804200184</v>
+        <v>0.7945459513118459</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.629778598905461</v>
+        <v>3.523020404820006</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07657543752743234</v>
+        <v>0.07742623188328993</v>
       </c>
       <c r="C36">
-        <v>27.97187274685353</v>
+        <v>26.42200122934226</v>
       </c>
       <c r="D36">
-        <v>41.70287274685354</v>
+        <v>40.58100122934226</v>
       </c>
       <c r="E36">
-        <v>-6.248000000000001</v>
+        <v>-5.82</v>
       </c>
       <c r="F36">
-        <v>14.552</v>
+        <v>14.98</v>
       </c>
       <c r="G36">
         <v>0.821</v>
@@ -4239,45 +4239,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M36">
-        <v>0.8920376</v>
+        <v>0.9602180000000001</v>
       </c>
       <c r="N36">
-        <v>2.250629066666667</v>
+        <v>2.182448666666667</v>
       </c>
       <c r="O36">
-        <v>0.33759436</v>
+        <v>0.3273673</v>
       </c>
       <c r="P36">
-        <v>1.913034706666667</v>
+        <v>1.855081366666667</v>
       </c>
       <c r="Q36">
-        <v>2.037034706666667</v>
+        <v>1.979081366666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08918142049610961</v>
+        <v>0.08977920289736913</v>
       </c>
       <c r="T36">
-        <v>0.7945459513118459</v>
+        <v>0.8054945459234221</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.523020404820006</v>
+        <v>3.272867897359419</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07742623188328993</v>
+        <v>0.07746782623914751</v>
       </c>
       <c r="C37">
-        <v>26.42200122934226</v>
+        <v>25.9406997935745</v>
       </c>
       <c r="D37">
-        <v>40.58100122934226</v>
+        <v>40.52769979357451</v>
       </c>
       <c r="E37">
-        <v>-5.82</v>
+        <v>-5.391999999999999</v>
       </c>
       <c r="F37">
-        <v>14.98</v>
+        <v>15.408</v>
       </c>
       <c r="G37">
         <v>0.821</v>
@@ -4321,28 +4321,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M37">
-        <v>0.9602180000000001</v>
+        <v>0.9876528000000001</v>
       </c>
       <c r="N37">
-        <v>2.182448666666667</v>
+        <v>2.155013866666667</v>
       </c>
       <c r="O37">
-        <v>0.3273673</v>
+        <v>0.32325208</v>
       </c>
       <c r="P37">
-        <v>1.855081366666667</v>
+        <v>1.831761786666667</v>
       </c>
       <c r="Q37">
-        <v>1.979081366666667</v>
+        <v>1.955761786666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08977920289736913</v>
+        <v>0.090395665998668</v>
       </c>
       <c r="T37">
-        <v>0.8054945459234221</v>
+        <v>0.8167852841166099</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.272867897359419</v>
+        <v>3.181954900210546</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07746782623914751</v>
+        <v>0.0775094205950051</v>
       </c>
       <c r="C38">
-        <v>25.94069979357451</v>
+        <v>25.4595381925212</v>
       </c>
       <c r="D38">
-        <v>40.52769979357451</v>
+        <v>40.4745381925212</v>
       </c>
       <c r="E38">
-        <v>-5.392000000000003</v>
+        <v>-4.964000000000002</v>
       </c>
       <c r="F38">
-        <v>15.408</v>
+        <v>15.836</v>
       </c>
       <c r="G38">
         <v>0.821</v>
@@ -4403,28 +4403,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M38">
-        <v>0.9876527999999999</v>
+        <v>1.0150876</v>
       </c>
       <c r="N38">
-        <v>2.155013866666667</v>
+        <v>2.127579066666667</v>
       </c>
       <c r="O38">
-        <v>0.3232520800000001</v>
+        <v>0.31913686</v>
       </c>
       <c r="P38">
-        <v>1.831761786666667</v>
+        <v>1.808442206666667</v>
       </c>
       <c r="Q38">
-        <v>1.955761786666667</v>
+        <v>1.932442206666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09039566599866798</v>
+        <v>0.09103169935715096</v>
       </c>
       <c r="T38">
-        <v>0.8167852841166097</v>
+        <v>0.8284344584429146</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.181954900210547</v>
+        <v>3.095956119123775</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0775094205950051</v>
+        <v>0.0775510149508627</v>
       </c>
       <c r="C39">
-        <v>25.4595381925212</v>
+        <v>24.97851587662493</v>
       </c>
       <c r="D39">
-        <v>40.4745381925212</v>
+        <v>40.42151587662493</v>
       </c>
       <c r="E39">
-        <v>-4.964000000000002</v>
+        <v>-4.536000000000001</v>
       </c>
       <c r="F39">
-        <v>15.836</v>
+        <v>16.264</v>
       </c>
       <c r="G39">
         <v>0.821</v>
@@ -4485,28 +4485,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M39">
-        <v>1.0150876</v>
+        <v>1.0425224</v>
       </c>
       <c r="N39">
-        <v>2.127579066666667</v>
+        <v>2.100144266666667</v>
       </c>
       <c r="O39">
-        <v>0.31913686</v>
+        <v>0.31502164</v>
       </c>
       <c r="P39">
-        <v>1.808442206666667</v>
+        <v>1.785122626666667</v>
       </c>
       <c r="Q39">
-        <v>1.932442206666667</v>
+        <v>1.909122626666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09103169935715096</v>
+        <v>0.09168824992074628</v>
       </c>
       <c r="T39">
-        <v>0.8284344584429146</v>
+        <v>0.8404594125861972</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.095956119123775</v>
+        <v>3.014483589673149</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0775510149508627</v>
+        <v>0.08017830930672029</v>
       </c>
       <c r="C40">
-        <v>24.97851587662493</v>
+        <v>21.46138140027926</v>
       </c>
       <c r="D40">
-        <v>40.42151587662493</v>
+        <v>37.33238140027926</v>
       </c>
       <c r="E40">
-        <v>-4.536000000000001</v>
+        <v>-4.108000000000001</v>
       </c>
       <c r="F40">
-        <v>16.264</v>
+        <v>16.692</v>
       </c>
       <c r="G40">
         <v>0.821</v>
@@ -4567,45 +4567,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M40">
-        <v>1.0425224</v>
+        <v>1.2001548</v>
       </c>
       <c r="N40">
-        <v>2.100144266666667</v>
+        <v>1.942511866666667</v>
       </c>
       <c r="O40">
-        <v>0.31502164</v>
+        <v>0.29137678</v>
       </c>
       <c r="P40">
-        <v>1.785122626666667</v>
+        <v>1.651135086666667</v>
       </c>
       <c r="Q40">
-        <v>1.909122626666667</v>
+        <v>1.775135086666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09168824992074628</v>
+        <v>0.09236632673232834</v>
       </c>
       <c r="T40">
-        <v>0.8404594125861972</v>
+        <v>0.8528786275210626</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.014483589673149</v>
+        <v>2.618551095797531</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08017830930672029</v>
+        <v>0.08028620366257788</v>
       </c>
       <c r="C41">
-        <v>21.46138140027926</v>
+        <v>20.91658242515217</v>
       </c>
       <c r="D41">
-        <v>37.33238140027926</v>
+        <v>37.21558242515218</v>
       </c>
       <c r="E41">
-        <v>-4.108000000000001</v>
+        <v>-3.68</v>
       </c>
       <c r="F41">
-        <v>16.692</v>
+        <v>17.12</v>
       </c>
       <c r="G41">
         <v>0.821</v>
@@ -4649,28 +4649,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M41">
-        <v>1.2001548</v>
+        <v>1.230928</v>
       </c>
       <c r="N41">
-        <v>1.942511866666667</v>
+        <v>1.911738666666667</v>
       </c>
       <c r="O41">
-        <v>0.29137678</v>
+        <v>0.2867608</v>
       </c>
       <c r="P41">
-        <v>1.651135086666667</v>
+        <v>1.624977866666667</v>
       </c>
       <c r="Q41">
-        <v>1.775135086666667</v>
+        <v>1.748977866666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09236632673232834</v>
+        <v>0.09306700610429645</v>
       </c>
       <c r="T41">
-        <v>0.8528786275210626</v>
+        <v>0.8657118162870904</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.618551095797531</v>
+        <v>2.553087318402592</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08028620366257788</v>
+        <v>0.08175324801843546</v>
       </c>
       <c r="C42">
-        <v>20.91658242515217</v>
+        <v>18.97002949444681</v>
       </c>
       <c r="D42">
-        <v>37.21558242515218</v>
+        <v>35.69702949444681</v>
       </c>
       <c r="E42">
-        <v>-3.68</v>
+        <v>-3.251999999999999</v>
       </c>
       <c r="F42">
-        <v>17.12</v>
+        <v>17.548</v>
       </c>
       <c r="G42">
         <v>0.821</v>
@@ -4731,45 +4731,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M42">
-        <v>1.230928</v>
+        <v>1.3301384</v>
       </c>
       <c r="N42">
-        <v>1.911738666666667</v>
+        <v>1.812528266666667</v>
       </c>
       <c r="O42">
-        <v>0.2867608</v>
+        <v>0.27187924</v>
       </c>
       <c r="P42">
-        <v>1.624977866666667</v>
+        <v>1.540649026666667</v>
       </c>
       <c r="Q42">
-        <v>1.748977866666667</v>
+        <v>1.664649026666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09306700610429645</v>
+        <v>0.09379143731938214</v>
       </c>
       <c r="T42">
-        <v>0.8657118162870904</v>
+        <v>0.8789800284011189</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.553087318402592</v>
+        <v>2.36266140926889</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08175324801843546</v>
+        <v>0.08189429237429305</v>
       </c>
       <c r="C43">
-        <v>18.97002949444681</v>
+        <v>18.40253750832161</v>
       </c>
       <c r="D43">
-        <v>35.69702949444681</v>
+        <v>35.55753750832162</v>
       </c>
       <c r="E43">
-        <v>-3.251999999999999</v>
+        <v>-2.824000000000002</v>
       </c>
       <c r="F43">
-        <v>17.548</v>
+        <v>17.976</v>
       </c>
       <c r="G43">
         <v>0.821</v>
@@ -4813,28 +4813,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M43">
-        <v>1.3301384</v>
+        <v>1.3625808</v>
       </c>
       <c r="N43">
-        <v>1.812528266666667</v>
+        <v>1.780085866666667</v>
       </c>
       <c r="O43">
-        <v>0.27187924</v>
+        <v>0.26701288</v>
       </c>
       <c r="P43">
-        <v>1.540649026666667</v>
+        <v>1.513072986666667</v>
       </c>
       <c r="Q43">
-        <v>1.664649026666667</v>
+        <v>1.637072986666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09379143731938214</v>
+        <v>0.09454084892119491</v>
       </c>
       <c r="T43">
-        <v>0.8789800284011189</v>
+        <v>0.8927057650708037</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.36266140926889</v>
+        <v>2.306407566191059</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08189429237429305</v>
+        <v>0.08203533673015063</v>
       </c>
       <c r="C44">
-        <v>18.40253750832161</v>
+        <v>17.83613145427851</v>
       </c>
       <c r="D44">
-        <v>35.55753750832162</v>
+        <v>35.41913145427851</v>
       </c>
       <c r="E44">
-        <v>-2.824000000000002</v>
+        <v>-2.396000000000001</v>
       </c>
       <c r="F44">
-        <v>17.976</v>
+        <v>18.404</v>
       </c>
       <c r="G44">
         <v>0.821</v>
@@ -4895,28 +4895,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M44">
-        <v>1.3625808</v>
+        <v>1.3950232</v>
       </c>
       <c r="N44">
-        <v>1.780085866666667</v>
+        <v>1.747643466666667</v>
       </c>
       <c r="O44">
-        <v>0.26701288</v>
+        <v>0.26214652</v>
       </c>
       <c r="P44">
-        <v>1.513072986666667</v>
+        <v>1.485496946666667</v>
       </c>
       <c r="Q44">
-        <v>1.637072986666667</v>
+        <v>1.609496946666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09454084892119491</v>
+        <v>0.09531655566693092</v>
       </c>
       <c r="T44">
-        <v>0.8927057650708036</v>
+        <v>0.9069131065359158</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.306407566191059</v>
+        <v>2.252770180930802</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08203533673015063</v>
+        <v>0.08217638108600822</v>
       </c>
       <c r="C45">
-        <v>17.83613145427851</v>
+        <v>17.27079870066589</v>
       </c>
       <c r="D45">
-        <v>35.41913145427851</v>
+        <v>35.28179870066589</v>
       </c>
       <c r="E45">
-        <v>-2.396000000000001</v>
+        <v>-1.968000000000004</v>
       </c>
       <c r="F45">
-        <v>18.404</v>
+        <v>18.832</v>
       </c>
       <c r="G45">
         <v>0.821</v>
@@ -4977,28 +4977,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M45">
-        <v>1.3950232</v>
+        <v>1.4274656</v>
       </c>
       <c r="N45">
-        <v>1.747643466666667</v>
+        <v>1.715201066666667</v>
       </c>
       <c r="O45">
-        <v>0.26214652</v>
+        <v>0.25728016</v>
       </c>
       <c r="P45">
-        <v>1.485496946666667</v>
+        <v>1.457920906666667</v>
       </c>
       <c r="Q45">
-        <v>1.609496946666667</v>
+        <v>1.581920906666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09531655566693092</v>
+        <v>0.09611996622501467</v>
       </c>
       <c r="T45">
-        <v>0.9069131065359158</v>
+        <v>0.9216278530533536</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.252770180930802</v>
+        <v>2.201570858636921</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08217638108600822</v>
+        <v>0.08231742544186582</v>
       </c>
       <c r="C46">
-        <v>17.27079870066589</v>
+        <v>16.7065268109853</v>
       </c>
       <c r="D46">
-        <v>35.28179870066589</v>
+        <v>35.1455268109853</v>
       </c>
       <c r="E46">
-        <v>-1.968000000000004</v>
+        <v>-1.540000000000003</v>
       </c>
       <c r="F46">
-        <v>18.832</v>
+        <v>19.26</v>
       </c>
       <c r="G46">
         <v>0.821</v>
@@ -5059,28 +5059,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M46">
-        <v>1.4274656</v>
+        <v>1.459908</v>
       </c>
       <c r="N46">
-        <v>1.715201066666667</v>
+        <v>1.682758666666667</v>
       </c>
       <c r="O46">
-        <v>0.25728016</v>
+        <v>0.2524138</v>
       </c>
       <c r="P46">
-        <v>1.457920906666667</v>
+        <v>1.430344866666667</v>
       </c>
       <c r="Q46">
-        <v>1.581920906666667</v>
+        <v>1.554344866666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09611996622501467</v>
+        <v>0.0969525917124833</v>
       </c>
       <c r="T46">
-        <v>0.9216278530533536</v>
+        <v>0.9368776812623346</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.201570858636921</v>
+        <v>2.152647061778322</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08231742544186582</v>
+        <v>0.08245846979772341</v>
       </c>
       <c r="C47">
-        <v>16.7065268109853</v>
+        <v>16.1433035401373</v>
       </c>
       <c r="D47">
-        <v>35.1455268109853</v>
+        <v>35.0103035401373</v>
       </c>
       <c r="E47">
-        <v>-1.540000000000003</v>
+        <v>-1.112000000000002</v>
       </c>
       <c r="F47">
-        <v>19.26</v>
+        <v>19.688</v>
       </c>
       <c r="G47">
         <v>0.821</v>
@@ -5141,28 +5141,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M47">
-        <v>1.459908</v>
+        <v>1.4923504</v>
       </c>
       <c r="N47">
-        <v>1.682758666666667</v>
+        <v>1.650316266666667</v>
       </c>
       <c r="O47">
-        <v>0.2524138</v>
+        <v>0.24754744</v>
       </c>
       <c r="P47">
-        <v>1.430344866666667</v>
+        <v>1.402768826666667</v>
       </c>
       <c r="Q47">
-        <v>1.554344866666667</v>
+        <v>1.526768826666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0969525917124833</v>
+        <v>0.09781605518096925</v>
       </c>
       <c r="T47">
-        <v>0.9368776812623346</v>
+        <v>0.9526923179235001</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.152647061778322</v>
+        <v>2.105850386522272</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08245846979772341</v>
+        <v>0.08259951415358099</v>
       </c>
       <c r="C48">
-        <v>16.1433035401373</v>
+        <v>15.58111683075334</v>
       </c>
       <c r="D48">
-        <v>35.0103035401373</v>
+        <v>34.87611683075335</v>
       </c>
       <c r="E48">
-        <v>-1.112000000000002</v>
+        <v>-0.6840000000000011</v>
       </c>
       <c r="F48">
-        <v>19.688</v>
+        <v>20.116</v>
       </c>
       <c r="G48">
         <v>0.821</v>
@@ -5223,28 +5223,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M48">
-        <v>1.4923504</v>
+        <v>1.5247928</v>
       </c>
       <c r="N48">
-        <v>1.650316266666667</v>
+        <v>1.617873866666667</v>
       </c>
       <c r="O48">
-        <v>0.24754744</v>
+        <v>0.24268108</v>
       </c>
       <c r="P48">
-        <v>1.402768826666667</v>
+        <v>1.375192786666667</v>
       </c>
       <c r="Q48">
-        <v>1.526768826666667</v>
+        <v>1.499192786666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09781605518096925</v>
+        <v>0.0987121021765679</v>
       </c>
       <c r="T48">
-        <v>0.9526923179235001</v>
+        <v>0.9691037333265963</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.105850386522272</v>
+        <v>2.061045059149457</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08259951415358099</v>
+        <v>0.08274055850943858</v>
       </c>
       <c r="C49">
-        <v>15.58111683075334</v>
+        <v>15.01995480961198</v>
       </c>
       <c r="D49">
-        <v>34.87611683075335</v>
+        <v>34.74295480961198</v>
       </c>
       <c r="E49">
-        <v>-0.6840000000000011</v>
+        <v>-0.2560000000000002</v>
       </c>
       <c r="F49">
-        <v>20.116</v>
+        <v>20.544</v>
       </c>
       <c r="G49">
         <v>0.821</v>
@@ -5305,28 +5305,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M49">
-        <v>1.5247928</v>
+        <v>1.5572352</v>
       </c>
       <c r="N49">
-        <v>1.617873866666667</v>
+        <v>1.585431466666667</v>
       </c>
       <c r="O49">
-        <v>0.24268108</v>
+        <v>0.23781472</v>
       </c>
       <c r="P49">
-        <v>1.375192786666667</v>
+        <v>1.347616746666667</v>
       </c>
       <c r="Q49">
-        <v>1.499192786666667</v>
+        <v>1.471616746666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0987121021765679</v>
+        <v>0.0996426125181511</v>
       </c>
       <c r="T49">
-        <v>0.9691037333265963</v>
+        <v>0.9861463570144268</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.061045059149457</v>
+        <v>2.018106620417177</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08274055850943857</v>
+        <v>0.08879590286529615</v>
       </c>
       <c r="C50">
-        <v>15.019954809612</v>
+        <v>9.698917536472042</v>
       </c>
       <c r="D50">
-        <v>34.74295480961199</v>
+        <v>29.84991753647204</v>
       </c>
       <c r="E50">
-        <v>-0.2560000000000038</v>
+        <v>0.171999999999997</v>
       </c>
       <c r="F50">
-        <v>20.544</v>
+        <v>20.972</v>
       </c>
       <c r="G50">
         <v>0.821</v>
@@ -5387,45 +5387,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M50">
-        <v>1.5572352</v>
+        <v>1.88748</v>
       </c>
       <c r="N50">
-        <v>1.585431466666667</v>
+        <v>1.255186666666667</v>
       </c>
       <c r="O50">
-        <v>0.2378147200000001</v>
+        <v>0.1882780000000001</v>
       </c>
       <c r="P50">
-        <v>1.347616746666667</v>
+        <v>1.066908666666667</v>
       </c>
       <c r="Q50">
-        <v>1.471616746666667</v>
+        <v>1.190908666666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0996426125181511</v>
+        <v>0.100609613461365</v>
       </c>
       <c r="T50">
-        <v>0.9861463570144268</v>
+        <v>1.003857318886094</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.018106620417178</v>
+        <v>1.665006604926498</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08879590286529615</v>
+        <v>0.08905764722115375</v>
       </c>
       <c r="C51">
-        <v>9.698917536472042</v>
+        <v>9.090300976397884</v>
       </c>
       <c r="D51">
-        <v>29.84991753647204</v>
+        <v>29.66930097639788</v>
       </c>
       <c r="E51">
-        <v>0.171999999999997</v>
+        <v>0.5999999999999979</v>
       </c>
       <c r="F51">
-        <v>20.972</v>
+        <v>21.4</v>
       </c>
       <c r="G51">
         <v>0.821</v>
@@ -5469,28 +5469,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M51">
-        <v>1.88748</v>
+        <v>1.926</v>
       </c>
       <c r="N51">
-        <v>1.255186666666667</v>
+        <v>1.216666666666667</v>
       </c>
       <c r="O51">
-        <v>0.1882780000000001</v>
+        <v>0.1825000000000001</v>
       </c>
       <c r="P51">
-        <v>1.066908666666667</v>
+        <v>1.034166666666667</v>
       </c>
       <c r="Q51">
-        <v>1.190908666666667</v>
+        <v>1.158166666666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.100609613461365</v>
+        <v>0.1016152944423075</v>
       </c>
       <c r="T51">
-        <v>1.003857318886094</v>
+        <v>1.022276719232628</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.665006604926498</v>
+        <v>1.631706472827969</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08905764722115375</v>
+        <v>0.08931939157701134</v>
       </c>
       <c r="C52">
-        <v>9.090300976397884</v>
+        <v>8.483857027817624</v>
       </c>
       <c r="D52">
-        <v>29.66930097639788</v>
+        <v>29.49085702781762</v>
       </c>
       <c r="E52">
-        <v>0.5999999999999979</v>
+        <v>1.027999999999999</v>
       </c>
       <c r="F52">
-        <v>21.4</v>
+        <v>21.828</v>
       </c>
       <c r="G52">
         <v>0.821</v>
@@ -5551,28 +5551,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M52">
-        <v>1.926</v>
+        <v>1.96452</v>
       </c>
       <c r="N52">
-        <v>1.216666666666667</v>
+        <v>1.178146666666667</v>
       </c>
       <c r="O52">
-        <v>0.1825000000000001</v>
+        <v>0.1767220000000001</v>
       </c>
       <c r="P52">
-        <v>1.034166666666667</v>
+        <v>1.001424666666667</v>
       </c>
       <c r="Q52">
-        <v>1.158166666666667</v>
+        <v>1.125424666666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1016152944423075</v>
+        <v>0.1026620236265538</v>
       </c>
       <c r="T52">
-        <v>1.022276719232628</v>
+        <v>1.041447931838204</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.631706472827969</v>
+        <v>1.599712228262714</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08931939157701134</v>
+        <v>0.08958113593286893</v>
       </c>
       <c r="C53">
-        <v>8.483857027817624</v>
+        <v>7.879546724031307</v>
       </c>
       <c r="D53">
-        <v>29.49085702781762</v>
+        <v>29.31454672403131</v>
       </c>
       <c r="E53">
-        <v>1.027999999999999</v>
+        <v>1.456</v>
       </c>
       <c r="F53">
-        <v>21.828</v>
+        <v>22.256</v>
       </c>
       <c r="G53">
         <v>0.821</v>
@@ -5633,28 +5633,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M53">
-        <v>1.96452</v>
+        <v>2.00304</v>
       </c>
       <c r="N53">
-        <v>1.178146666666667</v>
+        <v>1.139626666666667</v>
       </c>
       <c r="O53">
-        <v>0.1767220000000001</v>
+        <v>0.170944</v>
       </c>
       <c r="P53">
-        <v>1.001424666666667</v>
+        <v>0.968682666666667</v>
       </c>
       <c r="Q53">
-        <v>1.125424666666667</v>
+        <v>1.092682666666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1026620236265538</v>
+        <v>0.1037523665268103</v>
       </c>
       <c r="T53">
-        <v>1.041447931838204</v>
+        <v>1.061417944969012</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.599712228262714</v>
+        <v>1.568948531565354</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08958113593286893</v>
+        <v>0.08984288028872651</v>
       </c>
       <c r="C54">
-        <v>7.879546724031307</v>
+        <v>7.277332024646562</v>
       </c>
       <c r="D54">
-        <v>29.31454672403131</v>
+        <v>29.14033202464656</v>
       </c>
       <c r="E54">
-        <v>1.456</v>
+        <v>1.884</v>
       </c>
       <c r="F54">
-        <v>22.256</v>
+        <v>22.684</v>
       </c>
       <c r="G54">
         <v>0.821</v>
@@ -5715,28 +5715,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M54">
-        <v>2.00304</v>
+        <v>2.04156</v>
       </c>
       <c r="N54">
-        <v>1.139626666666667</v>
+        <v>1.101106666666667</v>
       </c>
       <c r="O54">
-        <v>0.170944</v>
+        <v>0.165166</v>
       </c>
       <c r="P54">
-        <v>0.968682666666667</v>
+        <v>0.9359406666666669</v>
       </c>
       <c r="Q54">
-        <v>1.092682666666667</v>
+        <v>1.059940666666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1037523665268103</v>
+        <v>0.1048891069972905</v>
       </c>
       <c r="T54">
-        <v>1.061417944969012</v>
+        <v>1.082237745892621</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.568948531565354</v>
+        <v>1.539345729082989</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08984288028872651</v>
+        <v>0.0901046246445841</v>
       </c>
       <c r="C55">
-        <v>7.277332024646562</v>
+        <v>6.677175788216292</v>
       </c>
       <c r="D55">
-        <v>29.14033202464656</v>
+        <v>28.96817578821629</v>
       </c>
       <c r="E55">
-        <v>1.884</v>
+        <v>2.311999999999998</v>
       </c>
       <c r="F55">
-        <v>22.684</v>
+        <v>23.112</v>
       </c>
       <c r="G55">
         <v>0.821</v>
@@ -5797,28 +5797,28 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M55">
-        <v>2.04156</v>
+        <v>2.08008</v>
       </c>
       <c r="N55">
-        <v>1.101106666666667</v>
+        <v>1.062586666666667</v>
       </c>
       <c r="O55">
-        <v>0.165166</v>
+        <v>0.1593880000000001</v>
       </c>
       <c r="P55">
-        <v>0.9359406666666669</v>
+        <v>0.9031986666666671</v>
       </c>
       <c r="Q55">
-        <v>1.059940666666667</v>
+        <v>1.027198666666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1048891069972905</v>
+        <v>0.1060752709664872</v>
       </c>
       <c r="T55">
-        <v>1.082237745892621</v>
+        <v>1.103962755552039</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.539345729082989</v>
+        <v>1.510839326692563</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0901046246445841</v>
+        <v>0.118242802605512</v>
       </c>
       <c r="C56">
-        <v>6.677175788216292</v>
+        <v>-5.002620887444813</v>
       </c>
       <c r="D56">
-        <v>28.96817578821629</v>
+        <v>17.71637911255518</v>
       </c>
       <c r="E56">
-        <v>2.311999999999998</v>
+        <v>2.739999999999998</v>
       </c>
       <c r="F56">
-        <v>23.112</v>
+        <v>23.54</v>
       </c>
       <c r="G56">
         <v>0.821</v>
@@ -5879,45 +5879,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M56">
-        <v>2.08008</v>
+        <v>3.455672</v>
       </c>
       <c r="N56">
-        <v>1.062586666666667</v>
+        <v>-0.3130053333333334</v>
       </c>
       <c r="O56">
-        <v>0.1593880000000001</v>
+        <v>-0.0469508</v>
       </c>
       <c r="P56">
-        <v>0.9031986666666671</v>
+        <v>-0.2660545333333333</v>
       </c>
       <c r="Q56">
-        <v>1.027198666666667</v>
+        <v>-0.1420545333333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1060752709664872</v>
+        <v>0.1078151584380018</v>
       </c>
       <c r="T56">
-        <v>1.103962755552039</v>
+        <v>1.13582940561607</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.15</v>
+        <v>0.1364134096060043</v>
       </c>
       <c r="W56">
-        <v>0.0765</v>
+        <v>0.1267745114698386</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.510839326692563</v>
+        <v>0.9094227307066951</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.118242802605512</v>
+        <v>0.119252802605512</v>
       </c>
       <c r="C57">
-        <v>-5.002620887444813</v>
+        <v>-5.674226880258729</v>
       </c>
       <c r="D57">
-        <v>17.71637911255518</v>
+        <v>17.47277311974127</v>
       </c>
       <c r="E57">
-        <v>2.739999999999998</v>
+        <v>3.167999999999999</v>
       </c>
       <c r="F57">
-        <v>23.54</v>
+        <v>23.968</v>
       </c>
       <c r="G57">
         <v>0.821</v>
@@ -5961,37 +5961,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M57">
-        <v>3.455672</v>
+        <v>3.5185024</v>
       </c>
       <c r="N57">
-        <v>-0.3130053333333334</v>
+        <v>-0.3758357333333335</v>
       </c>
       <c r="O57">
-        <v>-0.0469508</v>
+        <v>-0.05637536000000003</v>
       </c>
       <c r="P57">
-        <v>-0.2660545333333333</v>
+        <v>-0.3194603733333335</v>
       </c>
       <c r="Q57">
-        <v>-0.1420545333333333</v>
+        <v>-0.1954603733333335</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1078151584380018</v>
+        <v>0.1092245938570473</v>
       </c>
       <c r="T57">
-        <v>1.13582940561607</v>
+        <v>1.161643710289163</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1364134096060043</v>
+        <v>0.1339774558630399</v>
       </c>
       <c r="W57">
-        <v>0.1267745114698386</v>
+        <v>0.1271321094793058</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9094227307066951</v>
+        <v>0.8931830390869326</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.119252802605512</v>
+        <v>0.120262802605512</v>
       </c>
       <c r="C58">
-        <v>-5.674226880258729</v>
+        <v>-6.339224417733</v>
       </c>
       <c r="D58">
-        <v>17.47277311974127</v>
+        <v>17.235775582267</v>
       </c>
       <c r="E58">
-        <v>3.167999999999999</v>
+        <v>3.596</v>
       </c>
       <c r="F58">
-        <v>23.968</v>
+        <v>24.396</v>
       </c>
       <c r="G58">
         <v>0.821</v>
@@ -6043,37 +6043,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M58">
-        <v>3.5185024</v>
+        <v>3.581332800000001</v>
       </c>
       <c r="N58">
-        <v>-0.3758357333333335</v>
+        <v>-0.4386661333333337</v>
       </c>
       <c r="O58">
-        <v>-0.05637536000000003</v>
+        <v>-0.06579992000000005</v>
       </c>
       <c r="P58">
-        <v>-0.3194603733333335</v>
+        <v>-0.3728662133333336</v>
       </c>
       <c r="Q58">
-        <v>-0.1954603733333335</v>
+        <v>-0.2488662133333336</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1092245938570473</v>
+        <v>0.1106995844118623</v>
       </c>
       <c r="T58">
-        <v>1.161643710289163</v>
+        <v>1.188658680295887</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1339774558630399</v>
+        <v>0.1316269741812322</v>
       </c>
       <c r="W58">
-        <v>0.1271321094793058</v>
+        <v>0.1274771601901951</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8931830390869326</v>
+        <v>0.8775131612082145</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.120262802605512</v>
+        <v>0.121272802605512</v>
       </c>
       <c r="C59">
-        <v>-6.339224417733</v>
+        <v>-6.997878808945686</v>
       </c>
       <c r="D59">
-        <v>17.235775582267</v>
+        <v>17.00512119105431</v>
       </c>
       <c r="E59">
-        <v>3.596</v>
+        <v>4.024000000000001</v>
       </c>
       <c r="F59">
-        <v>24.396</v>
+        <v>24.824</v>
       </c>
       <c r="G59">
         <v>0.821</v>
@@ -6125,37 +6125,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M59">
-        <v>3.581332800000001</v>
+        <v>3.6441632</v>
       </c>
       <c r="N59">
-        <v>-0.4386661333333337</v>
+        <v>-0.5014965333333334</v>
       </c>
       <c r="O59">
-        <v>-0.06579992000000005</v>
+        <v>-0.07522448000000001</v>
       </c>
       <c r="P59">
-        <v>-0.3728662133333336</v>
+        <v>-0.4262720533333334</v>
       </c>
       <c r="Q59">
-        <v>-0.2488662133333336</v>
+        <v>-0.3022720533333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1106995844118623</v>
+        <v>0.1122448126121448</v>
       </c>
       <c r="T59">
-        <v>1.188658680295887</v>
+        <v>1.21696007744579</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1316269741812322</v>
+        <v>0.1293575435919006</v>
       </c>
       <c r="W59">
-        <v>0.1274771601901951</v>
+        <v>0.127810312600709</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8775131612082145</v>
+        <v>0.862383623946004</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.121272802605512</v>
+        <v>0.122282802605512</v>
       </c>
       <c r="C60">
-        <v>-6.997878808945678</v>
+        <v>-7.650441348730627</v>
       </c>
       <c r="D60">
-        <v>17.00512119105432</v>
+        <v>16.78055865126937</v>
       </c>
       <c r="E60">
-        <v>4.023999999999997</v>
+        <v>4.451999999999995</v>
       </c>
       <c r="F60">
-        <v>24.824</v>
+        <v>25.252</v>
       </c>
       <c r="G60">
         <v>0.821</v>
@@ -6207,37 +6207,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M60">
-        <v>3.6441632</v>
+        <v>3.7069936</v>
       </c>
       <c r="N60">
-        <v>-0.501496533333333</v>
+        <v>-0.5643269333333327</v>
       </c>
       <c r="O60">
-        <v>-0.07522447999999994</v>
+        <v>-0.08464903999999991</v>
       </c>
       <c r="P60">
-        <v>-0.4262720533333331</v>
+        <v>-0.4796778933333328</v>
       </c>
       <c r="Q60">
-        <v>-0.3022720533333331</v>
+        <v>-0.3556778933333328</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1122448126121448</v>
+        <v>0.1138654177978068</v>
       </c>
       <c r="T60">
-        <v>1.216960077445789</v>
+        <v>1.246642030554223</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1293575435919006</v>
+        <v>0.1271650428530549</v>
       </c>
       <c r="W60">
-        <v>0.127810312600709</v>
+        <v>0.1281321717091716</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8623836239460041</v>
+        <v>0.847766952353699</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.122282802605512</v>
+        <v>0.123292802605512</v>
       </c>
       <c r="C61">
-        <v>-7.650441348730627</v>
+        <v>-8.297150230948503</v>
       </c>
       <c r="D61">
-        <v>16.78055865126937</v>
+        <v>16.56184976905149</v>
       </c>
       <c r="E61">
-        <v>4.451999999999995</v>
+        <v>4.879999999999995</v>
       </c>
       <c r="F61">
-        <v>25.252</v>
+        <v>25.68</v>
       </c>
       <c r="G61">
         <v>0.821</v>
@@ -6289,37 +6289,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M61">
-        <v>3.7069936</v>
+        <v>3.769824</v>
       </c>
       <c r="N61">
-        <v>-0.5643269333333327</v>
+        <v>-0.6271573333333329</v>
       </c>
       <c r="O61">
-        <v>-0.08464903999999991</v>
+        <v>-0.09407359999999994</v>
       </c>
       <c r="P61">
-        <v>-0.4796778933333328</v>
+        <v>-0.5330837333333329</v>
       </c>
       <c r="Q61">
-        <v>-0.3556778933333328</v>
+        <v>-0.4090837333333329</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1138654177978068</v>
+        <v>0.115567053242752</v>
       </c>
       <c r="T61">
-        <v>1.246642030554223</v>
+        <v>1.277808081318079</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1271650428530549</v>
+        <v>0.1250456254721706</v>
       </c>
       <c r="W61">
-        <v>0.1281321717091716</v>
+        <v>0.1284433021806854</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.847766952353699</v>
+        <v>0.833637503147804</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.123292802605512</v>
+        <v>0.124302802605512</v>
       </c>
       <c r="C62">
-        <v>-8.297150230948503</v>
+        <v>-8.938231391258157</v>
       </c>
       <c r="D62">
-        <v>16.56184976905149</v>
+        <v>16.34876860874184</v>
       </c>
       <c r="E62">
-        <v>4.879999999999995</v>
+        <v>5.307999999999996</v>
       </c>
       <c r="F62">
-        <v>25.68</v>
+        <v>26.108</v>
       </c>
       <c r="G62">
         <v>0.821</v>
@@ -6371,37 +6371,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M62">
-        <v>3.769824</v>
+        <v>3.8326544</v>
       </c>
       <c r="N62">
-        <v>-0.6271573333333329</v>
+        <v>-0.6899877333333331</v>
       </c>
       <c r="O62">
-        <v>-0.09407359999999994</v>
+        <v>-0.10349816</v>
       </c>
       <c r="P62">
-        <v>-0.5330837333333329</v>
+        <v>-0.5864895733333331</v>
       </c>
       <c r="Q62">
-        <v>-0.4090837333333329</v>
+        <v>-0.4624895733333331</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.115567053242752</v>
+        <v>0.1173559520438482</v>
       </c>
       <c r="T62">
-        <v>1.277808081318079</v>
+        <v>1.310572391095466</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1250456254721706</v>
+        <v>0.1229956971857416</v>
       </c>
       <c r="W62">
-        <v>0.1284433021806854</v>
+        <v>0.1287442316531331</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.833637503147804</v>
+        <v>0.8199713145716104</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.124302802605512</v>
+        <v>0.125312802605512</v>
       </c>
       <c r="C63">
-        <v>-8.938231391258157</v>
+        <v>-9.5738992856569</v>
       </c>
       <c r="D63">
-        <v>16.34876860874184</v>
+        <v>16.1411007143431</v>
       </c>
       <c r="E63">
-        <v>5.307999999999996</v>
+        <v>5.735999999999997</v>
       </c>
       <c r="F63">
-        <v>26.108</v>
+        <v>26.536</v>
       </c>
       <c r="G63">
         <v>0.821</v>
@@ -6453,37 +6453,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M63">
-        <v>3.8326544</v>
+        <v>3.8954848</v>
       </c>
       <c r="N63">
-        <v>-0.6899877333333331</v>
+        <v>-0.7528181333333333</v>
       </c>
       <c r="O63">
-        <v>-0.10349816</v>
+        <v>-0.11292272</v>
       </c>
       <c r="P63">
-        <v>-0.5864895733333331</v>
+        <v>-0.6398954133333332</v>
       </c>
       <c r="Q63">
-        <v>-0.4624895733333331</v>
+        <v>-0.5158954133333332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1173559520438482</v>
+        <v>0.1192390034134232</v>
       </c>
       <c r="T63">
-        <v>1.310572391095466</v>
+        <v>1.345061138229557</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1229956971857416</v>
+        <v>0.1210118956182296</v>
       </c>
       <c r="W63">
-        <v>0.1287442316531331</v>
+        <v>0.1290354537232439</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8199713145716104</v>
+        <v>0.8067459707881973</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.125312802605512</v>
+        <v>0.160951541843975</v>
       </c>
       <c r="C64">
-        <v>-9.5738992856569</v>
+        <v>-14.99747702754834</v>
       </c>
       <c r="D64">
-        <v>16.1411007143431</v>
+        <v>11.14552297245166</v>
       </c>
       <c r="E64">
-        <v>5.735999999999997</v>
+        <v>6.163999999999998</v>
       </c>
       <c r="F64">
-        <v>26.536</v>
+        <v>26.964</v>
       </c>
       <c r="G64">
         <v>0.821</v>
@@ -6535,45 +6535,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M64">
-        <v>3.8954848</v>
+        <v>5.4143712</v>
       </c>
       <c r="N64">
-        <v>-0.7528181333333333</v>
+        <v>-2.271704533333333</v>
       </c>
       <c r="O64">
-        <v>-0.11292272</v>
+        <v>-0.3407556799999999</v>
       </c>
       <c r="P64">
-        <v>-0.6398954133333332</v>
+        <v>-1.930948853333333</v>
       </c>
       <c r="Q64">
-        <v>-0.5158954133333332</v>
+        <v>-1.806948853333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1192390034134232</v>
+        <v>0.1228690825285508</v>
       </c>
       <c r="T64">
-        <v>1.345061138229557</v>
+        <v>1.411547312054248</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1210118956182296</v>
+        <v>0.08706458840502108</v>
       </c>
       <c r="W64">
-        <v>0.1290354537232439</v>
+        <v>0.1833174306482718</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8067459707881973</v>
+        <v>0.5804305893668071</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.160951541843975</v>
+        <v>0.162501541843975</v>
       </c>
       <c r="C65">
-        <v>-14.99747702754834</v>
+        <v>-15.57350901011115</v>
       </c>
       <c r="D65">
-        <v>11.14552297245166</v>
+        <v>10.99749098988885</v>
       </c>
       <c r="E65">
-        <v>6.163999999999998</v>
+        <v>6.591999999999999</v>
       </c>
       <c r="F65">
-        <v>26.964</v>
+        <v>27.392</v>
       </c>
       <c r="G65">
         <v>0.821</v>
@@ -6617,37 +6617,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M65">
-        <v>5.4143712</v>
+        <v>5.5003136</v>
       </c>
       <c r="N65">
-        <v>-2.271704533333333</v>
+        <v>-2.357646933333333</v>
       </c>
       <c r="O65">
-        <v>-0.3407556799999999</v>
+        <v>-0.35364704</v>
       </c>
       <c r="P65">
-        <v>-1.930948853333333</v>
+        <v>-2.003999893333333</v>
       </c>
       <c r="Q65">
-        <v>-1.806948853333333</v>
+        <v>-1.879999893333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1228690825285508</v>
+        <v>0.1250098903765661</v>
       </c>
       <c r="T65">
-        <v>1.411547312054248</v>
+        <v>1.45075695961131</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08706458840502108</v>
+        <v>0.08570420421119261</v>
       </c>
       <c r="W65">
-        <v>0.1833174306482718</v>
+        <v>0.1835905957943925</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5804305893668071</v>
+        <v>0.5713613614079508</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.162501541843975</v>
+        <v>0.164051541843975</v>
       </c>
       <c r="C66">
-        <v>-15.57350901011115</v>
+        <v>-16.14566028939695</v>
       </c>
       <c r="D66">
-        <v>10.99749098988885</v>
+        <v>10.85333971060305</v>
       </c>
       <c r="E66">
-        <v>6.591999999999999</v>
+        <v>7.02</v>
       </c>
       <c r="F66">
-        <v>27.392</v>
+        <v>27.82</v>
       </c>
       <c r="G66">
         <v>0.821</v>
@@ -6699,37 +6699,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M66">
-        <v>5.5003136</v>
+        <v>5.586256000000001</v>
       </c>
       <c r="N66">
-        <v>-2.357646933333333</v>
+        <v>-2.443589333333334</v>
       </c>
       <c r="O66">
-        <v>-0.35364704</v>
+        <v>-0.3665384</v>
       </c>
       <c r="P66">
-        <v>-2.003999893333333</v>
+        <v>-2.077050933333334</v>
       </c>
       <c r="Q66">
-        <v>-1.879999893333333</v>
+        <v>-1.953050933333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1250098903765661</v>
+        <v>0.1272730301016108</v>
       </c>
       <c r="T66">
-        <v>1.45075695961131</v>
+        <v>1.492207158457348</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08570420421119261</v>
+        <v>0.08438567799255887</v>
       </c>
       <c r="W66">
-        <v>0.1835905957943925</v>
+        <v>0.1838553558590942</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5713613614079508</v>
+        <v>0.5625711866170592</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.164051541843975</v>
+        <v>0.165601541843975</v>
       </c>
       <c r="C67">
-        <v>-16.14566028939695</v>
+        <v>-16.71408149176631</v>
       </c>
       <c r="D67">
-        <v>10.85333971060305</v>
+        <v>10.71291850823368</v>
       </c>
       <c r="E67">
-        <v>7.02</v>
+        <v>7.448</v>
       </c>
       <c r="F67">
-        <v>27.82</v>
+        <v>28.248</v>
       </c>
       <c r="G67">
         <v>0.821</v>
@@ -6781,37 +6781,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M67">
-        <v>5.586256000000001</v>
+        <v>5.6721984</v>
       </c>
       <c r="N67">
-        <v>-2.443589333333334</v>
+        <v>-2.529531733333333</v>
       </c>
       <c r="O67">
-        <v>-0.3665384</v>
+        <v>-0.3794297599999999</v>
       </c>
       <c r="P67">
-        <v>-2.077050933333334</v>
+        <v>-2.150101973333333</v>
       </c>
       <c r="Q67">
-        <v>-1.953050933333333</v>
+        <v>-2.026101973333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1272730301016108</v>
+        <v>0.1296692956928347</v>
       </c>
       <c r="T67">
-        <v>1.492207158457348</v>
+        <v>1.536095604294329</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08438567799255887</v>
+        <v>0.08310710711388375</v>
       </c>
       <c r="W67">
-        <v>0.1838553558590942</v>
+        <v>0.1841120928915321</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5625711866170592</v>
+        <v>0.554047380759225</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.165601541843975</v>
+        <v>0.167151541843975</v>
       </c>
       <c r="C68">
-        <v>-16.71408149176631</v>
+        <v>-17.2789155478932</v>
       </c>
       <c r="D68">
-        <v>10.71291850823368</v>
+        <v>10.5760844521068</v>
       </c>
       <c r="E68">
-        <v>7.448</v>
+        <v>7.875999999999998</v>
       </c>
       <c r="F68">
-        <v>28.248</v>
+        <v>28.676</v>
       </c>
       <c r="G68">
         <v>0.821</v>
@@ -6863,37 +6863,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M68">
-        <v>5.6721984</v>
+        <v>5.7581408</v>
       </c>
       <c r="N68">
-        <v>-2.529531733333333</v>
+        <v>-2.615474133333333</v>
       </c>
       <c r="O68">
-        <v>-0.3794297599999999</v>
+        <v>-0.3923211199999999</v>
       </c>
       <c r="P68">
-        <v>-2.150101973333333</v>
+        <v>-2.223153013333333</v>
       </c>
       <c r="Q68">
-        <v>-2.026101973333333</v>
+        <v>-2.099153013333332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1296692956928347</v>
+        <v>0.1322107895017085</v>
       </c>
       <c r="T68">
-        <v>1.536095604294329</v>
+        <v>1.582643955939611</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08310710711388375</v>
+        <v>0.08186670253009444</v>
       </c>
       <c r="W68">
-        <v>0.1841120928915321</v>
+        <v>0.184361166131957</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.554047380759225</v>
+        <v>0.5457780168672963</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.167151541843975</v>
+        <v>0.168701541843975</v>
       </c>
       <c r="C69">
-        <v>-17.2789155478932</v>
+        <v>-17.84029817804423</v>
       </c>
       <c r="D69">
-        <v>10.5760844521068</v>
+        <v>10.44270182195577</v>
       </c>
       <c r="E69">
-        <v>7.875999999999998</v>
+        <v>8.303999999999998</v>
       </c>
       <c r="F69">
-        <v>28.676</v>
+        <v>29.104</v>
       </c>
       <c r="G69">
         <v>0.821</v>
@@ -6945,37 +6945,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M69">
-        <v>5.7581408</v>
+        <v>5.8440832</v>
       </c>
       <c r="N69">
-        <v>-2.615474133333333</v>
+        <v>-2.701416533333333</v>
       </c>
       <c r="O69">
-        <v>-0.3923211199999999</v>
+        <v>-0.4052124799999999</v>
       </c>
       <c r="P69">
-        <v>-2.223153013333333</v>
+        <v>-2.296204053333333</v>
       </c>
       <c r="Q69">
-        <v>-2.099153013333332</v>
+        <v>-2.172204053333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1322107895017085</v>
+        <v>0.1349111266736369</v>
       </c>
       <c r="T69">
-        <v>1.582643955939611</v>
+        <v>1.632101579562725</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08186670253009444</v>
+        <v>0.08066278043406365</v>
       </c>
       <c r="W69">
-        <v>0.184361166131957</v>
+        <v>0.18460291368884</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5457780168672963</v>
+        <v>0.5377518695604242</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.168701541843975</v>
+        <v>0.170251541843975</v>
       </c>
       <c r="C70">
-        <v>-17.84029817804423</v>
+        <v>-18.39835834109407</v>
       </c>
       <c r="D70">
-        <v>10.44270182195577</v>
+        <v>10.31264165890594</v>
       </c>
       <c r="E70">
-        <v>8.303999999999998</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="F70">
-        <v>29.104</v>
+        <v>29.532</v>
       </c>
       <c r="G70">
         <v>0.821</v>
@@ -7027,37 +7027,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M70">
-        <v>5.8440832</v>
+        <v>5.9300256</v>
       </c>
       <c r="N70">
-        <v>-2.701416533333333</v>
+        <v>-2.787358933333334</v>
       </c>
       <c r="O70">
-        <v>-0.4052124799999999</v>
+        <v>-0.41810384</v>
       </c>
       <c r="P70">
-        <v>-2.296204053333333</v>
+        <v>-2.369255093333333</v>
       </c>
       <c r="Q70">
-        <v>-2.172204053333333</v>
+        <v>-2.245255093333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1349111266736369</v>
+        <v>0.13778567914698</v>
       </c>
       <c r="T70">
-        <v>1.632101579562725</v>
+        <v>1.684750017613135</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08066278043406365</v>
+        <v>0.0794937546306714</v>
       </c>
       <c r="W70">
-        <v>0.18460291368884</v>
+        <v>0.1848376540701612</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5377518695604242</v>
+        <v>0.5299583642044761</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.170251541843975</v>
+        <v>0.1718015418439751</v>
       </c>
       <c r="C71">
-        <v>-18.39835834109407</v>
+        <v>-18.95321865039963</v>
       </c>
       <c r="D71">
-        <v>10.31264165890594</v>
+        <v>10.18578134960037</v>
       </c>
       <c r="E71">
-        <v>8.731999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="F71">
-        <v>29.532</v>
+        <v>29.96</v>
       </c>
       <c r="G71">
         <v>0.821</v>
@@ -7109,37 +7109,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M71">
-        <v>5.9300256</v>
+        <v>6.015968</v>
       </c>
       <c r="N71">
-        <v>-2.787358933333334</v>
+        <v>-2.873301333333333</v>
       </c>
       <c r="O71">
-        <v>-0.41810384</v>
+        <v>-0.4309952</v>
       </c>
       <c r="P71">
-        <v>-2.369255093333333</v>
+        <v>-2.442306133333333</v>
       </c>
       <c r="Q71">
-        <v>-2.245255093333333</v>
+        <v>-2.318306133333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.13778567914698</v>
+        <v>0.1408518684518794</v>
       </c>
       <c r="T71">
-        <v>1.684750017613135</v>
+        <v>1.740908351533573</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.0794937546306714</v>
+        <v>0.07835812956451896</v>
       </c>
       <c r="W71">
-        <v>0.1848376540701612</v>
+        <v>0.1850656875834446</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5299583642044761</v>
+        <v>0.5223875304301264</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1718015418439751</v>
+        <v>0.173351541843975</v>
       </c>
       <c r="C72">
-        <v>-18.95321865039963</v>
+        <v>-19.50499575935213</v>
       </c>
       <c r="D72">
-        <v>10.18578134960037</v>
+        <v>10.06200424064788</v>
       </c>
       <c r="E72">
-        <v>9.16</v>
+        <v>9.588000000000001</v>
       </c>
       <c r="F72">
-        <v>29.96</v>
+        <v>30.388</v>
       </c>
       <c r="G72">
         <v>0.821</v>
@@ -7191,37 +7191,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M72">
-        <v>6.015968</v>
+        <v>6.1019104</v>
       </c>
       <c r="N72">
-        <v>-2.873301333333333</v>
+        <v>-2.959243733333333</v>
       </c>
       <c r="O72">
-        <v>-0.4309952</v>
+        <v>-0.44388656</v>
       </c>
       <c r="P72">
-        <v>-2.442306133333333</v>
+        <v>-2.515357173333333</v>
       </c>
       <c r="Q72">
-        <v>-2.318306133333333</v>
+        <v>-2.391357173333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1408518684518794</v>
+        <v>0.1441295190881511</v>
       </c>
       <c r="T72">
-        <v>1.740908351533573</v>
+        <v>1.800939674000248</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.07835812956451896</v>
+        <v>0.07725449393684967</v>
       </c>
       <c r="W72">
-        <v>0.1850656875834446</v>
+        <v>0.1852872976174806</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5223875304301264</v>
+        <v>0.5150299595789979</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.173351541843975</v>
+        <v>0.174901541843975</v>
       </c>
       <c r="C73">
-        <v>-19.50499575935212</v>
+        <v>-20.05380071915541</v>
       </c>
       <c r="D73">
-        <v>10.06200424064788</v>
+        <v>9.941199280844588</v>
       </c>
       <c r="E73">
-        <v>9.587999999999997</v>
+        <v>10.01599999999999</v>
       </c>
       <c r="F73">
-        <v>30.388</v>
+        <v>30.816</v>
       </c>
       <c r="G73">
         <v>0.821</v>
@@ -7273,37 +7273,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M73">
-        <v>6.1019104</v>
+        <v>6.187852799999999</v>
       </c>
       <c r="N73">
-        <v>-2.959243733333333</v>
+        <v>-3.045186133333332</v>
       </c>
       <c r="O73">
-        <v>-0.4438865599999999</v>
+        <v>-0.4567779199999998</v>
       </c>
       <c r="P73">
-        <v>-2.515357173333333</v>
+        <v>-2.588408213333332</v>
       </c>
       <c r="Q73">
-        <v>-2.391357173333333</v>
+        <v>-2.464408213333332</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.144129519088151</v>
+        <v>0.1476412876270136</v>
       </c>
       <c r="T73">
-        <v>1.800939674000247</v>
+        <v>1.865258948071685</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.0772544939368497</v>
+        <v>0.07618151485439344</v>
       </c>
       <c r="W73">
-        <v>0.1852872976174806</v>
+        <v>0.1855027518172378</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.515029959578998</v>
+        <v>0.5078767656959564</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.174901541843975</v>
+        <v>0.176451541843975</v>
       </c>
       <c r="C74">
-        <v>-20.05380071915541</v>
+        <v>-20.59973931113705</v>
       </c>
       <c r="D74">
-        <v>9.941199280844588</v>
+        <v>9.823260688862947</v>
       </c>
       <c r="E74">
-        <v>10.01599999999999</v>
+        <v>10.444</v>
       </c>
       <c r="F74">
-        <v>30.816</v>
+        <v>31.244</v>
       </c>
       <c r="G74">
         <v>0.821</v>
@@ -7355,37 +7355,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M74">
-        <v>6.187852799999999</v>
+        <v>6.273795199999999</v>
       </c>
       <c r="N74">
-        <v>-3.045186133333332</v>
+        <v>-3.131128533333333</v>
       </c>
       <c r="O74">
-        <v>-0.4567779199999998</v>
+        <v>-0.4696692799999999</v>
       </c>
       <c r="P74">
-        <v>-2.588408213333332</v>
+        <v>-2.661459253333333</v>
       </c>
       <c r="Q74">
-        <v>-2.464408213333332</v>
+        <v>-2.537459253333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1476412876270136</v>
+        <v>0.1514131871687548</v>
       </c>
       <c r="T74">
-        <v>1.865258948071685</v>
+        <v>1.93434261281508</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07618151485439344</v>
+        <v>0.07513793245912777</v>
       </c>
       <c r="W74">
-        <v>0.1855027518172378</v>
+        <v>0.1857123031622071</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5078767656959564</v>
+        <v>0.5009195497275185</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.176451541843975</v>
+        <v>0.2041471754794494</v>
       </c>
       <c r="C75">
-        <v>-20.59973931113705</v>
+        <v>-22.74587181536865</v>
       </c>
       <c r="D75">
-        <v>9.823260688862947</v>
+        <v>8.105128184631347</v>
       </c>
       <c r="E75">
-        <v>10.444</v>
+        <v>10.872</v>
       </c>
       <c r="F75">
-        <v>31.244</v>
+        <v>31.672</v>
       </c>
       <c r="G75">
         <v>0.821</v>
@@ -7437,45 +7437,45 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M75">
-        <v>6.273795199999999</v>
+        <v>7.468257599999999</v>
       </c>
       <c r="N75">
-        <v>-3.131128533333333</v>
+        <v>-4.325590933333332</v>
       </c>
       <c r="O75">
-        <v>-0.4696692799999999</v>
+        <v>-0.6488386399999998</v>
       </c>
       <c r="P75">
-        <v>-2.661459253333333</v>
+        <v>-3.676752293333333</v>
       </c>
       <c r="Q75">
-        <v>-2.537459253333333</v>
+        <v>-3.552752293333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1514131871687548</v>
+        <v>0.1564199775809162</v>
       </c>
       <c r="T75">
-        <v>1.93434261281508</v>
+        <v>2.026043737525982</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07513793245912777</v>
+        <v>0.06312047940071056</v>
       </c>
       <c r="W75">
-        <v>0.1857123031622071</v>
+        <v>0.2209161909573125</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5009195497275185</v>
+        <v>0.420803196004737</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2041471754794494</v>
+        <v>0.2060471754794495</v>
       </c>
       <c r="C76">
-        <v>-22.74587181536865</v>
+        <v>-23.26997175288533</v>
       </c>
       <c r="D76">
-        <v>8.105128184631347</v>
+        <v>8.009028247114667</v>
       </c>
       <c r="E76">
-        <v>10.872</v>
+        <v>11.29999999999999</v>
       </c>
       <c r="F76">
-        <v>31.672</v>
+        <v>32.09999999999999</v>
       </c>
       <c r="G76">
         <v>0.821</v>
@@ -7519,37 +7519,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M76">
-        <v>7.468257599999999</v>
+        <v>7.569179999999999</v>
       </c>
       <c r="N76">
-        <v>-4.325590933333332</v>
+        <v>-4.426513333333332</v>
       </c>
       <c r="O76">
-        <v>-0.6488386399999998</v>
+        <v>-0.6639769999999998</v>
       </c>
       <c r="P76">
-        <v>-3.676752293333333</v>
+        <v>-3.762536333333332</v>
       </c>
       <c r="Q76">
-        <v>-3.552752293333333</v>
+        <v>-3.638536333333332</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1564199775809162</v>
+        <v>0.1608447766841529</v>
       </c>
       <c r="T76">
-        <v>2.026043737525982</v>
+        <v>2.107085487027022</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06312047940071056</v>
+        <v>0.06227887300870108</v>
       </c>
       <c r="W76">
-        <v>0.2209161909573125</v>
+        <v>0.2211146417445483</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.420803196004737</v>
+        <v>0.4151924867246739</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2060471754794495</v>
+        <v>0.2079471754794494</v>
       </c>
       <c r="C77">
-        <v>-23.26997175288533</v>
+        <v>-23.79181954039394</v>
       </c>
       <c r="D77">
-        <v>8.009028247114667</v>
+        <v>7.915180459606054</v>
       </c>
       <c r="E77">
-        <v>11.29999999999999</v>
+        <v>11.728</v>
       </c>
       <c r="F77">
-        <v>32.09999999999999</v>
+        <v>32.528</v>
       </c>
       <c r="G77">
         <v>0.821</v>
@@ -7601,37 +7601,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M77">
-        <v>7.569179999999999</v>
+        <v>7.6701024</v>
       </c>
       <c r="N77">
-        <v>-4.426513333333332</v>
+        <v>-4.527435733333333</v>
       </c>
       <c r="O77">
-        <v>-0.6639769999999998</v>
+        <v>-0.6791153599999999</v>
       </c>
       <c r="P77">
-        <v>-3.762536333333332</v>
+        <v>-3.848320373333333</v>
       </c>
       <c r="Q77">
-        <v>-3.638536333333332</v>
+        <v>-3.724320373333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1608447766841529</v>
+        <v>0.1656383090459926</v>
       </c>
       <c r="T77">
-        <v>2.107085487027022</v>
+        <v>2.194880715653148</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06227887300870108</v>
+        <v>0.06145941415332343</v>
       </c>
       <c r="W77">
-        <v>0.2211146417445483</v>
+        <v>0.2213078701426463</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4151924867246739</v>
+        <v>0.4097294276888229</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2079471754794494</v>
+        <v>0.2098471754794494</v>
       </c>
       <c r="C78">
-        <v>-23.79181954039394</v>
+        <v>-24.31149343132988</v>
       </c>
       <c r="D78">
-        <v>7.915180459606054</v>
+        <v>7.823506568670114</v>
       </c>
       <c r="E78">
-        <v>11.728</v>
+        <v>12.156</v>
       </c>
       <c r="F78">
-        <v>32.528</v>
+        <v>32.956</v>
       </c>
       <c r="G78">
         <v>0.821</v>
@@ -7683,37 +7683,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M78">
-        <v>7.6701024</v>
+        <v>7.771024799999999</v>
       </c>
       <c r="N78">
-        <v>-4.527435733333333</v>
+        <v>-4.628358133333332</v>
       </c>
       <c r="O78">
-        <v>-0.6791153599999999</v>
+        <v>-0.6942537199999999</v>
       </c>
       <c r="P78">
-        <v>-3.848320373333333</v>
+        <v>-3.934104413333332</v>
       </c>
       <c r="Q78">
-        <v>-3.724320373333333</v>
+        <v>-3.810104413333332</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1656383090459926</v>
+        <v>0.1708486703088618</v>
       </c>
       <c r="T78">
-        <v>2.194880715653148</v>
+        <v>2.290310311985893</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06145941415332343</v>
+        <v>0.06066123994354002</v>
       </c>
       <c r="W78">
-        <v>0.2213078701426463</v>
+        <v>0.2214960796213133</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4097294276888229</v>
+        <v>0.4044082662902668</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2098471754794494</v>
+        <v>0.2117471754794495</v>
       </c>
       <c r="C79">
-        <v>-24.31149343132988</v>
+        <v>-24.82906809530067</v>
       </c>
       <c r="D79">
-        <v>7.823506568670114</v>
+        <v>7.733931904699327</v>
       </c>
       <c r="E79">
-        <v>12.156</v>
+        <v>12.584</v>
       </c>
       <c r="F79">
-        <v>32.956</v>
+        <v>33.384</v>
       </c>
       <c r="G79">
         <v>0.821</v>
@@ -7765,37 +7765,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M79">
-        <v>7.771024799999999</v>
+        <v>7.8719472</v>
       </c>
       <c r="N79">
-        <v>-4.628358133333332</v>
+        <v>-4.729280533333333</v>
       </c>
       <c r="O79">
-        <v>-0.6942537199999999</v>
+        <v>-0.70939208</v>
       </c>
       <c r="P79">
-        <v>-3.934104413333332</v>
+        <v>-4.019888453333333</v>
       </c>
       <c r="Q79">
-        <v>-3.810104413333332</v>
+        <v>-3.895888453333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1708486703088618</v>
+        <v>0.1765327007774465</v>
       </c>
       <c r="T79">
-        <v>2.290310311985893</v>
+        <v>2.394415326167071</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06066123994354002</v>
+        <v>0.05988353173913565</v>
       </c>
       <c r="W79">
-        <v>0.2214960796213133</v>
+        <v>0.2216794632159118</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4044082662902668</v>
+        <v>0.3992235449275711</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2117471754794495</v>
+        <v>0.2136471754794494</v>
       </c>
       <c r="C80">
-        <v>-24.82906809530067</v>
+        <v>-25.34461482092745</v>
       </c>
       <c r="D80">
-        <v>7.733931904699327</v>
+        <v>7.64638517907255</v>
       </c>
       <c r="E80">
-        <v>12.584</v>
+        <v>13.012</v>
       </c>
       <c r="F80">
-        <v>33.384</v>
+        <v>33.812</v>
       </c>
       <c r="G80">
         <v>0.821</v>
@@ -7847,37 +7847,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M80">
-        <v>7.8719472</v>
+        <v>7.9728696</v>
       </c>
       <c r="N80">
-        <v>-4.729280533333333</v>
+        <v>-4.830202933333333</v>
       </c>
       <c r="O80">
-        <v>-0.70939208</v>
+        <v>-0.72453044</v>
       </c>
       <c r="P80">
-        <v>-4.019888453333333</v>
+        <v>-4.105672493333334</v>
       </c>
       <c r="Q80">
-        <v>-3.895888453333333</v>
+        <v>-3.981672493333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1765327007774465</v>
+        <v>0.1827580674811344</v>
       </c>
       <c r="T80">
-        <v>2.394415326167071</v>
+        <v>2.508435103603597</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05988353173913565</v>
+        <v>0.05912551235003266</v>
       </c>
       <c r="W80">
-        <v>0.2216794632159118</v>
+        <v>0.2218582041878623</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3992235449275711</v>
+        <v>0.3941700823335511</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2136471754794494</v>
+        <v>0.2155471754794495</v>
       </c>
       <c r="C81">
-        <v>-25.34461482092745</v>
+        <v>-25.85820170506383</v>
       </c>
       <c r="D81">
-        <v>7.64638517907255</v>
+        <v>7.560798294936169</v>
       </c>
       <c r="E81">
-        <v>13.012</v>
+        <v>13.44</v>
       </c>
       <c r="F81">
-        <v>33.812</v>
+        <v>34.24</v>
       </c>
       <c r="G81">
         <v>0.821</v>
@@ -7929,37 +7929,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M81">
-        <v>7.9728696</v>
+        <v>8.073792000000001</v>
       </c>
       <c r="N81">
-        <v>-4.830202933333333</v>
+        <v>-4.931125333333334</v>
       </c>
       <c r="O81">
-        <v>-0.72453044</v>
+        <v>-0.7396688000000001</v>
       </c>
       <c r="P81">
-        <v>-4.105672493333334</v>
+        <v>-4.191456533333334</v>
       </c>
       <c r="Q81">
-        <v>-3.981672493333333</v>
+        <v>-4.067456533333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1827580674811344</v>
+        <v>0.1896059708551911</v>
       </c>
       <c r="T81">
-        <v>2.508435103603597</v>
+        <v>2.633856858783778</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05912551235003266</v>
+        <v>0.05838644344565726</v>
       </c>
       <c r="W81">
-        <v>0.2218582041878623</v>
+        <v>0.222032476635514</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3941700823335511</v>
+        <v>0.3892429563043817</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2155471754794495</v>
+        <v>0.2174471754794494</v>
       </c>
       <c r="C82">
-        <v>-25.85820170506383</v>
+        <v>-26.36989382944778</v>
       </c>
       <c r="D82">
-        <v>7.560798294936169</v>
+        <v>7.477106170552225</v>
       </c>
       <c r="E82">
-        <v>13.44</v>
+        <v>13.868</v>
       </c>
       <c r="F82">
-        <v>34.24</v>
+        <v>34.668</v>
       </c>
       <c r="G82">
         <v>0.821</v>
@@ -8011,37 +8011,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M82">
-        <v>8.073792000000001</v>
+        <v>8.174714400000001</v>
       </c>
       <c r="N82">
-        <v>-4.931125333333334</v>
+        <v>-5.032047733333334</v>
       </c>
       <c r="O82">
-        <v>-0.7396688000000001</v>
+        <v>-0.75480716</v>
       </c>
       <c r="P82">
-        <v>-4.191456533333334</v>
+        <v>-4.277240573333334</v>
       </c>
       <c r="Q82">
-        <v>-4.067456533333334</v>
+        <v>-4.153240573333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1896059708551911</v>
+        <v>0.1971747061633591</v>
       </c>
       <c r="T82">
-        <v>2.633856858783778</v>
+        <v>2.772480903982924</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05838644344565726</v>
+        <v>0.05766562315620469</v>
       </c>
       <c r="W82">
-        <v>0.222032476635514</v>
+        <v>0.2222024460597669</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3892429563043817</v>
+        <v>0.3844374877080313</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2174471754794494</v>
+        <v>0.2193471754794494</v>
       </c>
       <c r="C83">
-        <v>-26.36989382944778</v>
+        <v>-26.87975342574948</v>
       </c>
       <c r="D83">
-        <v>7.477106170552225</v>
+        <v>7.395246574250518</v>
       </c>
       <c r="E83">
-        <v>13.868</v>
+        <v>14.296</v>
       </c>
       <c r="F83">
-        <v>34.668</v>
+        <v>35.096</v>
       </c>
       <c r="G83">
         <v>0.821</v>
@@ -8093,37 +8093,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M83">
-        <v>8.174714400000001</v>
+        <v>8.275636800000001</v>
       </c>
       <c r="N83">
-        <v>-5.032047733333334</v>
+        <v>-5.132970133333334</v>
       </c>
       <c r="O83">
-        <v>-0.75480716</v>
+        <v>-0.76994552</v>
       </c>
       <c r="P83">
-        <v>-4.277240573333334</v>
+        <v>-4.363024613333334</v>
       </c>
       <c r="Q83">
-        <v>-4.153240573333334</v>
+        <v>-4.239024613333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1971747061633591</v>
+        <v>0.2055844120613235</v>
       </c>
       <c r="T83">
-        <v>2.772480903982924</v>
+        <v>2.926507620870864</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05766562315620469</v>
+        <v>0.05696238384942171</v>
       </c>
       <c r="W83">
-        <v>0.2222024460597669</v>
+        <v>0.2223682698883064</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3844374877080313</v>
+        <v>0.3797492256628114</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2193471754794494</v>
+        <v>0.2212471754794494</v>
       </c>
       <c r="C84">
-        <v>-26.87975342574948</v>
+        <v>-27.38784002989503</v>
       </c>
       <c r="D84">
-        <v>7.395246574250518</v>
+        <v>7.315159970104974</v>
       </c>
       <c r="E84">
-        <v>14.296</v>
+        <v>14.724</v>
       </c>
       <c r="F84">
-        <v>35.096</v>
+        <v>35.524</v>
       </c>
       <c r="G84">
         <v>0.821</v>
@@ -8175,37 +8175,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M84">
-        <v>8.275636800000001</v>
+        <v>8.376559200000001</v>
       </c>
       <c r="N84">
-        <v>-5.132970133333334</v>
+        <v>-5.233892533333334</v>
       </c>
       <c r="O84">
-        <v>-0.76994552</v>
+        <v>-0.7850838800000001</v>
       </c>
       <c r="P84">
-        <v>-4.363024613333334</v>
+        <v>-4.448808653333334</v>
       </c>
       <c r="Q84">
-        <v>-4.239024613333334</v>
+        <v>-4.324808653333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2055844120613235</v>
+        <v>0.2149834951237543</v>
       </c>
       <c r="T84">
-        <v>2.926507620870864</v>
+        <v>3.098655127980916</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05696238384942171</v>
+        <v>0.05627609006810338</v>
       </c>
       <c r="W84">
-        <v>0.2223682698883064</v>
+        <v>0.2225300979619412</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3797492256628114</v>
+        <v>0.3751739337873559</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2212471754794494</v>
+        <v>0.2231471754794495</v>
       </c>
       <c r="C85">
-        <v>-27.38784002989503</v>
+        <v>-27.89421062646993</v>
       </c>
       <c r="D85">
-        <v>7.315159970104974</v>
+        <v>7.236789373530064</v>
       </c>
       <c r="E85">
-        <v>14.724</v>
+        <v>15.152</v>
       </c>
       <c r="F85">
-        <v>35.524</v>
+        <v>35.952</v>
       </c>
       <c r="G85">
         <v>0.821</v>
@@ -8257,37 +8257,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M85">
-        <v>8.376559200000001</v>
+        <v>8.477481599999999</v>
       </c>
       <c r="N85">
-        <v>-5.233892533333334</v>
+        <v>-5.334814933333332</v>
       </c>
       <c r="O85">
-        <v>-0.7850838800000001</v>
+        <v>-0.8002222399999998</v>
       </c>
       <c r="P85">
-        <v>-4.448808653333334</v>
+        <v>-4.534592693333332</v>
       </c>
       <c r="Q85">
-        <v>-4.324808653333334</v>
+        <v>-4.410592693333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2149834951237543</v>
+        <v>0.225557463568989</v>
       </c>
       <c r="T85">
-        <v>3.098655127980916</v>
+        <v>3.292321073479723</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05627609006810338</v>
+        <v>0.05560613661491168</v>
       </c>
       <c r="W85">
-        <v>0.2225300979619412</v>
+        <v>0.2226880729862039</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3751739337873559</v>
+        <v>0.3707075774327445</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2231471754794495</v>
+        <v>0.2250471754794494</v>
       </c>
       <c r="C86">
-        <v>-27.89421062646993</v>
+        <v>-28.39891978393882</v>
       </c>
       <c r="D86">
-        <v>7.236789373530064</v>
+        <v>7.160080216061176</v>
       </c>
       <c r="E86">
-        <v>15.152</v>
+        <v>15.57999999999999</v>
       </c>
       <c r="F86">
-        <v>35.952</v>
+        <v>36.38</v>
       </c>
       <c r="G86">
         <v>0.821</v>
@@ -8339,37 +8339,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M86">
-        <v>8.477481599999999</v>
+        <v>8.578403999999999</v>
       </c>
       <c r="N86">
-        <v>-5.334814933333332</v>
+        <v>-5.435737333333332</v>
       </c>
       <c r="O86">
-        <v>-0.8002222399999998</v>
+        <v>-0.8153605999999998</v>
       </c>
       <c r="P86">
-        <v>-4.534592693333332</v>
+        <v>-4.620376733333332</v>
       </c>
       <c r="Q86">
-        <v>-4.410592693333332</v>
+        <v>-4.496376733333332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2255574635689889</v>
+        <v>0.2375412944735881</v>
       </c>
       <c r="T86">
-        <v>3.292321073479721</v>
+        <v>3.511809145045036</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05560613661491168</v>
+        <v>0.0549519467723833</v>
       </c>
       <c r="W86">
-        <v>0.2226880729862039</v>
+        <v>0.222842330951072</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3707075774327445</v>
+        <v>0.3663463118158887</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2250471754794494</v>
+        <v>0.2269471754794494</v>
       </c>
       <c r="C87">
-        <v>-28.39891978393882</v>
+        <v>-28.90201978135534</v>
       </c>
       <c r="D87">
-        <v>7.160080216061176</v>
+        <v>7.084980218644657</v>
       </c>
       <c r="E87">
-        <v>15.57999999999999</v>
+        <v>16.008</v>
       </c>
       <c r="F87">
-        <v>36.38</v>
+        <v>36.808</v>
       </c>
       <c r="G87">
         <v>0.821</v>
@@ -8421,37 +8421,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M87">
-        <v>8.578403999999999</v>
+        <v>8.679326400000001</v>
       </c>
       <c r="N87">
-        <v>-5.435737333333332</v>
+        <v>-5.536659733333334</v>
       </c>
       <c r="O87">
-        <v>-0.8153605999999998</v>
+        <v>-0.83049896</v>
       </c>
       <c r="P87">
-        <v>-4.620376733333332</v>
+        <v>-4.706160773333334</v>
       </c>
       <c r="Q87">
-        <v>-4.496376733333332</v>
+        <v>-4.582160773333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2375412944735881</v>
+        <v>0.2512371012217015</v>
       </c>
       <c r="T87">
-        <v>3.511809145045036</v>
+        <v>3.762652655405395</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0549519467723833</v>
+        <v>0.05431297064712303</v>
       </c>
       <c r="W87">
-        <v>0.222842330951072</v>
+        <v>0.2229930015214084</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3663463118158887</v>
+        <v>0.3620864709808203</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2269471754794494</v>
+        <v>0.2288471754794494</v>
       </c>
       <c r="C88">
-        <v>-28.90201978135534</v>
+        <v>-29.40356072718073</v>
       </c>
       <c r="D88">
-        <v>7.084980218644657</v>
+        <v>7.011439272819265</v>
       </c>
       <c r="E88">
-        <v>16.008</v>
+        <v>16.436</v>
       </c>
       <c r="F88">
-        <v>36.808</v>
+        <v>37.236</v>
       </c>
       <c r="G88">
         <v>0.821</v>
@@ -8503,37 +8503,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M88">
-        <v>8.679326400000001</v>
+        <v>8.780248799999999</v>
       </c>
       <c r="N88">
-        <v>-5.536659733333334</v>
+        <v>-5.637582133333332</v>
       </c>
       <c r="O88">
-        <v>-0.83049896</v>
+        <v>-0.8456373199999998</v>
       </c>
       <c r="P88">
-        <v>-4.706160773333334</v>
+        <v>-4.791944813333332</v>
       </c>
       <c r="Q88">
-        <v>-4.582160773333334</v>
+        <v>-4.667944813333333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2512371012217015</v>
+        <v>0.2670399551618324</v>
       </c>
       <c r="T88">
-        <v>3.762652655405395</v>
+        <v>4.052087475051964</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05431297064712303</v>
+        <v>0.05368868362819059</v>
       </c>
       <c r="W88">
-        <v>0.2229930015214084</v>
+        <v>0.2231402084004727</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3620864709808203</v>
+        <v>0.3579245575212706</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2288471754794494</v>
+        <v>0.2307471754794495</v>
       </c>
       <c r="C89">
-        <v>-29.40356072718073</v>
+        <v>-29.90359067077853</v>
       </c>
       <c r="D89">
-        <v>7.011439272819265</v>
+        <v>6.939409329221468</v>
       </c>
       <c r="E89">
-        <v>16.436</v>
+        <v>16.86399999999999</v>
       </c>
       <c r="F89">
-        <v>37.236</v>
+        <v>37.66399999999999</v>
       </c>
       <c r="G89">
         <v>0.821</v>
@@ -8585,37 +8585,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M89">
-        <v>8.780248799999999</v>
+        <v>8.881171199999999</v>
       </c>
       <c r="N89">
-        <v>-5.637582133333332</v>
+        <v>-5.738504533333332</v>
       </c>
       <c r="O89">
-        <v>-0.8456373199999998</v>
+        <v>-0.8607756799999998</v>
       </c>
       <c r="P89">
-        <v>-4.791944813333332</v>
+        <v>-4.877728853333332</v>
       </c>
       <c r="Q89">
-        <v>-4.667944813333333</v>
+        <v>-4.753728853333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2670399551618324</v>
+        <v>0.2854766180919852</v>
       </c>
       <c r="T89">
-        <v>4.052087475051964</v>
+        <v>4.389761431306296</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05368868362819059</v>
+        <v>0.05307858495059752</v>
       </c>
       <c r="W89">
-        <v>0.2231402084004727</v>
+        <v>0.2232840696686491</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3579245575212706</v>
+        <v>0.3538572330039834</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2307471754794495</v>
+        <v>0.2326471754794494</v>
       </c>
       <c r="C90">
-        <v>-29.90359067077853</v>
+        <v>-30.40215570710668</v>
       </c>
       <c r="D90">
-        <v>6.939409329221468</v>
+        <v>6.868844292893316</v>
       </c>
       <c r="E90">
-        <v>16.86399999999999</v>
+        <v>17.292</v>
       </c>
       <c r="F90">
-        <v>37.66399999999999</v>
+        <v>38.092</v>
       </c>
       <c r="G90">
         <v>0.821</v>
@@ -8667,37 +8667,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M90">
-        <v>8.881171199999999</v>
+        <v>8.982093600000001</v>
       </c>
       <c r="N90">
-        <v>-5.738504533333332</v>
+        <v>-5.839426933333334</v>
       </c>
       <c r="O90">
-        <v>-0.8607756799999998</v>
+        <v>-0.8759140400000001</v>
       </c>
       <c r="P90">
-        <v>-4.877728853333332</v>
+        <v>-4.963512893333334</v>
       </c>
       <c r="Q90">
-        <v>-4.753728853333333</v>
+        <v>-4.839512893333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2854766180919852</v>
+        <v>0.3072654015548929</v>
       </c>
       <c r="T90">
-        <v>4.389761431306296</v>
+        <v>4.78883065233414</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05307858495059752</v>
+        <v>0.05248219635564697</v>
       </c>
       <c r="W90">
-        <v>0.2232840696686491</v>
+        <v>0.2234246980993385</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3538572330039834</v>
+        <v>0.3498813090376465</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2326471754794494</v>
+        <v>0.2345471754794494</v>
       </c>
       <c r="C91">
-        <v>-30.40215570710668</v>
+        <v>-30.89930007508647</v>
       </c>
       <c r="D91">
-        <v>6.868844292893316</v>
+        <v>6.799699924913523</v>
       </c>
       <c r="E91">
-        <v>17.292</v>
+        <v>17.72</v>
       </c>
       <c r="F91">
-        <v>38.092</v>
+        <v>38.52</v>
       </c>
       <c r="G91">
         <v>0.821</v>
@@ -8749,37 +8749,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M91">
-        <v>8.982093600000001</v>
+        <v>9.083015999999999</v>
       </c>
       <c r="N91">
-        <v>-5.839426933333334</v>
+        <v>-5.940349333333332</v>
       </c>
       <c r="O91">
-        <v>-0.8759140400000001</v>
+        <v>-0.8910523999999997</v>
       </c>
       <c r="P91">
-        <v>-4.963512893333334</v>
+        <v>-5.049296933333332</v>
       </c>
       <c r="Q91">
-        <v>-4.839512893333334</v>
+        <v>-4.925296933333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3072654015548929</v>
+        <v>0.3334119417103822</v>
       </c>
       <c r="T91">
-        <v>4.78883065233414</v>
+        <v>5.267713717567555</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05248219635564697</v>
+        <v>0.05189906084058424</v>
       </c>
       <c r="W91">
-        <v>0.2234246980993385</v>
+        <v>0.2235622014537902</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3498813090376465</v>
+        <v>0.3459937389372283</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2345471754794494</v>
+        <v>0.2364471754794494</v>
       </c>
       <c r="C92">
-        <v>-30.89930007508647</v>
+        <v>-31.39506625008931</v>
       </c>
       <c r="D92">
-        <v>6.799699924913523</v>
+        <v>6.731933749910693</v>
       </c>
       <c r="E92">
-        <v>17.72</v>
+        <v>18.148</v>
       </c>
       <c r="F92">
-        <v>38.52</v>
+        <v>38.948</v>
       </c>
       <c r="G92">
         <v>0.821</v>
@@ -8831,37 +8831,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M92">
-        <v>9.083015999999999</v>
+        <v>9.183938400000001</v>
       </c>
       <c r="N92">
-        <v>-5.940349333333332</v>
+        <v>-6.041271733333334</v>
       </c>
       <c r="O92">
-        <v>-0.8910523999999997</v>
+        <v>-0.90619076</v>
       </c>
       <c r="P92">
-        <v>-5.049296933333332</v>
+        <v>-5.135080973333333</v>
       </c>
       <c r="Q92">
-        <v>-4.925296933333333</v>
+        <v>-5.011080973333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3334119417103822</v>
+        <v>0.365368824122647</v>
       </c>
       <c r="T92">
-        <v>5.267713717567555</v>
+        <v>5.853015241741729</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05189906084058424</v>
+        <v>0.0513287414906877</v>
       </c>
       <c r="W92">
-        <v>0.2235622014537902</v>
+        <v>0.2236966827564958</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3459937389372283</v>
+        <v>0.342191609937918</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2364471754794494</v>
+        <v>0.2383471754794495</v>
       </c>
       <c r="C93">
-        <v>-31.39506625008931</v>
+        <v>-31.88949503094772</v>
       </c>
       <c r="D93">
-        <v>6.731933749910693</v>
+        <v>6.665504969052279</v>
       </c>
       <c r="E93">
-        <v>18.148</v>
+        <v>18.576</v>
       </c>
       <c r="F93">
-        <v>38.948</v>
+        <v>39.376</v>
       </c>
       <c r="G93">
         <v>0.821</v>
@@ -8913,37 +8913,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M93">
-        <v>9.183938400000001</v>
+        <v>9.284860800000001</v>
       </c>
       <c r="N93">
-        <v>-6.041271733333334</v>
+        <v>-6.142194133333334</v>
       </c>
       <c r="O93">
-        <v>-0.90619076</v>
+        <v>-0.92132912</v>
       </c>
       <c r="P93">
-        <v>-5.135080973333333</v>
+        <v>-5.220865013333333</v>
       </c>
       <c r="Q93">
-        <v>-5.011080973333334</v>
+        <v>-5.096865013333334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.365368824122647</v>
+        <v>0.405314927137978</v>
       </c>
       <c r="T93">
-        <v>5.853015241741729</v>
+        <v>6.584642146959447</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0513287414906877</v>
+        <v>0.05077082038752805</v>
       </c>
       <c r="W93">
-        <v>0.2236966827564958</v>
+        <v>0.2238282405526209</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.342191609937918</v>
+        <v>0.3384721359168537</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2383471754794495</v>
+        <v>0.2402471754794495</v>
       </c>
       <c r="C94">
-        <v>-31.88949503094772</v>
+        <v>-32.38262562186514</v>
       </c>
       <c r="D94">
-        <v>6.665504969052279</v>
+        <v>6.600374378134864</v>
       </c>
       <c r="E94">
-        <v>18.576</v>
+        <v>19.004</v>
       </c>
       <c r="F94">
-        <v>39.376</v>
+        <v>39.804</v>
       </c>
       <c r="G94">
         <v>0.821</v>
@@ -8995,37 +8995,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M94">
-        <v>9.284860800000001</v>
+        <v>9.385783200000001</v>
       </c>
       <c r="N94">
-        <v>-6.142194133333334</v>
+        <v>-6.243116533333334</v>
       </c>
       <c r="O94">
-        <v>-0.92132912</v>
+        <v>-0.93646748</v>
       </c>
       <c r="P94">
-        <v>-5.220865013333333</v>
+        <v>-5.306649053333333</v>
       </c>
       <c r="Q94">
-        <v>-5.096865013333334</v>
+        <v>-5.182649053333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.405314927137978</v>
+        <v>0.4566742024434035</v>
       </c>
       <c r="T94">
-        <v>6.584642146959447</v>
+        <v>7.525305310810797</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05077082038752805</v>
+        <v>0.05022489758766216</v>
       </c>
       <c r="W94">
-        <v>0.2238282405526209</v>
+        <v>0.2239569691488293</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3384721359168537</v>
+        <v>0.3348326505844144</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2402471754794495</v>
+        <v>0.2421471754794495</v>
       </c>
       <c r="C95">
-        <v>-32.38262562186514</v>
+        <v>-32.87449570956991</v>
       </c>
       <c r="D95">
-        <v>6.600374378134864</v>
+        <v>6.536504290430091</v>
       </c>
       <c r="E95">
-        <v>19.004</v>
+        <v>19.432</v>
       </c>
       <c r="F95">
-        <v>39.804</v>
+        <v>40.232</v>
       </c>
       <c r="G95">
         <v>0.821</v>
@@ -9077,37 +9077,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M95">
-        <v>9.385783200000001</v>
+        <v>9.486705600000001</v>
       </c>
       <c r="N95">
-        <v>-6.243116533333334</v>
+        <v>-6.344038933333334</v>
       </c>
       <c r="O95">
-        <v>-0.93646748</v>
+        <v>-0.95160584</v>
       </c>
       <c r="P95">
-        <v>-5.306649053333333</v>
+        <v>-5.392433093333334</v>
       </c>
       <c r="Q95">
-        <v>-5.182649053333334</v>
+        <v>-5.268433093333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4566742024434035</v>
+        <v>0.5251532361839708</v>
       </c>
       <c r="T95">
-        <v>7.525305310810797</v>
+        <v>8.7795228626126</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05022489758766216</v>
+        <v>0.04969059016651681</v>
       </c>
       <c r="W95">
-        <v>0.2239569691488293</v>
+        <v>0.2240829588387354</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3348326505844144</v>
+        <v>0.3312706011101121</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2421471754794495</v>
+        <v>0.2440471754794495</v>
       </c>
       <c r="C96">
-        <v>-32.87449570956991</v>
+        <v>-33.36514153603267</v>
       </c>
       <c r="D96">
-        <v>6.536504290430091</v>
+        <v>6.473858463967335</v>
       </c>
       <c r="E96">
-        <v>19.432</v>
+        <v>19.86</v>
       </c>
       <c r="F96">
-        <v>40.232</v>
+        <v>40.66</v>
       </c>
       <c r="G96">
         <v>0.821</v>
@@ -9159,37 +9159,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M96">
-        <v>9.486705600000001</v>
+        <v>9.587628</v>
       </c>
       <c r="N96">
-        <v>-6.344038933333334</v>
+        <v>-6.444961333333334</v>
       </c>
       <c r="O96">
-        <v>-0.95160584</v>
+        <v>-0.9667441999999999</v>
       </c>
       <c r="P96">
-        <v>-5.392433093333334</v>
+        <v>-5.478217133333334</v>
       </c>
       <c r="Q96">
-        <v>-5.268433093333334</v>
+        <v>-5.354217133333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5251532361839708</v>
+        <v>0.6210238834207651</v>
       </c>
       <c r="T96">
-        <v>8.7795228626126</v>
+        <v>10.53542743513512</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04969059016651681</v>
+        <v>0.04916753132265875</v>
       </c>
       <c r="W96">
-        <v>0.2240829588387354</v>
+        <v>0.2242062961141171</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3312706011101121</v>
+        <v>0.3277835421510583</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2440471754794495</v>
+        <v>0.2459471754794494</v>
       </c>
       <c r="C97">
-        <v>-33.36514153603267</v>
+        <v>-33.85459796704185</v>
       </c>
       <c r="D97">
-        <v>6.473858463967335</v>
+        <v>6.412402032958143</v>
       </c>
       <c r="E97">
-        <v>19.86</v>
+        <v>20.288</v>
       </c>
       <c r="F97">
-        <v>40.66</v>
+        <v>41.088</v>
       </c>
       <c r="G97">
         <v>0.821</v>
@@ -9241,37 +9241,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M97">
-        <v>9.587628</v>
+        <v>9.6885504</v>
       </c>
       <c r="N97">
-        <v>-6.444961333333334</v>
+        <v>-6.545883733333334</v>
       </c>
       <c r="O97">
-        <v>-0.9667441999999999</v>
+        <v>-0.98188256</v>
       </c>
       <c r="P97">
-        <v>-5.478217133333334</v>
+        <v>-5.564001173333334</v>
       </c>
       <c r="Q97">
-        <v>-5.354217133333334</v>
+        <v>-5.440001173333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6210238834207651</v>
+        <v>0.7648298542759567</v>
       </c>
       <c r="T97">
-        <v>10.53542743513512</v>
+        <v>13.16928429391891</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04916753132265875</v>
+        <v>0.04865536953804771</v>
       </c>
       <c r="W97">
-        <v>0.2242062961141171</v>
+        <v>0.2243270638629284</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3277835421510583</v>
+        <v>0.3243691302536514</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2459471754794494</v>
+        <v>0.2478471754794494</v>
       </c>
       <c r="C98">
-        <v>-33.85459796704185</v>
+        <v>-34.34289855691009</v>
       </c>
       <c r="D98">
-        <v>6.412402032958143</v>
+        <v>6.352101443089915</v>
       </c>
       <c r="E98">
-        <v>20.28799999999999</v>
+        <v>20.716</v>
       </c>
       <c r="F98">
-        <v>41.08799999999999</v>
+        <v>41.516</v>
       </c>
       <c r="G98">
         <v>0.821</v>
@@ -9323,37 +9323,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M98">
-        <v>9.688550399999999</v>
+        <v>9.7894728</v>
       </c>
       <c r="N98">
-        <v>-6.545883733333332</v>
+        <v>-6.646806133333333</v>
       </c>
       <c r="O98">
-        <v>-0.9818825599999997</v>
+        <v>-0.99702092</v>
       </c>
       <c r="P98">
-        <v>-5.564001173333332</v>
+        <v>-5.649785213333334</v>
       </c>
       <c r="Q98">
-        <v>-5.440001173333332</v>
+        <v>-5.525785213333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7648298542759548</v>
+        <v>1.00450647236794</v>
       </c>
       <c r="T98">
-        <v>13.16928429391887</v>
+        <v>17.55904572522517</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04865536953804772</v>
+        <v>0.0481537677902328</v>
       </c>
       <c r="W98">
-        <v>0.2243270638629284</v>
+        <v>0.2244453415550631</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3243691302536515</v>
+        <v>0.3210251186015519</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2478471754794494</v>
+        <v>0.2497471754794494</v>
       </c>
       <c r="C99">
-        <v>-34.34289855691009</v>
+        <v>-34.83007560956354</v>
       </c>
       <c r="D99">
-        <v>6.352101443089915</v>
+        <v>6.292924390436457</v>
       </c>
       <c r="E99">
-        <v>20.716</v>
+        <v>21.14399999999999</v>
       </c>
       <c r="F99">
-        <v>41.516</v>
+        <v>41.944</v>
       </c>
       <c r="G99">
         <v>0.821</v>
@@ -9405,37 +9405,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M99">
-        <v>9.7894728</v>
+        <v>9.890395199999999</v>
       </c>
       <c r="N99">
-        <v>-6.646806133333333</v>
+        <v>-6.747728533333332</v>
       </c>
       <c r="O99">
-        <v>-0.99702092</v>
+        <v>-1.01215928</v>
       </c>
       <c r="P99">
-        <v>-5.649785213333334</v>
+        <v>-5.735569253333332</v>
       </c>
       <c r="Q99">
-        <v>-5.525785213333334</v>
+        <v>-5.611569253333332</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.00450647236794</v>
+        <v>1.48385970855191</v>
       </c>
       <c r="T99">
-        <v>17.55904572522517</v>
+        <v>26.33856858783775</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0481537677902328</v>
+        <v>0.04766240281278145</v>
       </c>
       <c r="W99">
-        <v>0.2244453415550631</v>
+        <v>0.2245612054167462</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3210251186015519</v>
+        <v>0.3177493520852096</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2497471754794494</v>
+        <v>0.2516471754794495</v>
       </c>
       <c r="C100">
-        <v>-34.83007560956354</v>
+        <v>-35.31616023624827</v>
       </c>
       <c r="D100">
-        <v>6.292924390436457</v>
+        <v>6.234839763751729</v>
       </c>
       <c r="E100">
-        <v>21.14399999999999</v>
+        <v>21.572</v>
       </c>
       <c r="F100">
-        <v>41.944</v>
+        <v>42.372</v>
       </c>
       <c r="G100">
         <v>0.821</v>
@@ -9487,37 +9487,37 @@
         <v>3.142666666666667</v>
       </c>
       <c r="M100">
-        <v>9.890395199999999</v>
+        <v>9.9913176</v>
       </c>
       <c r="N100">
-        <v>-6.747728533333332</v>
+        <v>-6.848650933333333</v>
       </c>
       <c r="O100">
-        <v>-1.01215928</v>
+        <v>-1.02729764</v>
       </c>
       <c r="P100">
-        <v>-5.735569253333332</v>
+        <v>-5.821353293333333</v>
       </c>
       <c r="Q100">
-        <v>-5.611569253333332</v>
+        <v>-5.697353293333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.48385970855191</v>
+        <v>2.921919417103819</v>
       </c>
       <c r="T100">
-        <v>26.33856858783775</v>
+        <v>52.6771371756755</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04766240281278145</v>
+        <v>0.04718096440053111</v>
       </c>
       <c r="W100">
-        <v>0.2245612054167462</v>
+        <v>0.2246747285943548</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3177493520852096</v>
+        <v>0.3145397626702074</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2516471754794495</v>
-      </c>
-      <c r="C101">
-        <v>-35.31616023624827</v>
-      </c>
-      <c r="D101">
-        <v>6.234839763751729</v>
-      </c>
-      <c r="E101">
-        <v>21.572</v>
-      </c>
-      <c r="F101">
-        <v>42.372</v>
-      </c>
-      <c r="G101">
-        <v>0.821</v>
-      </c>
-      <c r="H101">
-        <v>22</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.124</v>
-      </c>
-      <c r="L101">
-        <v>3.142666666666667</v>
-      </c>
-      <c r="M101">
-        <v>9.9913176</v>
-      </c>
-      <c r="N101">
-        <v>-6.848650933333333</v>
-      </c>
-      <c r="O101">
-        <v>-1.02729764</v>
-      </c>
-      <c r="P101">
-        <v>-5.821353293333333</v>
-      </c>
-      <c r="Q101">
-        <v>-5.697353293333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.921919417103819</v>
-      </c>
-      <c r="T101">
-        <v>52.6771371756755</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04718096440053111</v>
-      </c>
-      <c r="W101">
-        <v>0.2246747285943548</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3145397626702074</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
